--- a/IPA_Zeitplan_Nicola_Maeder.xlsx
+++ b/IPA_Zeitplan_Nicola_Maeder.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taamanii\Documents\Individuelle Praktische Arbeit Nicola\individuelle-praktische-arbeit-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B6B5C4-84BA-4C51-B86F-56CA60715ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A327F332-557B-489B-BEA6-2F23E1117D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{09F15F46-AED7-3C4E-9C62-04C59C5DDA6F}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
   <si>
     <t>Tag</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Aussehen des Webinterfaces &amp; des PDF Reporting</t>
   </si>
   <si>
-    <t>Projektmanagementmethoden</t>
-  </si>
-  <si>
     <t>Kurzfassung schreiben</t>
   </si>
   <si>
@@ -263,6 +260,12 @@
   <si>
     <t>ZEITPLAN Nicola Maeder 22.4.2026</t>
   </si>
+  <si>
+    <t>Projektmanagementmethoden, Arbeitsorganisation</t>
+  </si>
+  <si>
+    <t>F+A6:D86ALSCH</t>
+  </si>
 </sst>
 </file>
 
@@ -272,9 +275,16 @@
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -793,69 +803,69 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -863,38 +873,14 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -911,166 +897,190 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="28" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="28" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="28" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="28" borderId="11" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="20" fontId="3" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="32" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="32" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="32" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="32" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="29" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="29" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="15" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1078,7 +1088,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1086,40 +1096,37 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1127,34 +1134,34 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1162,7 +1169,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1170,13 +1177,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1184,7 +1191,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1192,43 +1199,43 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="8" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1236,7 +1243,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1244,13 +1251,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1258,16 +1265,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1275,7 +1279,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1283,25 +1287,25 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="8" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1309,7 +1313,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1317,43 +1321,43 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="11" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="11" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1361,10 +1365,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1372,7 +1376,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1380,13 +1384,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1394,10 +1398,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1405,7 +1409,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1413,40 +1417,40 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="14" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="14" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="14" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1454,7 +1458,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1462,40 +1466,40 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="17" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1503,7 +1507,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1511,13 +1515,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1525,10 +1529,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1536,7 +1540,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1544,13 +1548,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1558,34 +1562,34 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="20" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="20" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1593,7 +1597,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1601,13 +1605,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1615,7 +1619,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1623,22 +1627,22 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="20" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="20" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="20" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="20" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="20" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="20" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1646,7 +1650,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1654,34 +1658,34 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="6" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1689,13 +1693,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1703,13 +1707,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1717,7 +1721,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1725,13 +1729,13 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1739,10 +1743,10 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -1750,88 +1754,103 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="25" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="25" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="28" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="28" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="28" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="28" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="25" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="25" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="25" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="25" borderId="16" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="25" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="25" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="25" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="25" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="32" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="32" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="20" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="20" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2202,8 +2221,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="107" t="s">
-        <v>66</v>
+      <c r="A1" s="288" t="s">
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2286,7 +2305,7 @@
       <c r="BB1" s="86"/>
     </row>
     <row r="2" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="108"/>
+      <c r="A2" s="107"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
@@ -2366,7 +2385,7 @@
       <c r="BB2" s="92"/>
     </row>
     <row r="3" spans="1:54" ht="83.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="108"/>
+      <c r="A3" s="107"/>
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2528,7 +2547,7 @@
       </c>
     </row>
     <row r="4" spans="1:54" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="109"/>
+      <c r="A4" s="108"/>
       <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2557,11 +2576,11 @@
       </c>
       <c r="K4" s="9" cm="1">
         <f t="array" ref="K4">_xlfn.LET(_xlpm.r, K7:K90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L4" s="10" cm="1">
         <f t="array" ref="L4">_xlfn.LET(_xlpm.r, L7:L90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M4" s="10" cm="1">
         <f t="array" ref="M4">_xlfn.LET(_xlpm.r, M7:M92,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
@@ -2796,7 +2815,7 @@
       </c>
       <c r="S5" s="10" cm="1">
         <f t="array" ref="S5">_xlfn.LET(_xlpm.r, S8:S92,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T5" s="11" cm="1">
         <f t="array" ref="T5">_xlfn.LET(_xlpm.r, T8:T92,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
@@ -2892,7 +2911,7 @@
       </c>
       <c r="AQ5" s="19" cm="1">
         <f t="array" ref="AQ5">_xlfn.LET(_xlpm.r, AQ7:AQ90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 1 ) ))</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AR5" s="19" cm="1">
         <f t="array" ref="AR5">_xlfn.LET(_xlpm.r, AR7:AR90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 1 ) ))</f>
@@ -2940,8 +2959,8 @@
       </c>
     </row>
     <row r="6" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="21" t="b">
-        <v>0</v>
+      <c r="A6" s="21" t="s">
+        <v>67</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>13</v>
@@ -3010,7 +3029,7 @@
     </row>
     <row r="7" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" s="99" t="s">
         <v>31</v>
@@ -3085,7 +3104,7 @@
       <c r="C8" s="102"/>
       <c r="D8" s="104"/>
       <c r="E8" s="106"/>
-      <c r="F8" s="27">
+      <c r="F8" s="284">
         <v>1</v>
       </c>
       <c r="G8" s="28"/>
@@ -3138,21 +3157,21 @@
       <c r="BB8" s="29"/>
     </row>
     <row r="9" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="110" t="b">
-        <v>0</v>
-      </c>
-      <c r="B9" s="111" t="s">
+      <c r="A9" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" s="110" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="112">
+      <c r="C9" s="111">
         <f>SUM(F9:BB9)</f>
         <v>0.5</v>
       </c>
-      <c r="D9" s="112">
+      <c r="D9" s="111">
         <f>SUM(F10:BB10)</f>
         <v>0.5</v>
       </c>
-      <c r="E9" s="113">
+      <c r="E9" s="112">
         <f>(AVERAGE(C9,C10)-AVERAGE(D9,D10) )</f>
         <v>0</v>
       </c>
@@ -3215,7 +3234,7 @@
       <c r="D10" s="102"/>
       <c r="E10" s="106"/>
       <c r="F10" s="28"/>
-      <c r="G10" s="28">
+      <c r="G10" s="285">
         <v>0.5</v>
       </c>
       <c r="H10" s="28"/>
@@ -3267,21 +3286,21 @@
       <c r="BB10" s="29"/>
     </row>
     <row r="11" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="110" t="b">
-        <v>0</v>
-      </c>
-      <c r="B11" s="111" t="s">
+      <c r="A11" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" s="110" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="112">
+      <c r="C11" s="111">
         <f>SUM(F11:BB11)</f>
         <v>0.5</v>
       </c>
-      <c r="D11" s="112">
+      <c r="D11" s="111">
         <f>SUM(F12:BB12)</f>
         <v>0.5</v>
       </c>
-      <c r="E11" s="113">
+      <c r="E11" s="112">
         <f>(AVERAGE(C11,C12)-AVERAGE(D11,D12) )</f>
         <v>0</v>
       </c>
@@ -3344,7 +3363,7 @@
       <c r="D12" s="102"/>
       <c r="E12" s="106"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="28">
+      <c r="G12" s="285">
         <v>0.5</v>
       </c>
       <c r="H12" s="28"/>
@@ -3396,21 +3415,21 @@
       <c r="BB12" s="29"/>
     </row>
     <row r="13" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="110" t="b">
-        <v>0</v>
-      </c>
-      <c r="B13" s="111" t="s">
+      <c r="A13" s="109" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" s="110" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="112">
+      <c r="C13" s="111">
         <f>SUM(F13:BB13)</f>
         <v>2.5</v>
       </c>
-      <c r="D13" s="112">
+      <c r="D13" s="111">
         <f>SUM(F14:BB14)</f>
         <v>2.5</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="112">
         <f>(AVERAGE(C13,C14)-AVERAGE(D13,D14) )</f>
         <v>0</v>
       </c>
@@ -3477,13 +3496,13 @@
       <c r="D14" s="102"/>
       <c r="E14" s="106"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="28">
+      <c r="G14" s="285">
         <v>0.5</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="285">
         <v>1.5</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="285">
         <v>0.5</v>
       </c>
       <c r="J14" s="29"/>
@@ -3533,142 +3552,142 @@
       <c r="BB14" s="29"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="124" t="b">
-        <v>0</v>
-      </c>
-      <c r="B15" s="126" t="s">
+      <c r="A15" s="123" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="128">
+      <c r="C15" s="127">
         <f>SUM(C17:C20)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="128">
+      <c r="D15" s="127">
         <f>SUM(D17:D20)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="130">
+      <c r="E15" s="129">
         <f>(C15-D15)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="114"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="115"/>
-      <c r="P15" s="115"/>
-      <c r="Q15" s="115"/>
-      <c r="R15" s="115"/>
-      <c r="S15" s="115"/>
-      <c r="T15" s="115"/>
-      <c r="U15" s="115"/>
-      <c r="V15" s="115"/>
-      <c r="W15" s="115"/>
-      <c r="X15" s="115"/>
-      <c r="Y15" s="115"/>
-      <c r="Z15" s="115"/>
-      <c r="AA15" s="115"/>
-      <c r="AB15" s="115"/>
-      <c r="AC15" s="115"/>
-      <c r="AD15" s="115"/>
-      <c r="AE15" s="115"/>
-      <c r="AF15" s="115"/>
-      <c r="AG15" s="115"/>
-      <c r="AH15" s="115"/>
-      <c r="AI15" s="115"/>
-      <c r="AJ15" s="115"/>
-      <c r="AK15" s="115"/>
-      <c r="AL15" s="115"/>
-      <c r="AM15" s="115"/>
-      <c r="AN15" s="115"/>
-      <c r="AO15" s="115"/>
-      <c r="AP15" s="115"/>
-      <c r="AQ15" s="115"/>
-      <c r="AR15" s="115"/>
-      <c r="AS15" s="115"/>
-      <c r="AT15" s="115"/>
-      <c r="AU15" s="115"/>
-      <c r="AV15" s="115"/>
-      <c r="AW15" s="115"/>
-      <c r="AX15" s="115"/>
-      <c r="AY15" s="115"/>
-      <c r="AZ15" s="115"/>
-      <c r="BA15" s="115"/>
-      <c r="BB15" s="116"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
+      <c r="V15" s="114"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="114"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="114"/>
+      <c r="AF15" s="114"/>
+      <c r="AG15" s="114"/>
+      <c r="AH15" s="114"/>
+      <c r="AI15" s="114"/>
+      <c r="AJ15" s="114"/>
+      <c r="AK15" s="114"/>
+      <c r="AL15" s="114"/>
+      <c r="AM15" s="114"/>
+      <c r="AN15" s="114"/>
+      <c r="AO15" s="114"/>
+      <c r="AP15" s="114"/>
+      <c r="AQ15" s="114"/>
+      <c r="AR15" s="114"/>
+      <c r="AS15" s="114"/>
+      <c r="AT15" s="114"/>
+      <c r="AU15" s="114"/>
+      <c r="AV15" s="114"/>
+      <c r="AW15" s="114"/>
+      <c r="AX15" s="114"/>
+      <c r="AY15" s="114"/>
+      <c r="AZ15" s="114"/>
+      <c r="BA15" s="114"/>
+      <c r="BB15" s="115"/>
     </row>
     <row r="16" spans="1:54" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="125"/>
-      <c r="B16" s="127"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="118"/>
-      <c r="P16" s="118"/>
-      <c r="Q16" s="118"/>
-      <c r="R16" s="118"/>
-      <c r="S16" s="118"/>
-      <c r="T16" s="118"/>
-      <c r="U16" s="118"/>
-      <c r="V16" s="118"/>
-      <c r="W16" s="118"/>
-      <c r="X16" s="118"/>
-      <c r="Y16" s="118"/>
-      <c r="Z16" s="118"/>
-      <c r="AA16" s="118"/>
-      <c r="AB16" s="118"/>
-      <c r="AC16" s="118"/>
-      <c r="AD16" s="118"/>
-      <c r="AE16" s="118"/>
-      <c r="AF16" s="118"/>
-      <c r="AG16" s="118"/>
-      <c r="AH16" s="118"/>
-      <c r="AI16" s="118"/>
-      <c r="AJ16" s="118"/>
-      <c r="AK16" s="118"/>
-      <c r="AL16" s="118"/>
-      <c r="AM16" s="118"/>
-      <c r="AN16" s="118"/>
-      <c r="AO16" s="118"/>
-      <c r="AP16" s="118"/>
-      <c r="AQ16" s="118"/>
-      <c r="AR16" s="118"/>
-      <c r="AS16" s="118"/>
-      <c r="AT16" s="118"/>
-      <c r="AU16" s="118"/>
-      <c r="AV16" s="118"/>
-      <c r="AW16" s="118"/>
-      <c r="AX16" s="118"/>
-      <c r="AY16" s="118"/>
-      <c r="AZ16" s="118"/>
-      <c r="BA16" s="118"/>
-      <c r="BB16" s="119"/>
+      <c r="A16" s="124"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="128"/>
+      <c r="D16" s="128"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
+      <c r="N16" s="117"/>
+      <c r="O16" s="117"/>
+      <c r="P16" s="117"/>
+      <c r="Q16" s="117"/>
+      <c r="R16" s="117"/>
+      <c r="S16" s="117"/>
+      <c r="T16" s="117"/>
+      <c r="U16" s="117"/>
+      <c r="V16" s="117"/>
+      <c r="W16" s="117"/>
+      <c r="X16" s="117"/>
+      <c r="Y16" s="117"/>
+      <c r="Z16" s="117"/>
+      <c r="AA16" s="117"/>
+      <c r="AB16" s="117"/>
+      <c r="AC16" s="117"/>
+      <c r="AD16" s="117"/>
+      <c r="AE16" s="117"/>
+      <c r="AF16" s="117"/>
+      <c r="AG16" s="117"/>
+      <c r="AH16" s="117"/>
+      <c r="AI16" s="117"/>
+      <c r="AJ16" s="117"/>
+      <c r="AK16" s="117"/>
+      <c r="AL16" s="117"/>
+      <c r="AM16" s="117"/>
+      <c r="AN16" s="117"/>
+      <c r="AO16" s="117"/>
+      <c r="AP16" s="117"/>
+      <c r="AQ16" s="117"/>
+      <c r="AR16" s="117"/>
+      <c r="AS16" s="117"/>
+      <c r="AT16" s="117"/>
+      <c r="AU16" s="117"/>
+      <c r="AV16" s="117"/>
+      <c r="AW16" s="117"/>
+      <c r="AX16" s="117"/>
+      <c r="AY16" s="117"/>
+      <c r="AZ16" s="117"/>
+      <c r="BA16" s="117"/>
+      <c r="BB16" s="118"/>
     </row>
     <row r="17" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="120" t="b">
-        <v>0</v>
-      </c>
-      <c r="B17" s="122" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="112">
+      <c r="A17" s="119" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="111">
         <f>SUM(F17:BB17)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="112">
+      <c r="D17" s="111">
         <f>SUM(F18:BB18)</f>
         <v>0.5</v>
       </c>
@@ -3729,15 +3748,15 @@
       <c r="BB17" s="26"/>
     </row>
     <row r="18" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="121"/>
-      <c r="B18" s="123"/>
+      <c r="A18" s="120"/>
+      <c r="B18" s="122"/>
       <c r="C18" s="102"/>
       <c r="D18" s="102"/>
       <c r="E18" s="106"/>
       <c r="F18" s="27"/>
       <c r="G18" s="28"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="28">
+      <c r="I18" s="285">
         <v>0.5</v>
       </c>
       <c r="J18" s="29"/>
@@ -3787,21 +3806,21 @@
       <c r="BB18" s="29"/>
     </row>
     <row r="19" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="142" t="b">
-        <v>0</v>
-      </c>
-      <c r="B19" s="143" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="112">
+      <c r="A19" s="141" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" s="287" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="111">
         <f>SUM(F19:BB19)</f>
         <v>0.5</v>
       </c>
-      <c r="D19" s="112">
+      <c r="D19" s="111">
         <f>SUM(F20:BB20)</f>
         <v>0.5</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="112">
         <f>(AVERAGE(C19,C20)-AVERAGE(D19,D20) )</f>
         <v>0</v>
       </c>
@@ -3858,15 +3877,15 @@
       <c r="BB19" s="32"/>
     </row>
     <row r="20" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="121"/>
-      <c r="B20" s="144"/>
+      <c r="A20" s="120"/>
+      <c r="B20" s="142"/>
       <c r="C20" s="102"/>
       <c r="D20" s="102"/>
-      <c r="E20" s="145"/>
+      <c r="E20" s="143"/>
       <c r="F20" s="25"/>
       <c r="G20" s="58"/>
       <c r="H20" s="58"/>
-      <c r="I20" s="58">
+      <c r="I20" s="286">
         <v>0.5</v>
       </c>
       <c r="J20" s="26"/>
@@ -3916,155 +3935,155 @@
       <c r="BB20" s="26"/>
     </row>
     <row r="21" spans="1:54" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="146" t="b">
-        <v>0</v>
-      </c>
-      <c r="B21" s="148" t="s">
+      <c r="A21" s="144" t="b">
+        <v>0</v>
+      </c>
+      <c r="B21" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="150">
+      <c r="C21" s="148">
         <f>SUM(C23:C28)</f>
         <v>3</v>
       </c>
-      <c r="D21" s="150">
+      <c r="D21" s="148">
         <f>SUM(D23:D28)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="152">
+        <v>2.5</v>
+      </c>
+      <c r="E21" s="150">
         <f>(C21-D21)</f>
-        <v>3</v>
-      </c>
-      <c r="F21" s="132"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
-      <c r="J21" s="133"/>
-      <c r="K21" s="133"/>
-      <c r="L21" s="133"/>
-      <c r="M21" s="133"/>
-      <c r="N21" s="133"/>
-      <c r="O21" s="133"/>
-      <c r="P21" s="133"/>
-      <c r="Q21" s="133"/>
-      <c r="R21" s="133"/>
-      <c r="S21" s="133"/>
-      <c r="T21" s="133"/>
-      <c r="U21" s="133"/>
-      <c r="V21" s="133"/>
-      <c r="W21" s="133"/>
-      <c r="X21" s="133"/>
-      <c r="Y21" s="133"/>
-      <c r="Z21" s="133"/>
-      <c r="AA21" s="133"/>
-      <c r="AB21" s="133"/>
-      <c r="AC21" s="133"/>
-      <c r="AD21" s="133"/>
-      <c r="AE21" s="133"/>
-      <c r="AF21" s="133"/>
-      <c r="AG21" s="133"/>
-      <c r="AH21" s="133"/>
-      <c r="AI21" s="133"/>
-      <c r="AJ21" s="133"/>
-      <c r="AK21" s="133"/>
-      <c r="AL21" s="133"/>
-      <c r="AM21" s="133"/>
-      <c r="AN21" s="133"/>
-      <c r="AO21" s="133"/>
-      <c r="AP21" s="133"/>
-      <c r="AQ21" s="133"/>
-      <c r="AR21" s="133"/>
-      <c r="AS21" s="133"/>
-      <c r="AT21" s="133"/>
-      <c r="AU21" s="133"/>
-      <c r="AV21" s="133"/>
-      <c r="AW21" s="133"/>
-      <c r="AX21" s="133"/>
-      <c r="AY21" s="133"/>
-      <c r="AZ21" s="133"/>
-      <c r="BA21" s="133"/>
-      <c r="BB21" s="134"/>
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="131"/>
+      <c r="G21" s="132"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="132"/>
+      <c r="J21" s="132"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="132"/>
+      <c r="M21" s="132"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="132"/>
+      <c r="P21" s="132"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="132"/>
+      <c r="S21" s="132"/>
+      <c r="T21" s="132"/>
+      <c r="U21" s="132"/>
+      <c r="V21" s="132"/>
+      <c r="W21" s="132"/>
+      <c r="X21" s="132"/>
+      <c r="Y21" s="132"/>
+      <c r="Z21" s="132"/>
+      <c r="AA21" s="132"/>
+      <c r="AB21" s="132"/>
+      <c r="AC21" s="132"/>
+      <c r="AD21" s="132"/>
+      <c r="AE21" s="132"/>
+      <c r="AF21" s="132"/>
+      <c r="AG21" s="132"/>
+      <c r="AH21" s="132"/>
+      <c r="AI21" s="132"/>
+      <c r="AJ21" s="132"/>
+      <c r="AK21" s="132"/>
+      <c r="AL21" s="132"/>
+      <c r="AM21" s="132"/>
+      <c r="AN21" s="132"/>
+      <c r="AO21" s="132"/>
+      <c r="AP21" s="132"/>
+      <c r="AQ21" s="132"/>
+      <c r="AR21" s="132"/>
+      <c r="AS21" s="132"/>
+      <c r="AT21" s="132"/>
+      <c r="AU21" s="132"/>
+      <c r="AV21" s="132"/>
+      <c r="AW21" s="132"/>
+      <c r="AX21" s="132"/>
+      <c r="AY21" s="132"/>
+      <c r="AZ21" s="132"/>
+      <c r="BA21" s="132"/>
+      <c r="BB21" s="133"/>
     </row>
     <row r="22" spans="1:54" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="147"/>
-      <c r="B22" s="149"/>
-      <c r="C22" s="151"/>
-      <c r="D22" s="151"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="135"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="136"/>
-      <c r="N22" s="136"/>
-      <c r="O22" s="136"/>
-      <c r="P22" s="136"/>
-      <c r="Q22" s="136"/>
-      <c r="R22" s="136"/>
-      <c r="S22" s="136"/>
-      <c r="T22" s="136"/>
-      <c r="U22" s="136"/>
-      <c r="V22" s="136"/>
-      <c r="W22" s="136"/>
-      <c r="X22" s="136"/>
-      <c r="Y22" s="136"/>
-      <c r="Z22" s="136"/>
-      <c r="AA22" s="136"/>
-      <c r="AB22" s="136"/>
-      <c r="AC22" s="136"/>
-      <c r="AD22" s="136"/>
-      <c r="AE22" s="136"/>
-      <c r="AF22" s="136"/>
-      <c r="AG22" s="136"/>
-      <c r="AH22" s="136"/>
-      <c r="AI22" s="136"/>
-      <c r="AJ22" s="136"/>
-      <c r="AK22" s="136"/>
-      <c r="AL22" s="136"/>
-      <c r="AM22" s="136"/>
-      <c r="AN22" s="136"/>
-      <c r="AO22" s="136"/>
-      <c r="AP22" s="136"/>
-      <c r="AQ22" s="136"/>
-      <c r="AR22" s="136"/>
-      <c r="AS22" s="136"/>
-      <c r="AT22" s="136"/>
-      <c r="AU22" s="136"/>
-      <c r="AV22" s="136"/>
-      <c r="AW22" s="136"/>
-      <c r="AX22" s="136"/>
-      <c r="AY22" s="136"/>
-      <c r="AZ22" s="136"/>
-      <c r="BA22" s="136"/>
-      <c r="BB22" s="137"/>
+      <c r="A22" s="145"/>
+      <c r="B22" s="147"/>
+      <c r="C22" s="149"/>
+      <c r="D22" s="149"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="134"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
+      <c r="I22" s="135"/>
+      <c r="J22" s="135"/>
+      <c r="K22" s="135"/>
+      <c r="L22" s="135"/>
+      <c r="M22" s="135"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="135"/>
+      <c r="Q22" s="135"/>
+      <c r="R22" s="135"/>
+      <c r="S22" s="135"/>
+      <c r="T22" s="135"/>
+      <c r="U22" s="135"/>
+      <c r="V22" s="135"/>
+      <c r="W22" s="135"/>
+      <c r="X22" s="135"/>
+      <c r="Y22" s="135"/>
+      <c r="Z22" s="135"/>
+      <c r="AA22" s="135"/>
+      <c r="AB22" s="135"/>
+      <c r="AC22" s="135"/>
+      <c r="AD22" s="135"/>
+      <c r="AE22" s="135"/>
+      <c r="AF22" s="135"/>
+      <c r="AG22" s="135"/>
+      <c r="AH22" s="135"/>
+      <c r="AI22" s="135"/>
+      <c r="AJ22" s="135"/>
+      <c r="AK22" s="135"/>
+      <c r="AL22" s="135"/>
+      <c r="AM22" s="135"/>
+      <c r="AN22" s="135"/>
+      <c r="AO22" s="135"/>
+      <c r="AP22" s="135"/>
+      <c r="AQ22" s="135"/>
+      <c r="AR22" s="135"/>
+      <c r="AS22" s="135"/>
+      <c r="AT22" s="135"/>
+      <c r="AU22" s="135"/>
+      <c r="AV22" s="135"/>
+      <c r="AW22" s="135"/>
+      <c r="AX22" s="135"/>
+      <c r="AY22" s="135"/>
+      <c r="AZ22" s="135"/>
+      <c r="BA22" s="135"/>
+      <c r="BB22" s="136"/>
     </row>
     <row r="23" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="138" t="b">
-        <v>0</v>
-      </c>
-      <c r="B23" s="140" t="s">
+      <c r="A23" s="137" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="112">
+      <c r="C23" s="111">
         <f>SUM(F23:BB23)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="112">
+      <c r="D23" s="111">
         <f>SUM(F24:BB24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="105">
         <f>(AVERAGE(C23,C24)-AVERAGE(D23,D24) )</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="33"/>
       <c r="G23" s="62"/>
       <c r="H23" s="62"/>
       <c r="I23" s="62"/>
       <c r="J23" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K23" s="64">
         <v>1</v>
@@ -4114,8 +4133,8 @@
       <c r="BB23" s="26"/>
     </row>
     <row r="24" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="139"/>
-      <c r="B24" s="141"/>
+      <c r="A24" s="138"/>
+      <c r="B24" s="140"/>
       <c r="C24" s="102"/>
       <c r="D24" s="102"/>
       <c r="E24" s="106"/>
@@ -4124,7 +4143,9 @@
       <c r="H24" s="36"/>
       <c r="I24" s="36"/>
       <c r="J24" s="37"/>
-      <c r="K24" s="27"/>
+      <c r="K24" s="27">
+        <v>1</v>
+      </c>
       <c r="L24" s="28"/>
       <c r="M24" s="28"/>
       <c r="N24" s="28"/>
@@ -4170,23 +4191,23 @@
       <c r="BB24" s="29"/>
     </row>
     <row r="25" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="168" t="b">
-        <v>0</v>
-      </c>
-      <c r="B25" s="169" t="s">
+      <c r="A25" s="166" t="b">
+        <v>0</v>
+      </c>
+      <c r="B25" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="C25" s="112">
+      <c r="C25" s="111">
         <f>SUM(F25:BB25)</f>
         <v>1</v>
       </c>
-      <c r="D25" s="112">
+      <c r="D25" s="111">
         <f>SUM(F26:BB26)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="113">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="112">
         <f>(AVERAGE(C25,C26)-AVERAGE(D25,D26) )</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F25" s="33"/>
       <c r="G25" s="62"/>
@@ -4241,8 +4262,8 @@
       <c r="BB25" s="26"/>
     </row>
     <row r="26" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="139"/>
-      <c r="B26" s="141"/>
+      <c r="A26" s="138"/>
+      <c r="B26" s="140"/>
       <c r="C26" s="102"/>
       <c r="D26" s="102"/>
       <c r="E26" s="106"/>
@@ -4251,8 +4272,12 @@
       <c r="H26" s="36"/>
       <c r="I26" s="36"/>
       <c r="J26" s="37"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="28"/>
+      <c r="K26" s="27">
+        <v>0.3</v>
+      </c>
+      <c r="L26" s="28">
+        <v>0.2</v>
+      </c>
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
       <c r="O26" s="29"/>
@@ -4297,23 +4322,23 @@
       <c r="BB26" s="29"/>
     </row>
     <row r="27" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="168" t="b">
-        <v>0</v>
-      </c>
-      <c r="B27" s="169" t="s">
+      <c r="A27" s="166" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" s="167" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="112">
+      <c r="C27" s="111">
         <f>SUM(F27:BB27)</f>
         <v>1</v>
       </c>
-      <c r="D27" s="112">
+      <c r="D27" s="111">
         <f>SUM(F28:BB28)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="113">
+        <v>1</v>
+      </c>
+      <c r="E27" s="112">
         <f>(AVERAGE(C27,C28)-AVERAGE(D27,D28) )</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="33"/>
       <c r="G27" s="62"/>
@@ -4368,18 +4393,20 @@
       <c r="BB27" s="32"/>
     </row>
     <row r="28" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="139"/>
-      <c r="B28" s="141"/>
+      <c r="A28" s="138"/>
+      <c r="B28" s="140"/>
       <c r="C28" s="102"/>
       <c r="D28" s="102"/>
-      <c r="E28" s="145"/>
+      <c r="E28" s="143"/>
       <c r="F28" s="33"/>
       <c r="G28" s="62"/>
       <c r="H28" s="62"/>
       <c r="I28" s="62"/>
       <c r="J28" s="34"/>
       <c r="K28" s="25"/>
-      <c r="L28" s="58"/>
+      <c r="L28" s="58">
+        <v>1</v>
+      </c>
       <c r="M28" s="58"/>
       <c r="N28" s="58"/>
       <c r="O28" s="26"/>
@@ -4424,142 +4451,142 @@
       <c r="BB28" s="26"/>
     </row>
     <row r="29" spans="1:54" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="154" t="b">
-        <v>0</v>
-      </c>
-      <c r="B29" s="156" t="s">
+      <c r="A29" s="152" t="b">
+        <v>0</v>
+      </c>
+      <c r="B29" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="158">
+      <c r="C29" s="156">
         <f>SUM(C31:C40)</f>
         <v>7.5</v>
       </c>
-      <c r="D29" s="158">
+      <c r="D29" s="156">
         <f>SUM(D31:D40)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="160">
+      <c r="E29" s="158">
         <f>(C29-D29)</f>
         <v>7.5</v>
       </c>
-      <c r="F29" s="162"/>
-      <c r="G29" s="163"/>
-      <c r="H29" s="163"/>
-      <c r="I29" s="163"/>
-      <c r="J29" s="163"/>
-      <c r="K29" s="163"/>
-      <c r="L29" s="163"/>
-      <c r="M29" s="163"/>
-      <c r="N29" s="163"/>
-      <c r="O29" s="163"/>
-      <c r="P29" s="163"/>
-      <c r="Q29" s="163"/>
-      <c r="R29" s="163"/>
-      <c r="S29" s="163"/>
-      <c r="T29" s="163"/>
-      <c r="U29" s="163"/>
-      <c r="V29" s="163"/>
-      <c r="W29" s="163"/>
-      <c r="X29" s="163"/>
-      <c r="Y29" s="163"/>
-      <c r="Z29" s="163"/>
-      <c r="AA29" s="163"/>
-      <c r="AB29" s="163"/>
-      <c r="AC29" s="163"/>
-      <c r="AD29" s="163"/>
-      <c r="AE29" s="163"/>
-      <c r="AF29" s="163"/>
-      <c r="AG29" s="163"/>
-      <c r="AH29" s="163"/>
-      <c r="AI29" s="163"/>
-      <c r="AJ29" s="163"/>
-      <c r="AK29" s="163"/>
-      <c r="AL29" s="163"/>
-      <c r="AM29" s="163"/>
-      <c r="AN29" s="163"/>
-      <c r="AO29" s="163"/>
-      <c r="AP29" s="163"/>
-      <c r="AQ29" s="163"/>
-      <c r="AR29" s="163"/>
-      <c r="AS29" s="163"/>
-      <c r="AT29" s="163"/>
-      <c r="AU29" s="163"/>
-      <c r="AV29" s="163"/>
-      <c r="AW29" s="163"/>
-      <c r="AX29" s="163"/>
-      <c r="AY29" s="163"/>
-      <c r="AZ29" s="163"/>
-      <c r="BA29" s="163"/>
-      <c r="BB29" s="164"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="161"/>
+      <c r="H29" s="161"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="161"/>
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="161"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="161"/>
+      <c r="S29" s="161"/>
+      <c r="T29" s="161"/>
+      <c r="U29" s="161"/>
+      <c r="V29" s="161"/>
+      <c r="W29" s="161"/>
+      <c r="X29" s="161"/>
+      <c r="Y29" s="161"/>
+      <c r="Z29" s="161"/>
+      <c r="AA29" s="161"/>
+      <c r="AB29" s="161"/>
+      <c r="AC29" s="161"/>
+      <c r="AD29" s="161"/>
+      <c r="AE29" s="161"/>
+      <c r="AF29" s="161"/>
+      <c r="AG29" s="161"/>
+      <c r="AH29" s="161"/>
+      <c r="AI29" s="161"/>
+      <c r="AJ29" s="161"/>
+      <c r="AK29" s="161"/>
+      <c r="AL29" s="161"/>
+      <c r="AM29" s="161"/>
+      <c r="AN29" s="161"/>
+      <c r="AO29" s="161"/>
+      <c r="AP29" s="161"/>
+      <c r="AQ29" s="161"/>
+      <c r="AR29" s="161"/>
+      <c r="AS29" s="161"/>
+      <c r="AT29" s="161"/>
+      <c r="AU29" s="161"/>
+      <c r="AV29" s="161"/>
+      <c r="AW29" s="161"/>
+      <c r="AX29" s="161"/>
+      <c r="AY29" s="161"/>
+      <c r="AZ29" s="161"/>
+      <c r="BA29" s="161"/>
+      <c r="BB29" s="162"/>
     </row>
     <row r="30" spans="1:54" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="155"/>
-      <c r="B30" s="157"/>
-      <c r="C30" s="159"/>
-      <c r="D30" s="159"/>
-      <c r="E30" s="161"/>
-      <c r="F30" s="165"/>
-      <c r="G30" s="166"/>
-      <c r="H30" s="166"/>
-      <c r="I30" s="166"/>
-      <c r="J30" s="166"/>
-      <c r="K30" s="166"/>
-      <c r="L30" s="166"/>
-      <c r="M30" s="166"/>
-      <c r="N30" s="166"/>
-      <c r="O30" s="166"/>
-      <c r="P30" s="166"/>
-      <c r="Q30" s="166"/>
-      <c r="R30" s="166"/>
-      <c r="S30" s="166"/>
-      <c r="T30" s="166"/>
-      <c r="U30" s="166"/>
-      <c r="V30" s="166"/>
-      <c r="W30" s="166"/>
-      <c r="X30" s="166"/>
-      <c r="Y30" s="166"/>
-      <c r="Z30" s="166"/>
-      <c r="AA30" s="166"/>
-      <c r="AB30" s="166"/>
-      <c r="AC30" s="166"/>
-      <c r="AD30" s="166"/>
-      <c r="AE30" s="166"/>
-      <c r="AF30" s="166"/>
-      <c r="AG30" s="166"/>
-      <c r="AH30" s="166"/>
-      <c r="AI30" s="166"/>
-      <c r="AJ30" s="166"/>
-      <c r="AK30" s="166"/>
-      <c r="AL30" s="166"/>
-      <c r="AM30" s="166"/>
-      <c r="AN30" s="166"/>
-      <c r="AO30" s="166"/>
-      <c r="AP30" s="166"/>
-      <c r="AQ30" s="166"/>
-      <c r="AR30" s="166"/>
-      <c r="AS30" s="166"/>
-      <c r="AT30" s="166"/>
-      <c r="AU30" s="166"/>
-      <c r="AV30" s="166"/>
-      <c r="AW30" s="166"/>
-      <c r="AX30" s="166"/>
-      <c r="AY30" s="166"/>
-      <c r="AZ30" s="166"/>
-      <c r="BA30" s="166"/>
-      <c r="BB30" s="167"/>
+      <c r="A30" s="153"/>
+      <c r="B30" s="155"/>
+      <c r="C30" s="157"/>
+      <c r="D30" s="157"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="163"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="164"/>
+      <c r="I30" s="164"/>
+      <c r="J30" s="164"/>
+      <c r="K30" s="164"/>
+      <c r="L30" s="164"/>
+      <c r="M30" s="164"/>
+      <c r="N30" s="164"/>
+      <c r="O30" s="164"/>
+      <c r="P30" s="164"/>
+      <c r="Q30" s="164"/>
+      <c r="R30" s="164"/>
+      <c r="S30" s="164"/>
+      <c r="T30" s="164"/>
+      <c r="U30" s="164"/>
+      <c r="V30" s="164"/>
+      <c r="W30" s="164"/>
+      <c r="X30" s="164"/>
+      <c r="Y30" s="164"/>
+      <c r="Z30" s="164"/>
+      <c r="AA30" s="164"/>
+      <c r="AB30" s="164"/>
+      <c r="AC30" s="164"/>
+      <c r="AD30" s="164"/>
+      <c r="AE30" s="164"/>
+      <c r="AF30" s="164"/>
+      <c r="AG30" s="164"/>
+      <c r="AH30" s="164"/>
+      <c r="AI30" s="164"/>
+      <c r="AJ30" s="164"/>
+      <c r="AK30" s="164"/>
+      <c r="AL30" s="164"/>
+      <c r="AM30" s="164"/>
+      <c r="AN30" s="164"/>
+      <c r="AO30" s="164"/>
+      <c r="AP30" s="164"/>
+      <c r="AQ30" s="164"/>
+      <c r="AR30" s="164"/>
+      <c r="AS30" s="164"/>
+      <c r="AT30" s="164"/>
+      <c r="AU30" s="164"/>
+      <c r="AV30" s="164"/>
+      <c r="AW30" s="164"/>
+      <c r="AX30" s="164"/>
+      <c r="AY30" s="164"/>
+      <c r="AZ30" s="164"/>
+      <c r="BA30" s="164"/>
+      <c r="BB30" s="165"/>
     </row>
     <row r="31" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="170" t="b">
-        <v>0</v>
-      </c>
-      <c r="B31" s="172" t="s">
+      <c r="A31" s="168" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="112">
+      <c r="C31" s="111">
         <f>SUM(F31:BB31)</f>
         <v>1.5</v>
       </c>
-      <c r="D31" s="112">
+      <c r="D31" s="111">
         <f>SUM(F32:BB32)</f>
         <v>0</v>
       </c>
@@ -4624,8 +4651,8 @@
       <c r="BB31" s="26"/>
     </row>
     <row r="32" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="171"/>
-      <c r="B32" s="173"/>
+      <c r="A32" s="169"/>
+      <c r="B32" s="171"/>
       <c r="C32" s="102"/>
       <c r="D32" s="102"/>
       <c r="E32" s="106"/>
@@ -4680,21 +4707,21 @@
       <c r="BB32" s="29"/>
     </row>
     <row r="33" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="174" t="b">
-        <v>0</v>
-      </c>
-      <c r="B33" s="175" t="s">
+      <c r="A33" s="172" t="b">
+        <v>0</v>
+      </c>
+      <c r="B33" s="173" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="112">
+      <c r="C33" s="111">
         <f>SUM(F33:BB33)</f>
         <v>1</v>
       </c>
-      <c r="D33" s="112">
+      <c r="D33" s="111">
         <f>SUM(F34:BB34)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="113">
+      <c r="E33" s="112">
         <f>(AVERAGE(C33,C34)-AVERAGE(D33,D34) )</f>
         <v>1</v>
       </c>
@@ -4751,8 +4778,8 @@
       <c r="BB33" s="32"/>
     </row>
     <row r="34" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="171"/>
-      <c r="B34" s="173"/>
+      <c r="A34" s="169"/>
+      <c r="B34" s="171"/>
       <c r="C34" s="102"/>
       <c r="D34" s="102"/>
       <c r="E34" s="106"/>
@@ -4807,21 +4834,21 @@
       <c r="BB34" s="29"/>
     </row>
     <row r="35" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="174" t="b">
-        <v>0</v>
-      </c>
-      <c r="B35" s="175" t="s">
+      <c r="A35" s="172" t="b">
+        <v>0</v>
+      </c>
+      <c r="B35" s="173" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="112">
+      <c r="C35" s="111">
         <f>SUM(F35:BB35)</f>
         <v>2</v>
       </c>
-      <c r="D35" s="112">
+      <c r="D35" s="111">
         <f>SUM(F36:BB36)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="113">
+      <c r="E35" s="112">
         <f t="shared" ref="E35" si="0">(AVERAGE(C35,C36)-AVERAGE(D35,D36) )</f>
         <v>2</v>
       </c>
@@ -4878,8 +4905,8 @@
       <c r="BB35" s="32"/>
     </row>
     <row r="36" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="171"/>
-      <c r="B36" s="173"/>
+      <c r="A36" s="169"/>
+      <c r="B36" s="171"/>
       <c r="C36" s="102"/>
       <c r="D36" s="102"/>
       <c r="E36" s="106"/>
@@ -4934,21 +4961,21 @@
       <c r="BB36" s="29"/>
     </row>
     <row r="37" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="174" t="b">
-        <v>0</v>
-      </c>
-      <c r="B37" s="175" t="s">
+      <c r="A37" s="172" t="b">
+        <v>0</v>
+      </c>
+      <c r="B37" s="173" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="112">
+      <c r="C37" s="111">
         <f>SUM(F37:BB37)</f>
         <v>0.5</v>
       </c>
-      <c r="D37" s="112">
+      <c r="D37" s="111">
         <f>SUM(F38:BB38)</f>
         <v>0</v>
       </c>
-      <c r="E37" s="113">
+      <c r="E37" s="112">
         <f t="shared" ref="E37" si="1">(AVERAGE(C37,C38)-AVERAGE(D37,D38) )</f>
         <v>0.5</v>
       </c>
@@ -5005,8 +5032,8 @@
       <c r="BB37" s="32"/>
     </row>
     <row r="38" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="171"/>
-      <c r="B38" s="173"/>
+      <c r="A38" s="169"/>
+      <c r="B38" s="171"/>
       <c r="C38" s="102"/>
       <c r="D38" s="102"/>
       <c r="E38" s="106"/>
@@ -5061,21 +5088,21 @@
       <c r="BB38" s="29"/>
     </row>
     <row r="39" spans="1:54" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="174" t="b">
-        <v>0</v>
-      </c>
-      <c r="B39" s="175" t="s">
+      <c r="A39" s="172" t="b">
+        <v>0</v>
+      </c>
+      <c r="B39" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="112">
+      <c r="C39" s="111">
         <f>SUM(F39:BB39)</f>
         <v>2.5</v>
       </c>
-      <c r="D39" s="112">
+      <c r="D39" s="111">
         <f>SUM(F40:BB40)</f>
         <v>0</v>
       </c>
-      <c r="E39" s="113">
+      <c r="E39" s="112">
         <f t="shared" ref="E39" si="2">(AVERAGE(C39,C40)-AVERAGE(D39,D40) )</f>
         <v>2.5</v>
       </c>
@@ -5134,8 +5161,8 @@
       <c r="BB39" s="32"/>
     </row>
     <row r="40" spans="1:54" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="171"/>
-      <c r="B40" s="173"/>
+      <c r="A40" s="169"/>
+      <c r="B40" s="171"/>
       <c r="C40" s="102"/>
       <c r="D40" s="102"/>
       <c r="E40" s="106"/>
@@ -5190,142 +5217,142 @@
       <c r="BB40" s="29"/>
     </row>
     <row r="41" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="176" t="b">
-        <v>0</v>
-      </c>
-      <c r="B41" s="178" t="s">
+      <c r="A41" s="174" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" s="176" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="180">
+      <c r="C41" s="178">
         <f>SUM(C43:C48)</f>
         <v>4.5</v>
       </c>
-      <c r="D41" s="180">
+      <c r="D41" s="178">
         <f>SUM(D43:D48)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="180">
+      <c r="E41" s="178">
         <f>(C41-D41)</f>
         <v>4.5</v>
       </c>
-      <c r="F41" s="183"/>
-      <c r="G41" s="184"/>
-      <c r="H41" s="184"/>
-      <c r="I41" s="184"/>
-      <c r="J41" s="184"/>
-      <c r="K41" s="184"/>
-      <c r="L41" s="184"/>
-      <c r="M41" s="184"/>
-      <c r="N41" s="184"/>
-      <c r="O41" s="184"/>
-      <c r="P41" s="184"/>
-      <c r="Q41" s="184"/>
-      <c r="R41" s="184"/>
-      <c r="S41" s="184"/>
-      <c r="T41" s="184"/>
-      <c r="U41" s="184"/>
-      <c r="V41" s="184"/>
-      <c r="W41" s="184"/>
-      <c r="X41" s="184"/>
-      <c r="Y41" s="184"/>
-      <c r="Z41" s="184"/>
-      <c r="AA41" s="184"/>
-      <c r="AB41" s="184"/>
-      <c r="AC41" s="184"/>
-      <c r="AD41" s="184"/>
-      <c r="AE41" s="184"/>
-      <c r="AF41" s="184"/>
-      <c r="AG41" s="184"/>
-      <c r="AH41" s="184"/>
-      <c r="AI41" s="184"/>
-      <c r="AJ41" s="184"/>
-      <c r="AK41" s="184"/>
-      <c r="AL41" s="184"/>
-      <c r="AM41" s="184"/>
-      <c r="AN41" s="184"/>
-      <c r="AO41" s="184"/>
-      <c r="AP41" s="184"/>
-      <c r="AQ41" s="184"/>
-      <c r="AR41" s="184"/>
-      <c r="AS41" s="184"/>
-      <c r="AT41" s="184"/>
-      <c r="AU41" s="184"/>
-      <c r="AV41" s="184"/>
-      <c r="AW41" s="184"/>
-      <c r="AX41" s="184"/>
-      <c r="AY41" s="184"/>
-      <c r="AZ41" s="184"/>
-      <c r="BA41" s="184"/>
-      <c r="BB41" s="185"/>
+      <c r="F41" s="181"/>
+      <c r="G41" s="182"/>
+      <c r="H41" s="182"/>
+      <c r="I41" s="182"/>
+      <c r="J41" s="182"/>
+      <c r="K41" s="182"/>
+      <c r="L41" s="182"/>
+      <c r="M41" s="182"/>
+      <c r="N41" s="182"/>
+      <c r="O41" s="182"/>
+      <c r="P41" s="182"/>
+      <c r="Q41" s="182"/>
+      <c r="R41" s="182"/>
+      <c r="S41" s="182"/>
+      <c r="T41" s="182"/>
+      <c r="U41" s="182"/>
+      <c r="V41" s="182"/>
+      <c r="W41" s="182"/>
+      <c r="X41" s="182"/>
+      <c r="Y41" s="182"/>
+      <c r="Z41" s="182"/>
+      <c r="AA41" s="182"/>
+      <c r="AB41" s="182"/>
+      <c r="AC41" s="182"/>
+      <c r="AD41" s="182"/>
+      <c r="AE41" s="182"/>
+      <c r="AF41" s="182"/>
+      <c r="AG41" s="182"/>
+      <c r="AH41" s="182"/>
+      <c r="AI41" s="182"/>
+      <c r="AJ41" s="182"/>
+      <c r="AK41" s="182"/>
+      <c r="AL41" s="182"/>
+      <c r="AM41" s="182"/>
+      <c r="AN41" s="182"/>
+      <c r="AO41" s="182"/>
+      <c r="AP41" s="182"/>
+      <c r="AQ41" s="182"/>
+      <c r="AR41" s="182"/>
+      <c r="AS41" s="182"/>
+      <c r="AT41" s="182"/>
+      <c r="AU41" s="182"/>
+      <c r="AV41" s="182"/>
+      <c r="AW41" s="182"/>
+      <c r="AX41" s="182"/>
+      <c r="AY41" s="182"/>
+      <c r="AZ41" s="182"/>
+      <c r="BA41" s="182"/>
+      <c r="BB41" s="183"/>
     </row>
     <row r="42" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="177"/>
-      <c r="B42" s="179"/>
-      <c r="C42" s="181"/>
-      <c r="D42" s="181"/>
-      <c r="E42" s="182"/>
-      <c r="F42" s="186"/>
-      <c r="G42" s="187"/>
-      <c r="H42" s="187"/>
-      <c r="I42" s="187"/>
-      <c r="J42" s="187"/>
-      <c r="K42" s="187"/>
-      <c r="L42" s="187"/>
-      <c r="M42" s="187"/>
-      <c r="N42" s="187"/>
-      <c r="O42" s="187"/>
-      <c r="P42" s="187"/>
-      <c r="Q42" s="187"/>
-      <c r="R42" s="187"/>
-      <c r="S42" s="187"/>
-      <c r="T42" s="187"/>
-      <c r="U42" s="187"/>
-      <c r="V42" s="187"/>
-      <c r="W42" s="187"/>
-      <c r="X42" s="187"/>
-      <c r="Y42" s="187"/>
-      <c r="Z42" s="187"/>
-      <c r="AA42" s="187"/>
-      <c r="AB42" s="187"/>
-      <c r="AC42" s="187"/>
-      <c r="AD42" s="187"/>
-      <c r="AE42" s="187"/>
-      <c r="AF42" s="187"/>
-      <c r="AG42" s="187"/>
-      <c r="AH42" s="187"/>
-      <c r="AI42" s="187"/>
-      <c r="AJ42" s="187"/>
-      <c r="AK42" s="187"/>
-      <c r="AL42" s="187"/>
-      <c r="AM42" s="187"/>
-      <c r="AN42" s="187"/>
-      <c r="AO42" s="187"/>
-      <c r="AP42" s="187"/>
-      <c r="AQ42" s="187"/>
-      <c r="AR42" s="187"/>
-      <c r="AS42" s="187"/>
-      <c r="AT42" s="187"/>
-      <c r="AU42" s="187"/>
-      <c r="AV42" s="187"/>
-      <c r="AW42" s="187"/>
-      <c r="AX42" s="187"/>
-      <c r="AY42" s="187"/>
-      <c r="AZ42" s="187"/>
-      <c r="BA42" s="187"/>
-      <c r="BB42" s="188"/>
+      <c r="A42" s="175"/>
+      <c r="B42" s="177"/>
+      <c r="C42" s="179"/>
+      <c r="D42" s="179"/>
+      <c r="E42" s="180"/>
+      <c r="F42" s="184"/>
+      <c r="G42" s="185"/>
+      <c r="H42" s="185"/>
+      <c r="I42" s="185"/>
+      <c r="J42" s="185"/>
+      <c r="K42" s="185"/>
+      <c r="L42" s="185"/>
+      <c r="M42" s="185"/>
+      <c r="N42" s="185"/>
+      <c r="O42" s="185"/>
+      <c r="P42" s="185"/>
+      <c r="Q42" s="185"/>
+      <c r="R42" s="185"/>
+      <c r="S42" s="185"/>
+      <c r="T42" s="185"/>
+      <c r="U42" s="185"/>
+      <c r="V42" s="185"/>
+      <c r="W42" s="185"/>
+      <c r="X42" s="185"/>
+      <c r="Y42" s="185"/>
+      <c r="Z42" s="185"/>
+      <c r="AA42" s="185"/>
+      <c r="AB42" s="185"/>
+      <c r="AC42" s="185"/>
+      <c r="AD42" s="185"/>
+      <c r="AE42" s="185"/>
+      <c r="AF42" s="185"/>
+      <c r="AG42" s="185"/>
+      <c r="AH42" s="185"/>
+      <c r="AI42" s="185"/>
+      <c r="AJ42" s="185"/>
+      <c r="AK42" s="185"/>
+      <c r="AL42" s="185"/>
+      <c r="AM42" s="185"/>
+      <c r="AN42" s="185"/>
+      <c r="AO42" s="185"/>
+      <c r="AP42" s="185"/>
+      <c r="AQ42" s="185"/>
+      <c r="AR42" s="185"/>
+      <c r="AS42" s="185"/>
+      <c r="AT42" s="185"/>
+      <c r="AU42" s="185"/>
+      <c r="AV42" s="185"/>
+      <c r="AW42" s="185"/>
+      <c r="AX42" s="185"/>
+      <c r="AY42" s="185"/>
+      <c r="AZ42" s="185"/>
+      <c r="BA42" s="185"/>
+      <c r="BB42" s="186"/>
     </row>
     <row r="43" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="202" t="b">
-        <v>0</v>
-      </c>
-      <c r="B43" s="204" t="s">
+      <c r="A43" s="200" t="b">
+        <v>0</v>
+      </c>
+      <c r="B43" s="202" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="112">
+      <c r="C43" s="111">
         <f>SUM(F43:BB43)</f>
         <v>1</v>
       </c>
-      <c r="D43" s="112">
+      <c r="D43" s="111">
         <f>SUM(F44:BB44)</f>
         <v>0</v>
       </c>
@@ -5386,8 +5413,8 @@
       <c r="BB43" s="40"/>
     </row>
     <row r="44" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="203"/>
-      <c r="B44" s="205"/>
+      <c r="A44" s="201"/>
+      <c r="B44" s="203"/>
       <c r="C44" s="102"/>
       <c r="D44" s="102"/>
       <c r="E44" s="106"/>
@@ -5442,21 +5469,21 @@
       <c r="BB44" s="29"/>
     </row>
     <row r="45" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="206" t="b">
-        <v>0</v>
-      </c>
-      <c r="B45" s="207" t="s">
+      <c r="A45" s="204" t="b">
+        <v>0</v>
+      </c>
+      <c r="B45" s="205" t="s">
         <v>44</v>
       </c>
-      <c r="C45" s="112">
+      <c r="C45" s="111">
         <f>SUM(F45:BB45)</f>
         <v>1</v>
       </c>
-      <c r="D45" s="112">
+      <c r="D45" s="111">
         <f>SUM(F46:BB46)</f>
         <v>0</v>
       </c>
-      <c r="E45" s="113">
+      <c r="E45" s="112">
         <f>(AVERAGE(C45,C46)-AVERAGE(D45,D46) )</f>
         <v>1</v>
       </c>
@@ -5513,11 +5540,11 @@
       <c r="BB45" s="32"/>
     </row>
     <row r="46" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="203"/>
-      <c r="B46" s="205"/>
+      <c r="A46" s="201"/>
+      <c r="B46" s="203"/>
       <c r="C46" s="102"/>
       <c r="D46" s="102"/>
-      <c r="E46" s="145"/>
+      <c r="E46" s="143"/>
       <c r="F46" s="27"/>
       <c r="G46" s="28"/>
       <c r="H46" s="28"/>
@@ -5569,21 +5596,21 @@
       <c r="BB46" s="29"/>
     </row>
     <row r="47" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="206" t="b">
-        <v>0</v>
-      </c>
-      <c r="B47" s="207" t="s">
+      <c r="A47" s="204" t="b">
+        <v>0</v>
+      </c>
+      <c r="B47" s="205" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="112">
+      <c r="C47" s="111">
         <f>SUM(F47:BB47)</f>
         <v>2.5</v>
       </c>
-      <c r="D47" s="112">
+      <c r="D47" s="111">
         <f>SUM(F48:BB48)</f>
         <v>0</v>
       </c>
-      <c r="E47" s="113">
+      <c r="E47" s="112">
         <f>(AVERAGE(C47,C48)-AVERAGE(D47,D48) )</f>
         <v>2.5</v>
       </c>
@@ -5642,11 +5669,11 @@
       <c r="BB47" s="32"/>
     </row>
     <row r="48" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A48" s="203"/>
-      <c r="B48" s="205"/>
+      <c r="A48" s="201"/>
+      <c r="B48" s="203"/>
       <c r="C48" s="102"/>
       <c r="D48" s="102"/>
-      <c r="E48" s="145"/>
+      <c r="E48" s="143"/>
       <c r="F48" s="27"/>
       <c r="G48" s="28"/>
       <c r="H48" s="28"/>
@@ -5698,142 +5725,142 @@
       <c r="BB48" s="29"/>
     </row>
     <row r="49" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="189" t="b">
-        <v>0</v>
-      </c>
-      <c r="B49" s="191" t="s">
+      <c r="A49" s="187" t="b">
+        <v>0</v>
+      </c>
+      <c r="B49" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="193">
+      <c r="C49" s="191">
         <f>SUM(C51:C66)</f>
         <v>23</v>
       </c>
-      <c r="D49" s="193">
+      <c r="D49" s="191">
         <f>SUM(D51:D66)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="193">
+      <c r="E49" s="191">
         <f>(C49-D49)</f>
         <v>23</v>
       </c>
-      <c r="F49" s="196"/>
-      <c r="G49" s="197"/>
-      <c r="H49" s="197"/>
-      <c r="I49" s="197"/>
-      <c r="J49" s="197"/>
-      <c r="K49" s="197"/>
-      <c r="L49" s="197"/>
-      <c r="M49" s="197"/>
-      <c r="N49" s="197"/>
-      <c r="O49" s="197"/>
-      <c r="P49" s="197"/>
-      <c r="Q49" s="197"/>
-      <c r="R49" s="197"/>
-      <c r="S49" s="197"/>
-      <c r="T49" s="197"/>
-      <c r="U49" s="197"/>
-      <c r="V49" s="197"/>
-      <c r="W49" s="197"/>
-      <c r="X49" s="197"/>
-      <c r="Y49" s="197"/>
-      <c r="Z49" s="197"/>
-      <c r="AA49" s="197"/>
-      <c r="AB49" s="197"/>
-      <c r="AC49" s="197"/>
-      <c r="AD49" s="197"/>
-      <c r="AE49" s="197"/>
-      <c r="AF49" s="197"/>
-      <c r="AG49" s="197"/>
-      <c r="AH49" s="197"/>
-      <c r="AI49" s="197"/>
-      <c r="AJ49" s="197"/>
-      <c r="AK49" s="197"/>
-      <c r="AL49" s="197"/>
-      <c r="AM49" s="197"/>
-      <c r="AN49" s="197"/>
-      <c r="AO49" s="197"/>
-      <c r="AP49" s="197"/>
-      <c r="AQ49" s="197"/>
-      <c r="AR49" s="197"/>
-      <c r="AS49" s="197"/>
-      <c r="AT49" s="197"/>
-      <c r="AU49" s="197"/>
-      <c r="AV49" s="197"/>
-      <c r="AW49" s="197"/>
-      <c r="AX49" s="197"/>
-      <c r="AY49" s="197"/>
-      <c r="AZ49" s="197"/>
-      <c r="BA49" s="197"/>
-      <c r="BB49" s="198"/>
+      <c r="F49" s="194"/>
+      <c r="G49" s="195"/>
+      <c r="H49" s="195"/>
+      <c r="I49" s="195"/>
+      <c r="J49" s="195"/>
+      <c r="K49" s="195"/>
+      <c r="L49" s="195"/>
+      <c r="M49" s="195"/>
+      <c r="N49" s="195"/>
+      <c r="O49" s="195"/>
+      <c r="P49" s="195"/>
+      <c r="Q49" s="195"/>
+      <c r="R49" s="195"/>
+      <c r="S49" s="195"/>
+      <c r="T49" s="195"/>
+      <c r="U49" s="195"/>
+      <c r="V49" s="195"/>
+      <c r="W49" s="195"/>
+      <c r="X49" s="195"/>
+      <c r="Y49" s="195"/>
+      <c r="Z49" s="195"/>
+      <c r="AA49" s="195"/>
+      <c r="AB49" s="195"/>
+      <c r="AC49" s="195"/>
+      <c r="AD49" s="195"/>
+      <c r="AE49" s="195"/>
+      <c r="AF49" s="195"/>
+      <c r="AG49" s="195"/>
+      <c r="AH49" s="195"/>
+      <c r="AI49" s="195"/>
+      <c r="AJ49" s="195"/>
+      <c r="AK49" s="195"/>
+      <c r="AL49" s="195"/>
+      <c r="AM49" s="195"/>
+      <c r="AN49" s="195"/>
+      <c r="AO49" s="195"/>
+      <c r="AP49" s="195"/>
+      <c r="AQ49" s="195"/>
+      <c r="AR49" s="195"/>
+      <c r="AS49" s="195"/>
+      <c r="AT49" s="195"/>
+      <c r="AU49" s="195"/>
+      <c r="AV49" s="195"/>
+      <c r="AW49" s="195"/>
+      <c r="AX49" s="195"/>
+      <c r="AY49" s="195"/>
+      <c r="AZ49" s="195"/>
+      <c r="BA49" s="195"/>
+      <c r="BB49" s="196"/>
     </row>
     <row r="50" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A50" s="190"/>
-      <c r="B50" s="192"/>
-      <c r="C50" s="194"/>
-      <c r="D50" s="194"/>
-      <c r="E50" s="195"/>
-      <c r="F50" s="199"/>
-      <c r="G50" s="200"/>
-      <c r="H50" s="200"/>
-      <c r="I50" s="200"/>
-      <c r="J50" s="200"/>
-      <c r="K50" s="200"/>
-      <c r="L50" s="200"/>
-      <c r="M50" s="200"/>
-      <c r="N50" s="200"/>
-      <c r="O50" s="200"/>
-      <c r="P50" s="200"/>
-      <c r="Q50" s="200"/>
-      <c r="R50" s="200"/>
-      <c r="S50" s="200"/>
-      <c r="T50" s="200"/>
-      <c r="U50" s="200"/>
-      <c r="V50" s="200"/>
-      <c r="W50" s="200"/>
-      <c r="X50" s="200"/>
-      <c r="Y50" s="200"/>
-      <c r="Z50" s="200"/>
-      <c r="AA50" s="200"/>
-      <c r="AB50" s="200"/>
-      <c r="AC50" s="200"/>
-      <c r="AD50" s="200"/>
-      <c r="AE50" s="200"/>
-      <c r="AF50" s="200"/>
-      <c r="AG50" s="200"/>
-      <c r="AH50" s="200"/>
-      <c r="AI50" s="200"/>
-      <c r="AJ50" s="200"/>
-      <c r="AK50" s="200"/>
-      <c r="AL50" s="200"/>
-      <c r="AM50" s="200"/>
-      <c r="AN50" s="200"/>
-      <c r="AO50" s="200"/>
-      <c r="AP50" s="200"/>
-      <c r="AQ50" s="200"/>
-      <c r="AR50" s="200"/>
-      <c r="AS50" s="200"/>
-      <c r="AT50" s="200"/>
-      <c r="AU50" s="200"/>
-      <c r="AV50" s="200"/>
-      <c r="AW50" s="200"/>
-      <c r="AX50" s="200"/>
-      <c r="AY50" s="200"/>
-      <c r="AZ50" s="200"/>
-      <c r="BA50" s="200"/>
-      <c r="BB50" s="201"/>
+      <c r="A50" s="188"/>
+      <c r="B50" s="190"/>
+      <c r="C50" s="192"/>
+      <c r="D50" s="192"/>
+      <c r="E50" s="193"/>
+      <c r="F50" s="197"/>
+      <c r="G50" s="198"/>
+      <c r="H50" s="198"/>
+      <c r="I50" s="198"/>
+      <c r="J50" s="198"/>
+      <c r="K50" s="198"/>
+      <c r="L50" s="198"/>
+      <c r="M50" s="198"/>
+      <c r="N50" s="198"/>
+      <c r="O50" s="198"/>
+      <c r="P50" s="198"/>
+      <c r="Q50" s="198"/>
+      <c r="R50" s="198"/>
+      <c r="S50" s="198"/>
+      <c r="T50" s="198"/>
+      <c r="U50" s="198"/>
+      <c r="V50" s="198"/>
+      <c r="W50" s="198"/>
+      <c r="X50" s="198"/>
+      <c r="Y50" s="198"/>
+      <c r="Z50" s="198"/>
+      <c r="AA50" s="198"/>
+      <c r="AB50" s="198"/>
+      <c r="AC50" s="198"/>
+      <c r="AD50" s="198"/>
+      <c r="AE50" s="198"/>
+      <c r="AF50" s="198"/>
+      <c r="AG50" s="198"/>
+      <c r="AH50" s="198"/>
+      <c r="AI50" s="198"/>
+      <c r="AJ50" s="198"/>
+      <c r="AK50" s="198"/>
+      <c r="AL50" s="198"/>
+      <c r="AM50" s="198"/>
+      <c r="AN50" s="198"/>
+      <c r="AO50" s="198"/>
+      <c r="AP50" s="198"/>
+      <c r="AQ50" s="198"/>
+      <c r="AR50" s="198"/>
+      <c r="AS50" s="198"/>
+      <c r="AT50" s="198"/>
+      <c r="AU50" s="198"/>
+      <c r="AV50" s="198"/>
+      <c r="AW50" s="198"/>
+      <c r="AX50" s="198"/>
+      <c r="AY50" s="198"/>
+      <c r="AZ50" s="198"/>
+      <c r="BA50" s="198"/>
+      <c r="BB50" s="199"/>
     </row>
     <row r="51" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="208" t="b">
-        <v>0</v>
-      </c>
-      <c r="B51" s="210" t="s">
-        <v>56</v>
-      </c>
-      <c r="C51" s="112">
+      <c r="A51" s="206" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" s="208" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="111">
         <f>SUM(F51:BB51)</f>
         <v>3</v>
       </c>
-      <c r="D51" s="112">
+      <c r="D51" s="111">
         <f>SUM(F52:BB52)</f>
         <v>0</v>
       </c>
@@ -5898,8 +5925,8 @@
       <c r="BB51" s="40"/>
     </row>
     <row r="52" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="209"/>
-      <c r="B52" s="211"/>
+      <c r="A52" s="207"/>
+      <c r="B52" s="209"/>
       <c r="C52" s="102"/>
       <c r="D52" s="102"/>
       <c r="E52" s="106"/>
@@ -5954,21 +5981,21 @@
       <c r="BB52" s="29"/>
     </row>
     <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B53" s="210" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="112">
+      <c r="A53" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B53" s="208" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="111">
         <f>SUM(F53:BB53)</f>
         <v>1.5</v>
       </c>
-      <c r="D53" s="112">
+      <c r="D53" s="111">
         <f>SUM(F54:BB54)</f>
         <v>0</v>
       </c>
-      <c r="E53" s="113">
+      <c r="E53" s="112">
         <f t="shared" ref="E53:E65" si="3">(AVERAGE(C53,C54)-AVERAGE(D53,D54) )</f>
         <v>1.5</v>
       </c>
@@ -6025,8 +6052,8 @@
       <c r="BB53" s="32"/>
     </row>
     <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="209"/>
-      <c r="B54" s="211"/>
+      <c r="A54" s="207"/>
+      <c r="B54" s="209"/>
       <c r="C54" s="102"/>
       <c r="D54" s="102"/>
       <c r="E54" s="106"/>
@@ -6081,21 +6108,21 @@
       <c r="BB54" s="29"/>
     </row>
     <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B55" s="210" t="s">
-        <v>59</v>
-      </c>
-      <c r="C55" s="112">
+      <c r="A55" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B55" s="208" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="111">
         <f>SUM(F55:BB55)</f>
         <v>1.5</v>
       </c>
-      <c r="D55" s="112">
+      <c r="D55" s="111">
         <f>SUM(F56:BB56)</f>
         <v>0</v>
       </c>
-      <c r="E55" s="113">
+      <c r="E55" s="112">
         <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
@@ -6152,8 +6179,8 @@
       <c r="BB55" s="32"/>
     </row>
     <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="209"/>
-      <c r="B56" s="211"/>
+      <c r="A56" s="207"/>
+      <c r="B56" s="209"/>
       <c r="C56" s="102"/>
       <c r="D56" s="102"/>
       <c r="E56" s="106"/>
@@ -6208,21 +6235,21 @@
       <c r="BB56" s="29"/>
     </row>
     <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B57" s="210" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" s="112">
+      <c r="A57" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B57" s="208" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="111">
         <f>SUM(F57:BB57)</f>
         <v>5.5</v>
       </c>
-      <c r="D57" s="112">
+      <c r="D57" s="111">
         <f>SUM(F58:BB58)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="113">
+      <c r="E57" s="112">
         <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
@@ -6289,8 +6316,8 @@
       <c r="BB57" s="32"/>
     </row>
     <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="209"/>
-      <c r="B58" s="211"/>
+      <c r="A58" s="207"/>
+      <c r="B58" s="209"/>
       <c r="C58" s="102"/>
       <c r="D58" s="102"/>
       <c r="E58" s="106"/>
@@ -6345,21 +6372,21 @@
       <c r="BB58" s="29"/>
     </row>
     <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B59" s="210" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" s="112">
+      <c r="A59" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B59" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="111">
         <f>SUM(F59:BB59)</f>
         <v>4</v>
       </c>
-      <c r="D59" s="112">
+      <c r="D59" s="111">
         <f>SUM(F60:BB60)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="113">
+      <c r="E59" s="112">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -6422,8 +6449,8 @@
       <c r="BB59" s="32"/>
     </row>
     <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="209"/>
-      <c r="B60" s="211"/>
+      <c r="A60" s="207"/>
+      <c r="B60" s="209"/>
       <c r="C60" s="102"/>
       <c r="D60" s="102"/>
       <c r="E60" s="106"/>
@@ -6478,21 +6505,21 @@
       <c r="BB60" s="29"/>
     </row>
     <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B61" s="210" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="112">
+      <c r="A61" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B61" s="208" t="s">
+        <v>60</v>
+      </c>
+      <c r="C61" s="111">
         <f>SUM(F61:BB61)</f>
         <v>1.5</v>
       </c>
-      <c r="D61" s="112">
+      <c r="D61" s="111">
         <f>SUM(F62:BB62)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="113">
+      <c r="E61" s="112">
         <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
@@ -6549,8 +6576,8 @@
       <c r="BB61" s="32"/>
     </row>
     <row r="62" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="209"/>
-      <c r="B62" s="211"/>
+      <c r="A62" s="207"/>
+      <c r="B62" s="209"/>
       <c r="C62" s="102"/>
       <c r="D62" s="102"/>
       <c r="E62" s="106"/>
@@ -6605,21 +6632,21 @@
       <c r="BB62" s="29"/>
     </row>
     <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B63" s="213" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" s="112">
+      <c r="A63" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B63" s="211" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" s="111">
         <f>SUM(F63:BB63)</f>
         <v>1.5</v>
       </c>
-      <c r="D63" s="112">
+      <c r="D63" s="111">
         <f>SUM(F64:BB64)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="113">
+      <c r="E63" s="112">
         <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
@@ -6676,8 +6703,8 @@
       <c r="BB63" s="32"/>
     </row>
     <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="209"/>
-      <c r="B64" s="214"/>
+      <c r="A64" s="207"/>
+      <c r="B64" s="212"/>
       <c r="C64" s="102"/>
       <c r="D64" s="102"/>
       <c r="E64" s="106"/>
@@ -6732,21 +6759,21 @@
       <c r="BB64" s="29"/>
     </row>
     <row r="65" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="212" t="b">
-        <v>0</v>
-      </c>
-      <c r="B65" s="215" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="112">
+      <c r="A65" s="210" t="b">
+        <v>0</v>
+      </c>
+      <c r="B65" s="213" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="111">
         <f>SUM(F65:BB65)</f>
         <v>4.5</v>
       </c>
-      <c r="D65" s="112">
+      <c r="D65" s="111">
         <f>SUM(F66:BB66)</f>
         <v>0</v>
       </c>
-      <c r="E65" s="113">
+      <c r="E65" s="112">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
@@ -6764,7 +6791,7 @@
       <c r="Q65" s="58"/>
       <c r="R65" s="58"/>
       <c r="S65" s="58"/>
-      <c r="T65" s="278"/>
+      <c r="T65" s="276"/>
       <c r="U65" s="30"/>
       <c r="V65" s="31"/>
       <c r="W65" s="31"/>
@@ -6807,8 +6834,8 @@
       <c r="BB65" s="32"/>
     </row>
     <row r="66" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A66" s="209"/>
-      <c r="B66" s="211"/>
+      <c r="A66" s="207"/>
+      <c r="B66" s="209"/>
       <c r="C66" s="102"/>
       <c r="D66" s="102"/>
       <c r="E66" s="106"/>
@@ -6863,142 +6890,142 @@
       <c r="BB66" s="29"/>
     </row>
     <row r="67" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="226" t="b">
-        <v>0</v>
-      </c>
-      <c r="B67" s="228" t="s">
+      <c r="A67" s="224" t="b">
+        <v>0</v>
+      </c>
+      <c r="B67" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="230">
+      <c r="C67" s="228">
         <f>SUM(C69:C74)</f>
         <v>3.5</v>
       </c>
-      <c r="D67" s="230">
+      <c r="D67" s="228">
         <f>SUM(D69:D74)</f>
         <v>0</v>
       </c>
-      <c r="E67" s="230">
+      <c r="E67" s="228">
         <f>(C67-D67)</f>
         <v>3.5</v>
       </c>
-      <c r="F67" s="216"/>
-      <c r="G67" s="217"/>
-      <c r="H67" s="217"/>
-      <c r="I67" s="217"/>
-      <c r="J67" s="217"/>
-      <c r="K67" s="217"/>
-      <c r="L67" s="217"/>
-      <c r="M67" s="217"/>
-      <c r="N67" s="217"/>
-      <c r="O67" s="217"/>
-      <c r="P67" s="217"/>
-      <c r="Q67" s="217"/>
-      <c r="R67" s="217"/>
-      <c r="S67" s="217"/>
-      <c r="T67" s="217"/>
-      <c r="U67" s="217"/>
-      <c r="V67" s="217"/>
-      <c r="W67" s="217"/>
-      <c r="X67" s="217"/>
-      <c r="Y67" s="217"/>
-      <c r="Z67" s="217"/>
-      <c r="AA67" s="217"/>
-      <c r="AB67" s="217"/>
-      <c r="AC67" s="217"/>
-      <c r="AD67" s="217"/>
-      <c r="AE67" s="217"/>
-      <c r="AF67" s="217"/>
-      <c r="AG67" s="217"/>
-      <c r="AH67" s="217"/>
-      <c r="AI67" s="217"/>
-      <c r="AJ67" s="217"/>
-      <c r="AK67" s="217"/>
-      <c r="AL67" s="217"/>
-      <c r="AM67" s="217"/>
-      <c r="AN67" s="217"/>
-      <c r="AO67" s="217"/>
-      <c r="AP67" s="217"/>
-      <c r="AQ67" s="217"/>
-      <c r="AR67" s="217"/>
-      <c r="AS67" s="217"/>
-      <c r="AT67" s="217"/>
-      <c r="AU67" s="217"/>
-      <c r="AV67" s="217"/>
-      <c r="AW67" s="217"/>
-      <c r="AX67" s="217"/>
-      <c r="AY67" s="217"/>
-      <c r="AZ67" s="217"/>
-      <c r="BA67" s="217"/>
-      <c r="BB67" s="218"/>
+      <c r="F67" s="214"/>
+      <c r="G67" s="215"/>
+      <c r="H67" s="215"/>
+      <c r="I67" s="215"/>
+      <c r="J67" s="215"/>
+      <c r="K67" s="215"/>
+      <c r="L67" s="215"/>
+      <c r="M67" s="215"/>
+      <c r="N67" s="215"/>
+      <c r="O67" s="215"/>
+      <c r="P67" s="215"/>
+      <c r="Q67" s="215"/>
+      <c r="R67" s="215"/>
+      <c r="S67" s="215"/>
+      <c r="T67" s="215"/>
+      <c r="U67" s="215"/>
+      <c r="V67" s="215"/>
+      <c r="W67" s="215"/>
+      <c r="X67" s="215"/>
+      <c r="Y67" s="215"/>
+      <c r="Z67" s="215"/>
+      <c r="AA67" s="215"/>
+      <c r="AB67" s="215"/>
+      <c r="AC67" s="215"/>
+      <c r="AD67" s="215"/>
+      <c r="AE67" s="215"/>
+      <c r="AF67" s="215"/>
+      <c r="AG67" s="215"/>
+      <c r="AH67" s="215"/>
+      <c r="AI67" s="215"/>
+      <c r="AJ67" s="215"/>
+      <c r="AK67" s="215"/>
+      <c r="AL67" s="215"/>
+      <c r="AM67" s="215"/>
+      <c r="AN67" s="215"/>
+      <c r="AO67" s="215"/>
+      <c r="AP67" s="215"/>
+      <c r="AQ67" s="215"/>
+      <c r="AR67" s="215"/>
+      <c r="AS67" s="215"/>
+      <c r="AT67" s="215"/>
+      <c r="AU67" s="215"/>
+      <c r="AV67" s="215"/>
+      <c r="AW67" s="215"/>
+      <c r="AX67" s="215"/>
+      <c r="AY67" s="215"/>
+      <c r="AZ67" s="215"/>
+      <c r="BA67" s="215"/>
+      <c r="BB67" s="216"/>
     </row>
     <row r="68" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A68" s="227"/>
-      <c r="B68" s="229"/>
-      <c r="C68" s="231"/>
-      <c r="D68" s="231"/>
-      <c r="E68" s="232"/>
-      <c r="F68" s="219"/>
-      <c r="G68" s="220"/>
-      <c r="H68" s="220"/>
-      <c r="I68" s="220"/>
-      <c r="J68" s="220"/>
-      <c r="K68" s="220"/>
-      <c r="L68" s="220"/>
-      <c r="M68" s="220"/>
-      <c r="N68" s="220"/>
-      <c r="O68" s="220"/>
-      <c r="P68" s="220"/>
-      <c r="Q68" s="220"/>
-      <c r="R68" s="220"/>
-      <c r="S68" s="220"/>
-      <c r="T68" s="220"/>
-      <c r="U68" s="220"/>
-      <c r="V68" s="220"/>
-      <c r="W68" s="220"/>
-      <c r="X68" s="220"/>
-      <c r="Y68" s="220"/>
-      <c r="Z68" s="220"/>
-      <c r="AA68" s="220"/>
-      <c r="AB68" s="220"/>
-      <c r="AC68" s="220"/>
-      <c r="AD68" s="220"/>
-      <c r="AE68" s="220"/>
-      <c r="AF68" s="220"/>
-      <c r="AG68" s="220"/>
-      <c r="AH68" s="220"/>
-      <c r="AI68" s="220"/>
-      <c r="AJ68" s="220"/>
-      <c r="AK68" s="220"/>
-      <c r="AL68" s="220"/>
-      <c r="AM68" s="220"/>
-      <c r="AN68" s="220"/>
-      <c r="AO68" s="220"/>
-      <c r="AP68" s="220"/>
-      <c r="AQ68" s="220"/>
-      <c r="AR68" s="220"/>
-      <c r="AS68" s="220"/>
-      <c r="AT68" s="220"/>
-      <c r="AU68" s="220"/>
-      <c r="AV68" s="220"/>
-      <c r="AW68" s="220"/>
-      <c r="AX68" s="220"/>
-      <c r="AY68" s="220"/>
-      <c r="AZ68" s="220"/>
-      <c r="BA68" s="220"/>
-      <c r="BB68" s="221"/>
+      <c r="A68" s="225"/>
+      <c r="B68" s="227"/>
+      <c r="C68" s="229"/>
+      <c r="D68" s="229"/>
+      <c r="E68" s="230"/>
+      <c r="F68" s="217"/>
+      <c r="G68" s="218"/>
+      <c r="H68" s="218"/>
+      <c r="I68" s="218"/>
+      <c r="J68" s="218"/>
+      <c r="K68" s="218"/>
+      <c r="L68" s="218"/>
+      <c r="M68" s="218"/>
+      <c r="N68" s="218"/>
+      <c r="O68" s="218"/>
+      <c r="P68" s="218"/>
+      <c r="Q68" s="218"/>
+      <c r="R68" s="218"/>
+      <c r="S68" s="218"/>
+      <c r="T68" s="218"/>
+      <c r="U68" s="218"/>
+      <c r="V68" s="218"/>
+      <c r="W68" s="218"/>
+      <c r="X68" s="218"/>
+      <c r="Y68" s="218"/>
+      <c r="Z68" s="218"/>
+      <c r="AA68" s="218"/>
+      <c r="AB68" s="218"/>
+      <c r="AC68" s="218"/>
+      <c r="AD68" s="218"/>
+      <c r="AE68" s="218"/>
+      <c r="AF68" s="218"/>
+      <c r="AG68" s="218"/>
+      <c r="AH68" s="218"/>
+      <c r="AI68" s="218"/>
+      <c r="AJ68" s="218"/>
+      <c r="AK68" s="218"/>
+      <c r="AL68" s="218"/>
+      <c r="AM68" s="218"/>
+      <c r="AN68" s="218"/>
+      <c r="AO68" s="218"/>
+      <c r="AP68" s="218"/>
+      <c r="AQ68" s="218"/>
+      <c r="AR68" s="218"/>
+      <c r="AS68" s="218"/>
+      <c r="AT68" s="218"/>
+      <c r="AU68" s="218"/>
+      <c r="AV68" s="218"/>
+      <c r="AW68" s="218"/>
+      <c r="AX68" s="218"/>
+      <c r="AY68" s="218"/>
+      <c r="AZ68" s="218"/>
+      <c r="BA68" s="218"/>
+      <c r="BB68" s="219"/>
     </row>
     <row r="69" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="222" t="b">
-        <v>0</v>
-      </c>
-      <c r="B69" s="224" t="s">
+      <c r="A69" s="220" t="b">
+        <v>0</v>
+      </c>
+      <c r="B69" s="222" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="112">
+      <c r="C69" s="111">
         <f>SUM(F69:BB69)</f>
         <v>1.5</v>
       </c>
-      <c r="D69" s="112">
+      <c r="D69" s="111">
         <f>SUM(F70:BB70)</f>
         <v>0</v>
       </c>
@@ -7059,8 +7086,8 @@
       <c r="BB69" s="32"/>
     </row>
     <row r="70" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="223"/>
-      <c r="B70" s="225"/>
+      <c r="A70" s="221"/>
+      <c r="B70" s="223"/>
       <c r="C70" s="102"/>
       <c r="D70" s="102"/>
       <c r="E70" s="106"/>
@@ -7115,21 +7142,21 @@
       <c r="BB70" s="29"/>
     </row>
     <row r="71" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="244" t="b">
-        <v>0</v>
-      </c>
-      <c r="B71" s="245" t="s">
+      <c r="A71" s="242" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="112">
+      <c r="C71" s="111">
         <f>SUM(F71:BB71)</f>
         <v>1</v>
       </c>
-      <c r="D71" s="112">
+      <c r="D71" s="111">
         <f>SUM(F72:BB72)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="113">
+      <c r="E71" s="112">
         <f t="shared" ref="E71" si="4">(AVERAGE(C71,C72)-AVERAGE(D71,D72) )</f>
         <v>1</v>
       </c>
@@ -7186,8 +7213,8 @@
       <c r="BB71" s="32"/>
     </row>
     <row r="72" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="223"/>
-      <c r="B72" s="246"/>
+      <c r="A72" s="221"/>
+      <c r="B72" s="244"/>
       <c r="C72" s="102"/>
       <c r="D72" s="102"/>
       <c r="E72" s="106"/>
@@ -7242,21 +7269,21 @@
       <c r="BB72" s="29"/>
     </row>
     <row r="73" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="247" t="b">
-        <v>0</v>
-      </c>
-      <c r="B73" s="248" t="s">
+      <c r="A73" s="245" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" s="246" t="s">
         <v>47</v>
       </c>
-      <c r="C73" s="112">
+      <c r="C73" s="111">
         <f>SUM(F73:BB73)</f>
         <v>1</v>
       </c>
-      <c r="D73" s="112">
+      <c r="D73" s="111">
         <f>SUM(F74:BB74)</f>
         <v>0</v>
       </c>
-      <c r="E73" s="113">
+      <c r="E73" s="112">
         <f>(AVERAGE(C73,C74)-AVERAGE(D73,D74) )</f>
         <v>1</v>
       </c>
@@ -7313,11 +7340,11 @@
       <c r="BB73" s="26"/>
     </row>
     <row r="74" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A74" s="247"/>
-      <c r="B74" s="249"/>
+      <c r="A74" s="245"/>
+      <c r="B74" s="247"/>
       <c r="C74" s="102"/>
       <c r="D74" s="102"/>
-      <c r="E74" s="145"/>
+      <c r="E74" s="143"/>
       <c r="F74" s="25"/>
       <c r="G74" s="58"/>
       <c r="H74" s="58"/>
@@ -7369,142 +7396,142 @@
       <c r="BB74" s="26"/>
     </row>
     <row r="75" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="233" t="b">
-        <v>0</v>
-      </c>
-      <c r="B75" s="235" t="s">
+      <c r="A75" s="231" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" s="233" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="128">
+      <c r="C75" s="127">
         <f>SUM(C77:C86)</f>
         <v>11</v>
       </c>
-      <c r="D75" s="128">
+      <c r="D75" s="127">
         <f>SUM(D77:D86)</f>
         <v>0</v>
       </c>
-      <c r="E75" s="128">
+      <c r="E75" s="127">
         <f>(C75-D75)</f>
         <v>11</v>
       </c>
-      <c r="F75" s="238"/>
-      <c r="G75" s="239"/>
-      <c r="H75" s="239"/>
-      <c r="I75" s="239"/>
-      <c r="J75" s="239"/>
-      <c r="K75" s="239"/>
-      <c r="L75" s="239"/>
-      <c r="M75" s="239"/>
-      <c r="N75" s="239"/>
-      <c r="O75" s="239"/>
-      <c r="P75" s="239"/>
-      <c r="Q75" s="239"/>
-      <c r="R75" s="239"/>
-      <c r="S75" s="239"/>
-      <c r="T75" s="239"/>
-      <c r="U75" s="239"/>
-      <c r="V75" s="239"/>
-      <c r="W75" s="239"/>
-      <c r="X75" s="239"/>
-      <c r="Y75" s="239"/>
-      <c r="Z75" s="239"/>
-      <c r="AA75" s="239"/>
-      <c r="AB75" s="239"/>
-      <c r="AC75" s="239"/>
-      <c r="AD75" s="239"/>
-      <c r="AE75" s="239"/>
-      <c r="AF75" s="239"/>
-      <c r="AG75" s="239"/>
-      <c r="AH75" s="239"/>
-      <c r="AI75" s="239"/>
-      <c r="AJ75" s="239"/>
-      <c r="AK75" s="239"/>
-      <c r="AL75" s="239"/>
-      <c r="AM75" s="239"/>
-      <c r="AN75" s="239"/>
-      <c r="AO75" s="239"/>
-      <c r="AP75" s="239"/>
-      <c r="AQ75" s="239"/>
-      <c r="AR75" s="239"/>
-      <c r="AS75" s="239"/>
-      <c r="AT75" s="239"/>
-      <c r="AU75" s="239"/>
-      <c r="AV75" s="239"/>
-      <c r="AW75" s="239"/>
-      <c r="AX75" s="239"/>
-      <c r="AY75" s="239"/>
-      <c r="AZ75" s="239"/>
-      <c r="BA75" s="239"/>
-      <c r="BB75" s="240"/>
+      <c r="F75" s="236"/>
+      <c r="G75" s="237"/>
+      <c r="H75" s="237"/>
+      <c r="I75" s="237"/>
+      <c r="J75" s="237"/>
+      <c r="K75" s="237"/>
+      <c r="L75" s="237"/>
+      <c r="M75" s="237"/>
+      <c r="N75" s="237"/>
+      <c r="O75" s="237"/>
+      <c r="P75" s="237"/>
+      <c r="Q75" s="237"/>
+      <c r="R75" s="237"/>
+      <c r="S75" s="237"/>
+      <c r="T75" s="237"/>
+      <c r="U75" s="237"/>
+      <c r="V75" s="237"/>
+      <c r="W75" s="237"/>
+      <c r="X75" s="237"/>
+      <c r="Y75" s="237"/>
+      <c r="Z75" s="237"/>
+      <c r="AA75" s="237"/>
+      <c r="AB75" s="237"/>
+      <c r="AC75" s="237"/>
+      <c r="AD75" s="237"/>
+      <c r="AE75" s="237"/>
+      <c r="AF75" s="237"/>
+      <c r="AG75" s="237"/>
+      <c r="AH75" s="237"/>
+      <c r="AI75" s="237"/>
+      <c r="AJ75" s="237"/>
+      <c r="AK75" s="237"/>
+      <c r="AL75" s="237"/>
+      <c r="AM75" s="237"/>
+      <c r="AN75" s="237"/>
+      <c r="AO75" s="237"/>
+      <c r="AP75" s="237"/>
+      <c r="AQ75" s="237"/>
+      <c r="AR75" s="237"/>
+      <c r="AS75" s="237"/>
+      <c r="AT75" s="237"/>
+      <c r="AU75" s="237"/>
+      <c r="AV75" s="237"/>
+      <c r="AW75" s="237"/>
+      <c r="AX75" s="237"/>
+      <c r="AY75" s="237"/>
+      <c r="AZ75" s="237"/>
+      <c r="BA75" s="237"/>
+      <c r="BB75" s="238"/>
     </row>
     <row r="76" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A76" s="234"/>
-      <c r="B76" s="236"/>
-      <c r="C76" s="237"/>
-      <c r="D76" s="237"/>
-      <c r="E76" s="129"/>
-      <c r="F76" s="241"/>
-      <c r="G76" s="242"/>
-      <c r="H76" s="242"/>
-      <c r="I76" s="242"/>
-      <c r="J76" s="242"/>
-      <c r="K76" s="242"/>
-      <c r="L76" s="242"/>
-      <c r="M76" s="242"/>
-      <c r="N76" s="242"/>
-      <c r="O76" s="242"/>
-      <c r="P76" s="242"/>
-      <c r="Q76" s="242"/>
-      <c r="R76" s="242"/>
-      <c r="S76" s="242"/>
-      <c r="T76" s="242"/>
-      <c r="U76" s="242"/>
-      <c r="V76" s="242"/>
-      <c r="W76" s="242"/>
-      <c r="X76" s="242"/>
-      <c r="Y76" s="242"/>
-      <c r="Z76" s="242"/>
-      <c r="AA76" s="242"/>
-      <c r="AB76" s="242"/>
-      <c r="AC76" s="242"/>
-      <c r="AD76" s="242"/>
-      <c r="AE76" s="242"/>
-      <c r="AF76" s="242"/>
-      <c r="AG76" s="242"/>
-      <c r="AH76" s="242"/>
-      <c r="AI76" s="242"/>
-      <c r="AJ76" s="242"/>
-      <c r="AK76" s="242"/>
-      <c r="AL76" s="242"/>
-      <c r="AM76" s="242"/>
-      <c r="AN76" s="242"/>
-      <c r="AO76" s="242"/>
-      <c r="AP76" s="242"/>
-      <c r="AQ76" s="242"/>
-      <c r="AR76" s="242"/>
-      <c r="AS76" s="242"/>
-      <c r="AT76" s="242"/>
-      <c r="AU76" s="242"/>
-      <c r="AV76" s="242"/>
-      <c r="AW76" s="242"/>
-      <c r="AX76" s="242"/>
-      <c r="AY76" s="242"/>
-      <c r="AZ76" s="242"/>
-      <c r="BA76" s="242"/>
-      <c r="BB76" s="243"/>
+      <c r="A76" s="232"/>
+      <c r="B76" s="234"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="235"/>
+      <c r="E76" s="128"/>
+      <c r="F76" s="239"/>
+      <c r="G76" s="240"/>
+      <c r="H76" s="240"/>
+      <c r="I76" s="240"/>
+      <c r="J76" s="240"/>
+      <c r="K76" s="240"/>
+      <c r="L76" s="240"/>
+      <c r="M76" s="240"/>
+      <c r="N76" s="240"/>
+      <c r="O76" s="240"/>
+      <c r="P76" s="240"/>
+      <c r="Q76" s="240"/>
+      <c r="R76" s="240"/>
+      <c r="S76" s="240"/>
+      <c r="T76" s="240"/>
+      <c r="U76" s="240"/>
+      <c r="V76" s="240"/>
+      <c r="W76" s="240"/>
+      <c r="X76" s="240"/>
+      <c r="Y76" s="240"/>
+      <c r="Z76" s="240"/>
+      <c r="AA76" s="240"/>
+      <c r="AB76" s="240"/>
+      <c r="AC76" s="240"/>
+      <c r="AD76" s="240"/>
+      <c r="AE76" s="240"/>
+      <c r="AF76" s="240"/>
+      <c r="AG76" s="240"/>
+      <c r="AH76" s="240"/>
+      <c r="AI76" s="240"/>
+      <c r="AJ76" s="240"/>
+      <c r="AK76" s="240"/>
+      <c r="AL76" s="240"/>
+      <c r="AM76" s="240"/>
+      <c r="AN76" s="240"/>
+      <c r="AO76" s="240"/>
+      <c r="AP76" s="240"/>
+      <c r="AQ76" s="240"/>
+      <c r="AR76" s="240"/>
+      <c r="AS76" s="240"/>
+      <c r="AT76" s="240"/>
+      <c r="AU76" s="240"/>
+      <c r="AV76" s="240"/>
+      <c r="AW76" s="240"/>
+      <c r="AX76" s="240"/>
+      <c r="AY76" s="240"/>
+      <c r="AZ76" s="240"/>
+      <c r="BA76" s="240"/>
+      <c r="BB76" s="241"/>
     </row>
     <row r="77" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="250" t="b">
-        <v>0</v>
-      </c>
-      <c r="B77" s="252" t="s">
+      <c r="A77" s="248" t="b">
+        <v>0</v>
+      </c>
+      <c r="B77" s="250" t="s">
         <v>48</v>
       </c>
-      <c r="C77" s="112">
+      <c r="C77" s="111">
         <f>SUM(F77:BB77)</f>
         <v>1.5</v>
       </c>
-      <c r="D77" s="112">
+      <c r="D77" s="111">
         <f>SUM(F78:BB78)</f>
         <v>0</v>
       </c>
@@ -7565,8 +7592,8 @@
       <c r="BB77" s="40"/>
     </row>
     <row r="78" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="251"/>
-      <c r="B78" s="253"/>
+      <c r="A78" s="249"/>
+      <c r="B78" s="251"/>
       <c r="C78" s="102"/>
       <c r="D78" s="102"/>
       <c r="E78" s="106"/>
@@ -7621,21 +7648,21 @@
       <c r="BB78" s="29"/>
     </row>
     <row r="79" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="254" t="b">
-        <v>0</v>
-      </c>
-      <c r="B79" s="255" t="s">
+      <c r="A79" s="252" t="b">
+        <v>0</v>
+      </c>
+      <c r="B79" s="253" t="s">
         <v>49</v>
       </c>
-      <c r="C79" s="112">
+      <c r="C79" s="111">
         <f>SUM(F79:BB79)</f>
         <v>1</v>
       </c>
-      <c r="D79" s="112">
+      <c r="D79" s="111">
         <f>SUM(F80:BB80)</f>
         <v>0</v>
       </c>
-      <c r="E79" s="113">
+      <c r="E79" s="112">
         <f t="shared" ref="E79:E83" si="5">(AVERAGE(C79,C80)-AVERAGE(D79,D80) )</f>
         <v>1</v>
       </c>
@@ -7692,8 +7719,8 @@
       <c r="BB79" s="26"/>
     </row>
     <row r="80" spans="1:54" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="251"/>
-      <c r="B80" s="253"/>
+      <c r="A80" s="249"/>
+      <c r="B80" s="251"/>
       <c r="C80" s="102"/>
       <c r="D80" s="102"/>
       <c r="E80" s="106"/>
@@ -7748,21 +7775,21 @@
       <c r="BB80" s="29"/>
     </row>
     <row r="81" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="256" t="b">
-        <v>0</v>
-      </c>
-      <c r="B81" s="257" t="s">
+      <c r="A81" s="254" t="b">
+        <v>0</v>
+      </c>
+      <c r="B81" s="255" t="s">
         <v>52</v>
       </c>
-      <c r="C81" s="112">
+      <c r="C81" s="111">
         <f>SUM(F81:BB81)</f>
         <v>2.5</v>
       </c>
-      <c r="D81" s="112">
+      <c r="D81" s="111">
         <f>SUM(F82:BB82)</f>
         <v>0</v>
       </c>
-      <c r="E81" s="113">
+      <c r="E81" s="112">
         <f t="shared" si="5"/>
         <v>2.5</v>
       </c>
@@ -7821,8 +7848,8 @@
       <c r="BB81" s="32"/>
     </row>
     <row r="82" spans="1:55" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="251"/>
-      <c r="B82" s="253"/>
+      <c r="A82" s="249"/>
+      <c r="B82" s="251"/>
       <c r="C82" s="102"/>
       <c r="D82" s="102"/>
       <c r="E82" s="106"/>
@@ -7877,21 +7904,21 @@
       <c r="BB82" s="29"/>
     </row>
     <row r="83" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="254" t="b">
-        <v>0</v>
-      </c>
-      <c r="B83" s="255" t="s">
+      <c r="A83" s="252" t="b">
+        <v>0</v>
+      </c>
+      <c r="B83" s="253" t="s">
         <v>51</v>
       </c>
-      <c r="C83" s="112">
+      <c r="C83" s="111">
         <f>SUM(F83:BB83)</f>
         <v>5.5</v>
       </c>
-      <c r="D83" s="112">
+      <c r="D83" s="111">
         <f>SUM(F84:BB84)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="113">
+      <c r="E83" s="112">
         <f t="shared" si="5"/>
         <v>5.5</v>
       </c>
@@ -7954,8 +7981,8 @@
       <c r="BB83" s="32"/>
     </row>
     <row r="84" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="251"/>
-      <c r="B84" s="253"/>
+      <c r="A84" s="249"/>
+      <c r="B84" s="251"/>
       <c r="C84" s="102"/>
       <c r="D84" s="102"/>
       <c r="E84" s="106"/>
@@ -8010,21 +8037,21 @@
       <c r="BB84" s="29"/>
     </row>
     <row r="85" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="254" t="b">
-        <v>0</v>
-      </c>
-      <c r="B85" s="268" t="s">
+      <c r="A85" s="252" t="b">
+        <v>0</v>
+      </c>
+      <c r="B85" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="C85" s="112">
+      <c r="C85" s="111">
         <f>SUM(F85:BB85)</f>
         <v>0.5</v>
       </c>
-      <c r="D85" s="112">
+      <c r="D85" s="111">
         <f>SUM(F86:BB86)</f>
         <v>0</v>
       </c>
-      <c r="E85" s="113">
+      <c r="E85" s="112">
         <f>(AVERAGE(C85,C86)-AVERAGE(D85,D86) )</f>
         <v>0.5</v>
       </c>
@@ -8081,11 +8108,11 @@
       </c>
     </row>
     <row r="86" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A86" s="256"/>
-      <c r="B86" s="269"/>
+      <c r="A86" s="254"/>
+      <c r="B86" s="267"/>
       <c r="C86" s="102"/>
       <c r="D86" s="102"/>
-      <c r="E86" s="145"/>
+      <c r="E86" s="143"/>
       <c r="F86" s="25"/>
       <c r="G86" s="58"/>
       <c r="H86" s="58"/>
@@ -8137,142 +8164,142 @@
       <c r="BB86" s="26"/>
     </row>
     <row r="87" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="270" t="s">
+      <c r="A87" s="268" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="271"/>
-      <c r="C87" s="274">
+      <c r="B87" s="269"/>
+      <c r="C87" s="272">
         <f>SUM(C89,C92)</f>
         <v>22</v>
       </c>
-      <c r="D87" s="274">
+      <c r="D87" s="272">
         <f>SUM(D89)</f>
         <v>2.5</v>
       </c>
-      <c r="E87" s="276">
+      <c r="E87" s="274">
         <f>(C87-D87)</f>
         <v>19.5</v>
       </c>
-      <c r="F87" s="258"/>
-      <c r="G87" s="259"/>
-      <c r="H87" s="259"/>
-      <c r="I87" s="259"/>
-      <c r="J87" s="259"/>
-      <c r="K87" s="259"/>
-      <c r="L87" s="259"/>
-      <c r="M87" s="259"/>
-      <c r="N87" s="259"/>
-      <c r="O87" s="259"/>
-      <c r="P87" s="259"/>
-      <c r="Q87" s="259"/>
-      <c r="R87" s="259"/>
-      <c r="S87" s="259"/>
-      <c r="T87" s="259"/>
-      <c r="U87" s="259"/>
-      <c r="V87" s="259"/>
-      <c r="W87" s="259"/>
-      <c r="X87" s="259"/>
-      <c r="Y87" s="259"/>
-      <c r="Z87" s="259"/>
-      <c r="AA87" s="259"/>
-      <c r="AB87" s="259"/>
-      <c r="AC87" s="259"/>
-      <c r="AD87" s="259"/>
-      <c r="AE87" s="259"/>
-      <c r="AF87" s="259"/>
-      <c r="AG87" s="259"/>
-      <c r="AH87" s="259"/>
-      <c r="AI87" s="259"/>
-      <c r="AJ87" s="259"/>
-      <c r="AK87" s="259"/>
-      <c r="AL87" s="259"/>
-      <c r="AM87" s="259"/>
-      <c r="AN87" s="259"/>
-      <c r="AO87" s="259"/>
-      <c r="AP87" s="259"/>
-      <c r="AQ87" s="259"/>
-      <c r="AR87" s="259"/>
-      <c r="AS87" s="259"/>
-      <c r="AT87" s="259"/>
-      <c r="AU87" s="259"/>
-      <c r="AV87" s="259"/>
-      <c r="AW87" s="259"/>
-      <c r="AX87" s="259"/>
-      <c r="AY87" s="259"/>
-      <c r="AZ87" s="259"/>
-      <c r="BA87" s="259"/>
-      <c r="BB87" s="260"/>
+      <c r="F87" s="256"/>
+      <c r="G87" s="257"/>
+      <c r="H87" s="257"/>
+      <c r="I87" s="257"/>
+      <c r="J87" s="257"/>
+      <c r="K87" s="257"/>
+      <c r="L87" s="257"/>
+      <c r="M87" s="257"/>
+      <c r="N87" s="257"/>
+      <c r="O87" s="257"/>
+      <c r="P87" s="257"/>
+      <c r="Q87" s="257"/>
+      <c r="R87" s="257"/>
+      <c r="S87" s="257"/>
+      <c r="T87" s="257"/>
+      <c r="U87" s="257"/>
+      <c r="V87" s="257"/>
+      <c r="W87" s="257"/>
+      <c r="X87" s="257"/>
+      <c r="Y87" s="257"/>
+      <c r="Z87" s="257"/>
+      <c r="AA87" s="257"/>
+      <c r="AB87" s="257"/>
+      <c r="AC87" s="257"/>
+      <c r="AD87" s="257"/>
+      <c r="AE87" s="257"/>
+      <c r="AF87" s="257"/>
+      <c r="AG87" s="257"/>
+      <c r="AH87" s="257"/>
+      <c r="AI87" s="257"/>
+      <c r="AJ87" s="257"/>
+      <c r="AK87" s="257"/>
+      <c r="AL87" s="257"/>
+      <c r="AM87" s="257"/>
+      <c r="AN87" s="257"/>
+      <c r="AO87" s="257"/>
+      <c r="AP87" s="257"/>
+      <c r="AQ87" s="257"/>
+      <c r="AR87" s="257"/>
+      <c r="AS87" s="257"/>
+      <c r="AT87" s="257"/>
+      <c r="AU87" s="257"/>
+      <c r="AV87" s="257"/>
+      <c r="AW87" s="257"/>
+      <c r="AX87" s="257"/>
+      <c r="AY87" s="257"/>
+      <c r="AZ87" s="257"/>
+      <c r="BA87" s="257"/>
+      <c r="BB87" s="258"/>
     </row>
     <row r="88" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A88" s="272"/>
-      <c r="B88" s="273"/>
-      <c r="C88" s="275"/>
-      <c r="D88" s="275"/>
-      <c r="E88" s="277"/>
-      <c r="F88" s="261"/>
-      <c r="G88" s="262"/>
-      <c r="H88" s="262"/>
-      <c r="I88" s="262"/>
-      <c r="J88" s="262"/>
-      <c r="K88" s="262"/>
-      <c r="L88" s="262"/>
-      <c r="M88" s="262"/>
-      <c r="N88" s="262"/>
-      <c r="O88" s="262"/>
-      <c r="P88" s="262"/>
-      <c r="Q88" s="262"/>
-      <c r="R88" s="262"/>
-      <c r="S88" s="262"/>
-      <c r="T88" s="262"/>
-      <c r="U88" s="262"/>
-      <c r="V88" s="262"/>
-      <c r="W88" s="262"/>
-      <c r="X88" s="262"/>
-      <c r="Y88" s="262"/>
-      <c r="Z88" s="262"/>
-      <c r="AA88" s="262"/>
-      <c r="AB88" s="262"/>
-      <c r="AC88" s="262"/>
-      <c r="AD88" s="262"/>
-      <c r="AE88" s="262"/>
-      <c r="AF88" s="262"/>
-      <c r="AG88" s="262"/>
-      <c r="AH88" s="262"/>
-      <c r="AI88" s="262"/>
-      <c r="AJ88" s="262"/>
-      <c r="AK88" s="262"/>
-      <c r="AL88" s="262"/>
-      <c r="AM88" s="262"/>
-      <c r="AN88" s="262"/>
-      <c r="AO88" s="262"/>
-      <c r="AP88" s="262"/>
-      <c r="AQ88" s="262"/>
-      <c r="AR88" s="262"/>
-      <c r="AS88" s="262"/>
-      <c r="AT88" s="262"/>
-      <c r="AU88" s="262"/>
-      <c r="AV88" s="262"/>
-      <c r="AW88" s="262"/>
-      <c r="AX88" s="262"/>
-      <c r="AY88" s="262"/>
-      <c r="AZ88" s="262"/>
-      <c r="BA88" s="262"/>
-      <c r="BB88" s="263"/>
+      <c r="A88" s="270"/>
+      <c r="B88" s="271"/>
+      <c r="C88" s="273"/>
+      <c r="D88" s="273"/>
+      <c r="E88" s="275"/>
+      <c r="F88" s="259"/>
+      <c r="G88" s="260"/>
+      <c r="H88" s="260"/>
+      <c r="I88" s="260"/>
+      <c r="J88" s="260"/>
+      <c r="K88" s="260"/>
+      <c r="L88" s="260"/>
+      <c r="M88" s="260"/>
+      <c r="N88" s="260"/>
+      <c r="O88" s="260"/>
+      <c r="P88" s="260"/>
+      <c r="Q88" s="260"/>
+      <c r="R88" s="260"/>
+      <c r="S88" s="260"/>
+      <c r="T88" s="260"/>
+      <c r="U88" s="260"/>
+      <c r="V88" s="260"/>
+      <c r="W88" s="260"/>
+      <c r="X88" s="260"/>
+      <c r="Y88" s="260"/>
+      <c r="Z88" s="260"/>
+      <c r="AA88" s="260"/>
+      <c r="AB88" s="260"/>
+      <c r="AC88" s="260"/>
+      <c r="AD88" s="260"/>
+      <c r="AE88" s="260"/>
+      <c r="AF88" s="260"/>
+      <c r="AG88" s="260"/>
+      <c r="AH88" s="260"/>
+      <c r="AI88" s="260"/>
+      <c r="AJ88" s="260"/>
+      <c r="AK88" s="260"/>
+      <c r="AL88" s="260"/>
+      <c r="AM88" s="260"/>
+      <c r="AN88" s="260"/>
+      <c r="AO88" s="260"/>
+      <c r="AP88" s="260"/>
+      <c r="AQ88" s="260"/>
+      <c r="AR88" s="260"/>
+      <c r="AS88" s="260"/>
+      <c r="AT88" s="260"/>
+      <c r="AU88" s="260"/>
+      <c r="AV88" s="260"/>
+      <c r="AW88" s="260"/>
+      <c r="AX88" s="260"/>
+      <c r="AY88" s="260"/>
+      <c r="AZ88" s="260"/>
+      <c r="BA88" s="260"/>
+      <c r="BB88" s="261"/>
     </row>
     <row r="89" spans="1:55" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41"/>
-      <c r="B89" s="264" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="112">
+      <c r="B89" s="262" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="111">
         <f>SUM(F89:BB89)</f>
         <v>22</v>
       </c>
-      <c r="D89" s="112">
+      <c r="D89" s="111">
         <f>SUM(F90:BB90)</f>
         <v>2.5</v>
       </c>
-      <c r="E89" s="113">
+      <c r="E89" s="112">
         <f>(AVERAGE(C89,C90)-AVERAGE(D89,D90) )</f>
         <v>19.5</v>
       </c>
@@ -8308,7 +8335,7 @@
         <v>0.5</v>
       </c>
       <c r="S89" s="66">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T89" s="67"/>
       <c r="U89" s="68"/>
@@ -8365,9 +8392,7 @@
       <c r="AP89" s="66">
         <v>0.5</v>
       </c>
-      <c r="AQ89" s="66">
-        <v>0.5</v>
-      </c>
+      <c r="AQ89" s="31"/>
       <c r="AR89" s="66">
         <v>0.5</v>
       </c>
@@ -8400,10 +8425,10 @@
     </row>
     <row r="90" spans="1:55" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A90" s="42"/>
-      <c r="B90" s="265"/>
+      <c r="B90" s="263"/>
       <c r="C90" s="102"/>
       <c r="D90" s="102"/>
-      <c r="E90" s="145"/>
+      <c r="E90" s="143"/>
       <c r="F90" s="77">
         <v>1</v>
       </c>
@@ -8463,15 +8488,15 @@
       <c r="BC90" s="76"/>
     </row>
     <row r="91" spans="1:55" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="280"/>
-      <c r="B91" s="281" t="s">
+      <c r="A91" s="278"/>
+      <c r="B91" s="279" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="283">
+      <c r="C91" s="281">
         <f>SUM((F91:BB91))</f>
         <v>1</v>
       </c>
-      <c r="D91" s="112"/>
+      <c r="D91" s="111"/>
       <c r="E91" s="101"/>
       <c r="F91" s="30"/>
       <c r="G91" s="31"/>
@@ -8527,11 +8552,11 @@
       <c r="BC91" s="76"/>
     </row>
     <row r="92" spans="1:55" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A92" s="279"/>
-      <c r="B92" s="282"/>
-      <c r="C92" s="284"/>
-      <c r="D92" s="285"/>
-      <c r="E92" s="285"/>
+      <c r="A92" s="277"/>
+      <c r="B92" s="280"/>
+      <c r="C92" s="282"/>
+      <c r="D92" s="283"/>
+      <c r="E92" s="283"/>
       <c r="F92" s="27"/>
       <c r="G92" s="28"/>
       <c r="H92" s="28"/>
@@ -8592,61 +8617,61 @@
       </c>
       <c r="D93" s="47">
         <f>SUM(D21,D29,D41,D49,D67,D75,D87, D15,D6)</f>
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="E93" s="48">
         <f>SUM(E21,E29,E41,E49,E67,E75,E87,E6,E15)</f>
-        <v>72</v>
-      </c>
-      <c r="F93" s="266"/>
-      <c r="G93" s="267"/>
-      <c r="H93" s="267"/>
-      <c r="I93" s="267"/>
-      <c r="J93" s="267"/>
-      <c r="K93" s="267"/>
-      <c r="L93" s="267"/>
-      <c r="M93" s="267"/>
-      <c r="N93" s="267"/>
-      <c r="O93" s="267"/>
-      <c r="P93" s="267"/>
-      <c r="Q93" s="267"/>
-      <c r="R93" s="267"/>
-      <c r="S93" s="267"/>
-      <c r="T93" s="267"/>
-      <c r="U93" s="267"/>
-      <c r="V93" s="267"/>
-      <c r="W93" s="267"/>
-      <c r="X93" s="267"/>
-      <c r="Y93" s="267"/>
-      <c r="Z93" s="267"/>
-      <c r="AA93" s="267"/>
-      <c r="AB93" s="267"/>
-      <c r="AC93" s="267"/>
-      <c r="AD93" s="267"/>
-      <c r="AE93" s="267"/>
-      <c r="AF93" s="267"/>
-      <c r="AG93" s="267"/>
-      <c r="AH93" s="267"/>
-      <c r="AI93" s="267"/>
-      <c r="AJ93" s="267"/>
-      <c r="AK93" s="267"/>
-      <c r="AL93" s="267"/>
-      <c r="AM93" s="267"/>
-      <c r="AN93" s="267"/>
-      <c r="AO93" s="267"/>
-      <c r="AP93" s="267"/>
-      <c r="AQ93" s="267"/>
-      <c r="AR93" s="267"/>
-      <c r="AS93" s="267"/>
-      <c r="AT93" s="267"/>
-      <c r="AU93" s="267"/>
-      <c r="AV93" s="267"/>
-      <c r="AW93" s="267"/>
-      <c r="AX93" s="267"/>
-      <c r="AY93" s="267"/>
-      <c r="AZ93" s="267"/>
-      <c r="BA93" s="267"/>
-      <c r="BB93" s="267"/>
+        <v>69.5</v>
+      </c>
+      <c r="F93" s="264"/>
+      <c r="G93" s="265"/>
+      <c r="H93" s="265"/>
+      <c r="I93" s="265"/>
+      <c r="J93" s="265"/>
+      <c r="K93" s="265"/>
+      <c r="L93" s="265"/>
+      <c r="M93" s="265"/>
+      <c r="N93" s="265"/>
+      <c r="O93" s="265"/>
+      <c r="P93" s="265"/>
+      <c r="Q93" s="265"/>
+      <c r="R93" s="265"/>
+      <c r="S93" s="265"/>
+      <c r="T93" s="265"/>
+      <c r="U93" s="265"/>
+      <c r="V93" s="265"/>
+      <c r="W93" s="265"/>
+      <c r="X93" s="265"/>
+      <c r="Y93" s="265"/>
+      <c r="Z93" s="265"/>
+      <c r="AA93" s="265"/>
+      <c r="AB93" s="265"/>
+      <c r="AC93" s="265"/>
+      <c r="AD93" s="265"/>
+      <c r="AE93" s="265"/>
+      <c r="AF93" s="265"/>
+      <c r="AG93" s="265"/>
+      <c r="AH93" s="265"/>
+      <c r="AI93" s="265"/>
+      <c r="AJ93" s="265"/>
+      <c r="AK93" s="265"/>
+      <c r="AL93" s="265"/>
+      <c r="AM93" s="265"/>
+      <c r="AN93" s="265"/>
+      <c r="AO93" s="265"/>
+      <c r="AP93" s="265"/>
+      <c r="AQ93" s="265"/>
+      <c r="AR93" s="265"/>
+      <c r="AS93" s="265"/>
+      <c r="AT93" s="265"/>
+      <c r="AU93" s="265"/>
+      <c r="AV93" s="265"/>
+      <c r="AW93" s="265"/>
+      <c r="AX93" s="265"/>
+      <c r="AY93" s="265"/>
+      <c r="AZ93" s="265"/>
+      <c r="BA93" s="265"/>
+      <c r="BB93" s="265"/>
     </row>
     <row r="94" spans="1:55" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C94" s="49" t="s">

--- a/IPA_Zeitplan_Nicola_Maeder.xlsx
+++ b/IPA_Zeitplan_Nicola_Maeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taamanii\Documents\Individuelle Praktische Arbeit Nicola\individuelle-praktische-arbeit-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A327F332-557B-489B-BEA6-2F23E1117D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{749CB50B-BB0F-4ED4-BF40-C4CCC458858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{09F15F46-AED7-3C4E-9C62-04C59C5DDA6F}"/>
+    <workbookView xWindow="14550" yWindow="-17400" windowWidth="30960" windowHeight="16800" xr2:uid="{09F15F46-AED7-3C4E-9C62-04C59C5DDA6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Zeitplan_Nicola_Mäder" sheetId="2" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Zeitplan_Nicola_Mäder!$A$1:$BB$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>Tag</t>
   </si>
@@ -139,9 +140,6 @@
   </si>
   <si>
     <t>Ist-Zustand</t>
-  </si>
-  <si>
-    <t>Meilenstein</t>
   </si>
   <si>
     <t>08:00 - 10:00</t>
@@ -341,7 +339,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,12 +511,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,7 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="287">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -965,7 +957,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -994,10 +985,10 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="32" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="31" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="32" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="31" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1018,7 +1009,6 @@
     <xf numFmtId="2" fontId="7" fillId="3" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="29" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
@@ -1026,23 +1016,17 @@
     <xf numFmtId="2" fontId="7" fillId="29" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="2" fontId="7" fillId="31" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="29" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1120,11 +1104,32 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1265,6 +1270,9 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1817,11 +1825,8 @@
     <xf numFmtId="2" fontId="5" fillId="25" borderId="18" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="32" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="20" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="20" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -1836,21 +1841,6 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="29" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="29" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="29" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2215,177 +2205,177 @@
     <col min="2" max="2" width="55.44921875" style="2" customWidth="1"/>
     <col min="3" max="3" width="7.5" style="51" customWidth="1"/>
     <col min="4" max="4" width="7.5" style="52" customWidth="1"/>
-    <col min="5" max="5" width="7.5" style="57" customWidth="1"/>
+    <col min="5" max="5" width="7.5" style="56" customWidth="1"/>
     <col min="6" max="54" width="3.34765625" style="2" customWidth="1"/>
     <col min="55" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="288" t="s">
-        <v>65</v>
+      <c r="A1" s="103" t="s">
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="79" t="s">
+      <c r="C1" s="106" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="80"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="85">
+      <c r="D1" s="107"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="81">
         <v>1</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="87"/>
-      <c r="K1" s="85">
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="81">
         <v>2</v>
       </c>
-      <c r="L1" s="86"/>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="85">
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+      <c r="N1" s="82"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="81">
         <v>3</v>
       </c>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="86"/>
-      <c r="T1" s="87"/>
-      <c r="U1" s="85">
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
+      <c r="S1" s="82"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="81">
         <v>4</v>
       </c>
-      <c r="V1" s="86"/>
-      <c r="W1" s="86"/>
-      <c r="X1" s="86"/>
-      <c r="Y1" s="87"/>
-      <c r="Z1" s="85">
+      <c r="V1" s="82"/>
+      <c r="W1" s="82"/>
+      <c r="X1" s="82"/>
+      <c r="Y1" s="83"/>
+      <c r="Z1" s="81">
         <v>5</v>
       </c>
-      <c r="AA1" s="86"/>
-      <c r="AB1" s="86"/>
-      <c r="AC1" s="86"/>
-      <c r="AD1" s="87"/>
-      <c r="AE1" s="85">
+      <c r="AA1" s="82"/>
+      <c r="AB1" s="82"/>
+      <c r="AC1" s="82"/>
+      <c r="AD1" s="83"/>
+      <c r="AE1" s="81">
         <v>6</v>
       </c>
-      <c r="AF1" s="86"/>
-      <c r="AG1" s="86"/>
-      <c r="AH1" s="86"/>
-      <c r="AI1" s="87"/>
-      <c r="AJ1" s="85">
+      <c r="AF1" s="82"/>
+      <c r="AG1" s="82"/>
+      <c r="AH1" s="82"/>
+      <c r="AI1" s="83"/>
+      <c r="AJ1" s="81">
         <v>7</v>
       </c>
-      <c r="AK1" s="86"/>
-      <c r="AL1" s="86"/>
-      <c r="AM1" s="86"/>
-      <c r="AN1" s="87"/>
-      <c r="AO1" s="85">
+      <c r="AK1" s="82"/>
+      <c r="AL1" s="82"/>
+      <c r="AM1" s="82"/>
+      <c r="AN1" s="83"/>
+      <c r="AO1" s="81">
         <v>8</v>
       </c>
-      <c r="AP1" s="86"/>
-      <c r="AQ1" s="86"/>
-      <c r="AR1" s="86"/>
-      <c r="AS1" s="87"/>
-      <c r="AT1" s="85">
+      <c r="AP1" s="82"/>
+      <c r="AQ1" s="82"/>
+      <c r="AR1" s="82"/>
+      <c r="AS1" s="83"/>
+      <c r="AT1" s="81">
         <v>9</v>
       </c>
-      <c r="AU1" s="86"/>
-      <c r="AV1" s="85">
+      <c r="AU1" s="82"/>
+      <c r="AV1" s="81">
         <v>10</v>
       </c>
-      <c r="AW1" s="86"/>
-      <c r="AX1" s="86"/>
-      <c r="AY1" s="86"/>
-      <c r="AZ1" s="87"/>
-      <c r="BA1" s="85">
+      <c r="AW1" s="82"/>
+      <c r="AX1" s="82"/>
+      <c r="AY1" s="82"/>
+      <c r="AZ1" s="83"/>
+      <c r="BA1" s="81">
         <v>11</v>
       </c>
-      <c r="BB1" s="86"/>
+      <c r="BB1" s="82"/>
     </row>
     <row r="2" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="107"/>
+      <c r="A2" s="104"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="91">
+      <c r="C2" s="109"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="87">
         <v>46134</v>
       </c>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="91">
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="87">
         <v>46135</v>
       </c>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="92"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="88">
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="89"/>
+      <c r="P2" s="84">
         <v>46136</v>
       </c>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="90"/>
-      <c r="U2" s="91">
+      <c r="Q2" s="85"/>
+      <c r="R2" s="85"/>
+      <c r="S2" s="85"/>
+      <c r="T2" s="86"/>
+      <c r="U2" s="87">
         <v>46139</v>
       </c>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="92"/>
-      <c r="Y2" s="93"/>
-      <c r="Z2" s="91">
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="88"/>
+      <c r="Y2" s="89"/>
+      <c r="Z2" s="87">
         <v>46140</v>
       </c>
-      <c r="AA2" s="92"/>
-      <c r="AB2" s="92"/>
-      <c r="AC2" s="92"/>
-      <c r="AD2" s="93"/>
-      <c r="AE2" s="91">
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="88"/>
+      <c r="AC2" s="88"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="87">
         <v>46141</v>
       </c>
-      <c r="AF2" s="92"/>
-      <c r="AG2" s="92"/>
-      <c r="AH2" s="92"/>
-      <c r="AI2" s="93"/>
-      <c r="AJ2" s="91">
+      <c r="AF2" s="88"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="88"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="87">
         <v>46142</v>
       </c>
-      <c r="AK2" s="92"/>
-      <c r="AL2" s="92"/>
-      <c r="AM2" s="92"/>
-      <c r="AN2" s="93"/>
-      <c r="AO2" s="91">
+      <c r="AK2" s="88"/>
+      <c r="AL2" s="88"/>
+      <c r="AM2" s="88"/>
+      <c r="AN2" s="89"/>
+      <c r="AO2" s="87">
         <v>46146</v>
       </c>
-      <c r="AP2" s="92"/>
-      <c r="AQ2" s="92"/>
-      <c r="AR2" s="92"/>
-      <c r="AS2" s="93"/>
-      <c r="AT2" s="91">
+      <c r="AP2" s="88"/>
+      <c r="AQ2" s="88"/>
+      <c r="AR2" s="88"/>
+      <c r="AS2" s="89"/>
+      <c r="AT2" s="87">
         <v>46147</v>
       </c>
-      <c r="AU2" s="92"/>
-      <c r="AV2" s="91">
+      <c r="AU2" s="88"/>
+      <c r="AV2" s="87">
         <v>46148</v>
       </c>
-      <c r="AW2" s="92"/>
-      <c r="AX2" s="92"/>
-      <c r="AY2" s="92"/>
-      <c r="AZ2" s="93"/>
-      <c r="BA2" s="91">
+      <c r="AW2" s="88"/>
+      <c r="AX2" s="88"/>
+      <c r="AY2" s="88"/>
+      <c r="AZ2" s="89"/>
+      <c r="BA2" s="87">
         <v>46180</v>
       </c>
-      <c r="BB2" s="92"/>
+      <c r="BB2" s="88"/>
     </row>
     <row r="3" spans="1:54" ht="83.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="107"/>
+      <c r="A3" s="104"/>
       <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
@@ -2398,156 +2388,156 @@
       <c r="E3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="60" t="s">
+      <c r="H3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="61" t="s">
+      <c r="I3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="I3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="60" t="s">
+      <c r="M3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="61" t="s">
+      <c r="N3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="N3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="Q3" s="60" t="s">
+      <c r="R3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="61" t="s">
+      <c r="S3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="S3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="U3" s="59" t="s">
+      <c r="U3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="V3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="V3" s="60" t="s">
+      <c r="W3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="W3" s="61" t="s">
+      <c r="X3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="X3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="Y3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="Z3" s="59" t="s">
+      <c r="Z3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AA3" s="60" t="s">
+      <c r="AB3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AB3" s="61" t="s">
+      <c r="AC3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="AC3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="AD3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="59" t="s">
+      <c r="AE3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AF3" s="60" t="s">
+      <c r="AG3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AG3" s="61" t="s">
+      <c r="AH3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="AH3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="AI3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AJ3" s="59" t="s">
+      <c r="AJ3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="60" t="s">
+      <c r="AL3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AL3" s="61" t="s">
+      <c r="AM3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="AM3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="AN3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="59" t="s">
+      <c r="AO3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="AP3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AP3" s="60" t="s">
+      <c r="AQ3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AQ3" s="61" t="s">
+      <c r="AR3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="AR3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="AS3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AT3" s="59" t="s">
+      <c r="AT3" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="AU3" s="60" t="s">
+      <c r="AU3" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="AV3" s="59" t="s">
+      <c r="AV3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="AW3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AW3" s="60" t="s">
+      <c r="AX3" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="AX3" s="61" t="s">
+      <c r="AY3" s="59" t="s">
         <v>29</v>
-      </c>
-      <c r="AY3" s="60" t="s">
-        <v>30</v>
       </c>
       <c r="AZ3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="BA3" s="59" t="s">
+      <c r="BA3" s="58" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB3" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="BB3" s="60" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="4" spans="1:54" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="108"/>
+      <c r="A4" s="105"/>
       <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
@@ -2576,19 +2566,19 @@
       </c>
       <c r="K4" s="9" cm="1">
         <f t="array" ref="K4">_xlfn.LET(_xlpm.r, K7:K90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="10" cm="1">
         <f t="array" ref="L4">_xlfn.LET(_xlpm.r, L7:L90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="M4" s="10" cm="1">
         <f t="array" ref="M4">_xlfn.LET(_xlpm.r, M7:M92,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" s="10" cm="1">
         <f t="array" ref="N4">_xlfn.LET(_xlpm.r, N7:N90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O4" s="11" cm="1">
         <f t="array" ref="O4">_xlfn.LET(_xlpm.r, O7:O90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
@@ -2596,19 +2586,19 @@
       </c>
       <c r="P4" s="9" cm="1">
         <f t="array" ref="P4">_xlfn.LET(_xlpm.r, P7:P90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="10" cm="1">
         <f t="array" ref="Q4">_xlfn.LET(_xlpm.r, Q7:Q90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="10" cm="1">
         <f t="array" ref="R4">_xlfn.LET(_xlpm.r, R7:R90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" s="10" cm="1">
         <f t="array" ref="S4">_xlfn.LET(_xlpm.r, S7:S90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4" s="11" cm="1">
         <f t="array" ref="T4">_xlfn.LET(_xlpm.r, T7:T90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
@@ -2616,15 +2606,15 @@
       </c>
       <c r="U4" s="9" cm="1">
         <f t="array" ref="U4">_xlfn.LET(_xlpm.r, U7:U90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" s="10" cm="1">
         <f t="array" ref="V4">_xlfn.LET(_xlpm.r, V7:V90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" s="10" cm="1">
         <f t="array" ref="W4">_xlfn.LET(_xlpm.r, W7:W90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" s="10" cm="1">
         <f t="array" ref="X4">_xlfn.LET(_xlpm.r, X7:X90,SUM( _xlfn._xlws.FILTER( _xlpm.r, MOD(ROW(_xlpm.r) - ROW(INDEX(_xlpm.r,1,1)) + 1, 2) = 0 ) ))</f>
@@ -2755,7 +2745,7 @@
       <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="13"/>
@@ -2960,7 +2950,7 @@
     </row>
     <row r="6" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A6" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>13</v>
@@ -2971,140 +2961,140 @@
       </c>
       <c r="D6" s="23">
         <f>SUM(D7:D14)</f>
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E6" s="24">
         <f>(C6-D6)</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="94"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="95"/>
-      <c r="L6" s="95"/>
-      <c r="M6" s="95"/>
-      <c r="N6" s="95"/>
-      <c r="O6" s="95"/>
-      <c r="P6" s="95"/>
-      <c r="Q6" s="95"/>
-      <c r="R6" s="95"/>
-      <c r="S6" s="95"/>
-      <c r="T6" s="95"/>
-      <c r="U6" s="95"/>
-      <c r="V6" s="95"/>
-      <c r="W6" s="95"/>
-      <c r="X6" s="95"/>
-      <c r="Y6" s="95"/>
-      <c r="Z6" s="95"/>
-      <c r="AA6" s="95"/>
-      <c r="AB6" s="95"/>
-      <c r="AC6" s="95"/>
-      <c r="AD6" s="95"/>
-      <c r="AE6" s="95"/>
-      <c r="AF6" s="95"/>
-      <c r="AG6" s="95"/>
-      <c r="AH6" s="95"/>
-      <c r="AI6" s="95"/>
-      <c r="AJ6" s="95"/>
-      <c r="AK6" s="95"/>
-      <c r="AL6" s="95"/>
-      <c r="AM6" s="95"/>
-      <c r="AN6" s="95"/>
-      <c r="AO6" s="95"/>
-      <c r="AP6" s="95"/>
-      <c r="AQ6" s="95"/>
-      <c r="AR6" s="95"/>
-      <c r="AS6" s="95"/>
-      <c r="AT6" s="95"/>
-      <c r="AU6" s="95"/>
-      <c r="AV6" s="95"/>
-      <c r="AW6" s="95"/>
-      <c r="AX6" s="95"/>
-      <c r="AY6" s="95"/>
-      <c r="AZ6" s="95"/>
-      <c r="BA6" s="95"/>
-      <c r="BB6" s="96"/>
+        <v>-1</v>
+      </c>
+      <c r="F6" s="90"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="91"/>
+      <c r="L6" s="91"/>
+      <c r="M6" s="91"/>
+      <c r="N6" s="91"/>
+      <c r="O6" s="91"/>
+      <c r="P6" s="91"/>
+      <c r="Q6" s="91"/>
+      <c r="R6" s="91"/>
+      <c r="S6" s="91"/>
+      <c r="T6" s="91"/>
+      <c r="U6" s="91"/>
+      <c r="V6" s="91"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="91"/>
+      <c r="Y6" s="91"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="91"/>
+      <c r="AC6" s="91"/>
+      <c r="AD6" s="91"/>
+      <c r="AE6" s="91"/>
+      <c r="AF6" s="91"/>
+      <c r="AG6" s="91"/>
+      <c r="AH6" s="91"/>
+      <c r="AI6" s="91"/>
+      <c r="AJ6" s="91"/>
+      <c r="AK6" s="91"/>
+      <c r="AL6" s="91"/>
+      <c r="AM6" s="91"/>
+      <c r="AN6" s="91"/>
+      <c r="AO6" s="91"/>
+      <c r="AP6" s="91"/>
+      <c r="AQ6" s="91"/>
+      <c r="AR6" s="91"/>
+      <c r="AS6" s="91"/>
+      <c r="AT6" s="91"/>
+      <c r="AU6" s="91"/>
+      <c r="AV6" s="91"/>
+      <c r="AW6" s="91"/>
+      <c r="AX6" s="91"/>
+      <c r="AY6" s="91"/>
+      <c r="AZ6" s="91"/>
+      <c r="BA6" s="91"/>
+      <c r="BB6" s="92"/>
     </row>
     <row r="7" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="97" t="b">
+      <c r="A7" s="93" t="b">
         <v>1</v>
       </c>
-      <c r="B7" s="99" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="101">
+      <c r="B7" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="97">
         <f>SUM(F7:BB7)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="103">
+      <c r="D7" s="99">
         <f>SUM(F8:BB8)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="105">
+      <c r="E7" s="101">
         <f>(AVERAGE(C7,C8)-AVERAGE(D7,D8) )</f>
         <v>0</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="63">
         <v>1</v>
       </c>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
       <c r="J7" s="26"/>
       <c r="K7" s="25"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="57"/>
       <c r="O7" s="26"/>
       <c r="P7" s="25"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
       <c r="T7" s="26"/>
       <c r="U7" s="25"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
+      <c r="V7" s="57"/>
+      <c r="W7" s="57"/>
+      <c r="X7" s="57"/>
       <c r="Y7" s="26"/>
       <c r="Z7" s="25"/>
-      <c r="AA7" s="58"/>
-      <c r="AB7" s="58"/>
-      <c r="AC7" s="58"/>
+      <c r="AA7" s="57"/>
+      <c r="AB7" s="57"/>
+      <c r="AC7" s="57"/>
       <c r="AD7" s="26"/>
       <c r="AE7" s="25"/>
-      <c r="AF7" s="58"/>
-      <c r="AG7" s="58"/>
-      <c r="AH7" s="58"/>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="57"/>
+      <c r="AH7" s="57"/>
       <c r="AI7" s="26"/>
       <c r="AJ7" s="25"/>
-      <c r="AK7" s="58"/>
-      <c r="AL7" s="58"/>
-      <c r="AM7" s="58"/>
+      <c r="AK7" s="57"/>
+      <c r="AL7" s="57"/>
+      <c r="AM7" s="57"/>
       <c r="AN7" s="26"/>
       <c r="AO7" s="25"/>
-      <c r="AP7" s="58"/>
-      <c r="AQ7" s="58"/>
-      <c r="AR7" s="58"/>
+      <c r="AP7" s="57"/>
+      <c r="AQ7" s="57"/>
+      <c r="AR7" s="57"/>
       <c r="AS7" s="26"/>
       <c r="AT7" s="25"/>
-      <c r="AU7" s="58"/>
+      <c r="AU7" s="57"/>
       <c r="AV7" s="25"/>
-      <c r="AW7" s="58"/>
-      <c r="AX7" s="58"/>
-      <c r="AY7" s="58"/>
+      <c r="AW7" s="57"/>
+      <c r="AX7" s="57"/>
+      <c r="AY7" s="57"/>
       <c r="AZ7" s="26"/>
       <c r="BA7" s="38"/>
       <c r="BB7" s="40"/>
     </row>
     <row r="8" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="98"/>
-      <c r="B8" s="100"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="284">
+      <c r="A8" s="94"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="78">
         <v>1</v>
       </c>
       <c r="G8" s="28"/>
@@ -3157,30 +3147,30 @@
       <c r="BB8" s="29"/>
     </row>
     <row r="9" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="109" t="b">
+      <c r="A9" s="112" t="b">
         <v>1</v>
       </c>
-      <c r="B9" s="110" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="111">
+      <c r="B9" s="113" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="114">
         <f>SUM(F9:BB9)</f>
         <v>0.5</v>
       </c>
-      <c r="D9" s="111">
+      <c r="D9" s="114">
         <f>SUM(F10:BB10)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="115">
+        <f>(AVERAGE(C9,C10)-AVERAGE(D9,D10) )</f>
+        <v>-1</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="65">
         <v>0.5</v>
       </c>
-      <c r="E9" s="112">
-        <f>(AVERAGE(C9,C10)-AVERAGE(D9,D10) )</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="66">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
       <c r="J9" s="26"/>
       <c r="K9" s="30"/>
       <c r="L9" s="31"/>
@@ -3188,9 +3178,9 @@
       <c r="N9" s="31"/>
       <c r="O9" s="32"/>
       <c r="P9" s="25"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
+      <c r="Q9" s="57"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="57"/>
       <c r="T9" s="26"/>
       <c r="U9" s="30"/>
       <c r="V9" s="31"/>
@@ -3228,20 +3218,22 @@
       <c r="BB9" s="32"/>
     </row>
     <row r="10" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="98"/>
-      <c r="B10" s="100"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="106"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="96"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="102"/>
       <c r="F10" s="28"/>
-      <c r="G10" s="285">
+      <c r="G10" s="79">
         <v>0.5</v>
       </c>
       <c r="H10" s="28"/>
       <c r="I10" s="28"/>
       <c r="J10" s="29"/>
       <c r="K10" s="27"/>
-      <c r="L10" s="28"/>
+      <c r="L10" s="28">
+        <v>1</v>
+      </c>
       <c r="M10" s="28"/>
       <c r="N10" s="28"/>
       <c r="O10" s="29"/>
@@ -3286,30 +3278,30 @@
       <c r="BB10" s="29"/>
     </row>
     <row r="11" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="109" t="b">
+      <c r="A11" s="112" t="b">
         <v>1</v>
       </c>
-      <c r="B11" s="110" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="111">
+      <c r="B11" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="114">
         <f>SUM(F11:BB11)</f>
         <v>0.5</v>
       </c>
-      <c r="D11" s="111">
+      <c r="D11" s="114">
         <f>SUM(F12:BB12)</f>
         <v>0.5</v>
       </c>
-      <c r="E11" s="112">
+      <c r="E11" s="115">
         <f>(AVERAGE(C11,C12)-AVERAGE(D11,D12) )</f>
         <v>0</v>
       </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="66">
+      <c r="F11" s="57"/>
+      <c r="G11" s="65">
         <v>0.5</v>
       </c>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
       <c r="J11" s="26"/>
       <c r="K11" s="30"/>
       <c r="L11" s="31"/>
@@ -3317,9 +3309,9 @@
       <c r="N11" s="31"/>
       <c r="O11" s="32"/>
       <c r="P11" s="25"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
       <c r="T11" s="26"/>
       <c r="U11" s="30"/>
       <c r="V11" s="31"/>
@@ -3357,13 +3349,13 @@
       <c r="BB11" s="32"/>
     </row>
     <row r="12" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="98"/>
-      <c r="B12" s="100"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="106"/>
+      <c r="A12" s="94"/>
+      <c r="B12" s="96"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="102"/>
       <c r="F12" s="28"/>
-      <c r="G12" s="285">
+      <c r="G12" s="79">
         <v>0.5</v>
       </c>
       <c r="H12" s="28"/>
@@ -3415,32 +3407,32 @@
       <c r="BB12" s="29"/>
     </row>
     <row r="13" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="109" t="b">
+      <c r="A13" s="112" t="b">
         <v>1</v>
       </c>
-      <c r="B13" s="110" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="111">
+      <c r="B13" s="113" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="114">
         <f>SUM(F13:BB13)</f>
         <v>2.5</v>
       </c>
-      <c r="D13" s="111">
+      <c r="D13" s="114">
         <f>SUM(F14:BB14)</f>
         <v>2.5</v>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="115">
         <f>(AVERAGE(C13,C14)-AVERAGE(D13,D14) )</f>
         <v>0</v>
       </c>
       <c r="F13" s="25"/>
-      <c r="G13" s="66">
+      <c r="G13" s="65">
         <v>0.5</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="65">
         <v>1.5</v>
       </c>
-      <c r="I13" s="66">
+      <c r="I13" s="65">
         <v>0.5</v>
       </c>
       <c r="J13" s="26"/>
@@ -3450,9 +3442,9 @@
       <c r="N13" s="31"/>
       <c r="O13" s="32"/>
       <c r="P13" s="25"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
+      <c r="Q13" s="57"/>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
       <c r="T13" s="26"/>
       <c r="U13" s="30"/>
       <c r="V13" s="31"/>
@@ -3490,19 +3482,19 @@
       <c r="BB13" s="32"/>
     </row>
     <row r="14" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="98"/>
-      <c r="B14" s="100"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="106"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="96"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="102"/>
       <c r="F14" s="27"/>
-      <c r="G14" s="285">
+      <c r="G14" s="79">
         <v>0.5</v>
       </c>
-      <c r="H14" s="285">
+      <c r="H14" s="79">
         <v>1.5</v>
       </c>
-      <c r="I14" s="285">
+      <c r="I14" s="79">
         <v>0.5</v>
       </c>
       <c r="J14" s="29"/>
@@ -3552,211 +3544,211 @@
       <c r="BB14" s="29"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="123" t="b">
+      <c r="A15" s="126" t="b">
         <v>1</v>
       </c>
-      <c r="B15" s="125" t="s">
+      <c r="B15" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="127">
+      <c r="C15" s="130">
         <f>SUM(C17:C20)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="127">
+      <c r="D15" s="130">
         <f>SUM(D17:D20)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E15" s="132">
+        <f>(C15-D15)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="F15" s="116"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="117"/>
+      <c r="W15" s="117"/>
+      <c r="X15" s="117"/>
+      <c r="Y15" s="117"/>
+      <c r="Z15" s="117"/>
+      <c r="AA15" s="117"/>
+      <c r="AB15" s="117"/>
+      <c r="AC15" s="117"/>
+      <c r="AD15" s="117"/>
+      <c r="AE15" s="117"/>
+      <c r="AF15" s="117"/>
+      <c r="AG15" s="117"/>
+      <c r="AH15" s="117"/>
+      <c r="AI15" s="117"/>
+      <c r="AJ15" s="117"/>
+      <c r="AK15" s="117"/>
+      <c r="AL15" s="117"/>
+      <c r="AM15" s="117"/>
+      <c r="AN15" s="117"/>
+      <c r="AO15" s="117"/>
+      <c r="AP15" s="117"/>
+      <c r="AQ15" s="117"/>
+      <c r="AR15" s="117"/>
+      <c r="AS15" s="117"/>
+      <c r="AT15" s="117"/>
+      <c r="AU15" s="117"/>
+      <c r="AV15" s="117"/>
+      <c r="AW15" s="117"/>
+      <c r="AX15" s="117"/>
+      <c r="AY15" s="117"/>
+      <c r="AZ15" s="117"/>
+      <c r="BA15" s="117"/>
+      <c r="BB15" s="118"/>
+    </row>
+    <row r="16" spans="1:54" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="127"/>
+      <c r="B16" s="129"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="120"/>
+      <c r="U16" s="120"/>
+      <c r="V16" s="120"/>
+      <c r="W16" s="120"/>
+      <c r="X16" s="120"/>
+      <c r="Y16" s="120"/>
+      <c r="Z16" s="120"/>
+      <c r="AA16" s="120"/>
+      <c r="AB16" s="120"/>
+      <c r="AC16" s="120"/>
+      <c r="AD16" s="120"/>
+      <c r="AE16" s="120"/>
+      <c r="AF16" s="120"/>
+      <c r="AG16" s="120"/>
+      <c r="AH16" s="120"/>
+      <c r="AI16" s="120"/>
+      <c r="AJ16" s="120"/>
+      <c r="AK16" s="120"/>
+      <c r="AL16" s="120"/>
+      <c r="AM16" s="120"/>
+      <c r="AN16" s="120"/>
+      <c r="AO16" s="120"/>
+      <c r="AP16" s="120"/>
+      <c r="AQ16" s="120"/>
+      <c r="AR16" s="120"/>
+      <c r="AS16" s="120"/>
+      <c r="AT16" s="120"/>
+      <c r="AU16" s="120"/>
+      <c r="AV16" s="120"/>
+      <c r="AW16" s="120"/>
+      <c r="AX16" s="120"/>
+      <c r="AY16" s="120"/>
+      <c r="AZ16" s="120"/>
+      <c r="BA16" s="120"/>
+      <c r="BB16" s="121"/>
+    </row>
+    <row r="17" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="122" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="129">
-        <f>(C15-D15)</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="113"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="114"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
-      <c r="S15" s="114"/>
-      <c r="T15" s="114"/>
-      <c r="U15" s="114"/>
-      <c r="V15" s="114"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="114"/>
-      <c r="Y15" s="114"/>
-      <c r="Z15" s="114"/>
-      <c r="AA15" s="114"/>
-      <c r="AB15" s="114"/>
-      <c r="AC15" s="114"/>
-      <c r="AD15" s="114"/>
-      <c r="AE15" s="114"/>
-      <c r="AF15" s="114"/>
-      <c r="AG15" s="114"/>
-      <c r="AH15" s="114"/>
-      <c r="AI15" s="114"/>
-      <c r="AJ15" s="114"/>
-      <c r="AK15" s="114"/>
-      <c r="AL15" s="114"/>
-      <c r="AM15" s="114"/>
-      <c r="AN15" s="114"/>
-      <c r="AO15" s="114"/>
-      <c r="AP15" s="114"/>
-      <c r="AQ15" s="114"/>
-      <c r="AR15" s="114"/>
-      <c r="AS15" s="114"/>
-      <c r="AT15" s="114"/>
-      <c r="AU15" s="114"/>
-      <c r="AV15" s="114"/>
-      <c r="AW15" s="114"/>
-      <c r="AX15" s="114"/>
-      <c r="AY15" s="114"/>
-      <c r="AZ15" s="114"/>
-      <c r="BA15" s="114"/>
-      <c r="BB15" s="115"/>
-    </row>
-    <row r="16" spans="1:54" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="124"/>
-      <c r="B16" s="126"/>
-      <c r="C16" s="128"/>
-      <c r="D16" s="128"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="117"/>
-      <c r="M16" s="117"/>
-      <c r="N16" s="117"/>
-      <c r="O16" s="117"/>
-      <c r="P16" s="117"/>
-      <c r="Q16" s="117"/>
-      <c r="R16" s="117"/>
-      <c r="S16" s="117"/>
-      <c r="T16" s="117"/>
-      <c r="U16" s="117"/>
-      <c r="V16" s="117"/>
-      <c r="W16" s="117"/>
-      <c r="X16" s="117"/>
-      <c r="Y16" s="117"/>
-      <c r="Z16" s="117"/>
-      <c r="AA16" s="117"/>
-      <c r="AB16" s="117"/>
-      <c r="AC16" s="117"/>
-      <c r="AD16" s="117"/>
-      <c r="AE16" s="117"/>
-      <c r="AF16" s="117"/>
-      <c r="AG16" s="117"/>
-      <c r="AH16" s="117"/>
-      <c r="AI16" s="117"/>
-      <c r="AJ16" s="117"/>
-      <c r="AK16" s="117"/>
-      <c r="AL16" s="117"/>
-      <c r="AM16" s="117"/>
-      <c r="AN16" s="117"/>
-      <c r="AO16" s="117"/>
-      <c r="AP16" s="117"/>
-      <c r="AQ16" s="117"/>
-      <c r="AR16" s="117"/>
-      <c r="AS16" s="117"/>
-      <c r="AT16" s="117"/>
-      <c r="AU16" s="117"/>
-      <c r="AV16" s="117"/>
-      <c r="AW16" s="117"/>
-      <c r="AX16" s="117"/>
-      <c r="AY16" s="117"/>
-      <c r="AZ16" s="117"/>
-      <c r="BA16" s="117"/>
-      <c r="BB16" s="118"/>
-    </row>
-    <row r="17" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="119" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" s="121" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="111">
+      <c r="B17" s="124" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="114">
         <f>SUM(F17:BB17)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="111">
+      <c r="D17" s="114">
         <f>SUM(F18:BB18)</f>
         <v>0.5</v>
       </c>
-      <c r="E17" s="105">
+      <c r="E17" s="101">
         <f>(AVERAGE(C17,C18)-AVERAGE(D17,D18) )</f>
         <v>0</v>
       </c>
       <c r="F17" s="25"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="66">
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="65">
         <v>0.5</v>
       </c>
       <c r="J17" s="26"/>
       <c r="K17" s="25"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
+      <c r="L17" s="57"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="57"/>
       <c r="O17" s="26"/>
       <c r="P17" s="25"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
+      <c r="Q17" s="57"/>
+      <c r="R17" s="57"/>
+      <c r="S17" s="57"/>
       <c r="T17" s="26"/>
       <c r="U17" s="25"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="58"/>
+      <c r="V17" s="57"/>
+      <c r="W17" s="57"/>
+      <c r="X17" s="57"/>
       <c r="Y17" s="26"/>
       <c r="Z17" s="25"/>
-      <c r="AA17" s="58"/>
-      <c r="AB17" s="58"/>
-      <c r="AC17" s="58"/>
+      <c r="AA17" s="57"/>
+      <c r="AB17" s="57"/>
+      <c r="AC17" s="57"/>
       <c r="AD17" s="26"/>
       <c r="AE17" s="25"/>
-      <c r="AF17" s="58"/>
-      <c r="AG17" s="58"/>
-      <c r="AH17" s="58"/>
+      <c r="AF17" s="57"/>
+      <c r="AG17" s="57"/>
+      <c r="AH17" s="57"/>
       <c r="AI17" s="26"/>
       <c r="AJ17" s="25"/>
-      <c r="AK17" s="58"/>
-      <c r="AL17" s="58"/>
-      <c r="AM17" s="58"/>
+      <c r="AK17" s="57"/>
+      <c r="AL17" s="57"/>
+      <c r="AM17" s="57"/>
       <c r="AN17" s="26"/>
       <c r="AO17" s="25"/>
-      <c r="AP17" s="58"/>
-      <c r="AQ17" s="58"/>
-      <c r="AR17" s="58"/>
+      <c r="AP17" s="57"/>
+      <c r="AQ17" s="57"/>
+      <c r="AR17" s="57"/>
       <c r="AS17" s="26"/>
       <c r="AT17" s="25"/>
-      <c r="AU17" s="58"/>
+      <c r="AU17" s="57"/>
       <c r="AV17" s="25"/>
-      <c r="AW17" s="58"/>
-      <c r="AX17" s="58"/>
-      <c r="AY17" s="58"/>
+      <c r="AW17" s="57"/>
+      <c r="AX17" s="57"/>
+      <c r="AY17" s="57"/>
       <c r="AZ17" s="26"/>
       <c r="BA17" s="25"/>
       <c r="BB17" s="26"/>
     </row>
     <row r="18" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="120"/>
-      <c r="B18" s="122"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="106"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="125"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="102"/>
       <c r="F18" s="27"/>
       <c r="G18" s="28"/>
       <c r="H18" s="28"/>
-      <c r="I18" s="285">
+      <c r="I18" s="79">
         <v>0.5</v>
       </c>
       <c r="J18" s="29"/>
@@ -3806,28 +3798,28 @@
       <c r="BB18" s="29"/>
     </row>
     <row r="19" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141" t="b">
+      <c r="A19" s="144" t="b">
         <v>1</v>
       </c>
-      <c r="B19" s="287" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="111">
+      <c r="B19" s="145" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="114">
         <f>SUM(F19:BB19)</f>
         <v>0.5</v>
       </c>
-      <c r="D19" s="111">
+      <c r="D19" s="114">
         <f>SUM(F20:BB20)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E19" s="112">
+        <v>1</v>
+      </c>
+      <c r="E19" s="115">
         <f>(AVERAGE(C19,C20)-AVERAGE(D19,D20) )</f>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="F19" s="30"/>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
-      <c r="I19" s="70">
+      <c r="I19" s="69">
         <v>0.5</v>
       </c>
       <c r="J19" s="32"/>
@@ -3837,9 +3829,9 @@
       <c r="N19" s="31"/>
       <c r="O19" s="32"/>
       <c r="P19" s="25"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
+      <c r="Q19" s="57"/>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
       <c r="T19" s="26"/>
       <c r="U19" s="30"/>
       <c r="V19" s="31"/>
@@ -3877,22 +3869,24 @@
       <c r="BB19" s="32"/>
     </row>
     <row r="20" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A20" s="120"/>
-      <c r="B20" s="142"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="143"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="146"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="147"/>
       <c r="F20" s="25"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="286">
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="80">
         <v>0.5</v>
       </c>
       <c r="J20" s="26"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
+      <c r="K20" s="25">
+        <v>0.5</v>
+      </c>
+      <c r="L20" s="57"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="57"/>
       <c r="O20" s="26"/>
       <c r="P20" s="27"/>
       <c r="Q20" s="28"/>
@@ -3900,244 +3894,244 @@
       <c r="S20" s="28"/>
       <c r="T20" s="29"/>
       <c r="U20" s="25"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="58"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="57"/>
+      <c r="X20" s="57"/>
       <c r="Y20" s="26"/>
       <c r="Z20" s="25"/>
-      <c r="AA20" s="58"/>
-      <c r="AB20" s="58"/>
-      <c r="AC20" s="58"/>
+      <c r="AA20" s="57"/>
+      <c r="AB20" s="57"/>
+      <c r="AC20" s="57"/>
       <c r="AD20" s="26"/>
       <c r="AE20" s="25"/>
-      <c r="AF20" s="58"/>
-      <c r="AG20" s="58"/>
-      <c r="AH20" s="58"/>
+      <c r="AF20" s="57"/>
+      <c r="AG20" s="57"/>
+      <c r="AH20" s="57"/>
       <c r="AI20" s="26"/>
       <c r="AJ20" s="25"/>
-      <c r="AK20" s="58"/>
-      <c r="AL20" s="58"/>
-      <c r="AM20" s="58"/>
+      <c r="AK20" s="57"/>
+      <c r="AL20" s="57"/>
+      <c r="AM20" s="57"/>
       <c r="AN20" s="26"/>
       <c r="AO20" s="25"/>
-      <c r="AP20" s="58"/>
-      <c r="AQ20" s="58"/>
-      <c r="AR20" s="58"/>
+      <c r="AP20" s="57"/>
+      <c r="AQ20" s="57"/>
+      <c r="AR20" s="57"/>
       <c r="AS20" s="26"/>
       <c r="AT20" s="25"/>
-      <c r="AU20" s="58"/>
+      <c r="AU20" s="57"/>
       <c r="AV20" s="25"/>
-      <c r="AW20" s="58"/>
-      <c r="AX20" s="58"/>
-      <c r="AY20" s="58"/>
+      <c r="AW20" s="57"/>
+      <c r="AX20" s="57"/>
+      <c r="AY20" s="57"/>
       <c r="AZ20" s="26"/>
       <c r="BA20" s="25"/>
       <c r="BB20" s="26"/>
     </row>
     <row r="21" spans="1:54" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="144" t="b">
-        <v>0</v>
-      </c>
-      <c r="B21" s="146" t="s">
+      <c r="A21" s="148" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" s="150" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="148">
+      <c r="C21" s="152">
         <f>SUM(C23:C28)</f>
         <v>3</v>
       </c>
-      <c r="D21" s="148">
+      <c r="D21" s="152">
         <f>SUM(D23:D28)</f>
-        <v>2.5</v>
-      </c>
-      <c r="E21" s="150">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="154">
         <f>(C21-D21)</f>
-        <v>0.5</v>
-      </c>
-      <c r="F21" s="131"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="132"/>
-      <c r="I21" s="132"/>
-      <c r="J21" s="132"/>
-      <c r="K21" s="132"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="132"/>
-      <c r="N21" s="132"/>
-      <c r="O21" s="132"/>
-      <c r="P21" s="132"/>
-      <c r="Q21" s="132"/>
-      <c r="R21" s="132"/>
-      <c r="S21" s="132"/>
-      <c r="T21" s="132"/>
-      <c r="U21" s="132"/>
-      <c r="V21" s="132"/>
-      <c r="W21" s="132"/>
-      <c r="X21" s="132"/>
-      <c r="Y21" s="132"/>
-      <c r="Z21" s="132"/>
-      <c r="AA21" s="132"/>
-      <c r="AB21" s="132"/>
-      <c r="AC21" s="132"/>
-      <c r="AD21" s="132"/>
-      <c r="AE21" s="132"/>
-      <c r="AF21" s="132"/>
-      <c r="AG21" s="132"/>
-      <c r="AH21" s="132"/>
-      <c r="AI21" s="132"/>
-      <c r="AJ21" s="132"/>
-      <c r="AK21" s="132"/>
-      <c r="AL21" s="132"/>
-      <c r="AM21" s="132"/>
-      <c r="AN21" s="132"/>
-      <c r="AO21" s="132"/>
-      <c r="AP21" s="132"/>
-      <c r="AQ21" s="132"/>
-      <c r="AR21" s="132"/>
-      <c r="AS21" s="132"/>
-      <c r="AT21" s="132"/>
-      <c r="AU21" s="132"/>
-      <c r="AV21" s="132"/>
-      <c r="AW21" s="132"/>
-      <c r="AX21" s="132"/>
-      <c r="AY21" s="132"/>
-      <c r="AZ21" s="132"/>
-      <c r="BA21" s="132"/>
-      <c r="BB21" s="133"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F21" s="134"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="135"/>
+      <c r="J21" s="135"/>
+      <c r="K21" s="135"/>
+      <c r="L21" s="135"/>
+      <c r="M21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="135"/>
+      <c r="R21" s="135"/>
+      <c r="S21" s="135"/>
+      <c r="T21" s="135"/>
+      <c r="U21" s="135"/>
+      <c r="V21" s="135"/>
+      <c r="W21" s="135"/>
+      <c r="X21" s="135"/>
+      <c r="Y21" s="135"/>
+      <c r="Z21" s="135"/>
+      <c r="AA21" s="135"/>
+      <c r="AB21" s="135"/>
+      <c r="AC21" s="135"/>
+      <c r="AD21" s="135"/>
+      <c r="AE21" s="135"/>
+      <c r="AF21" s="135"/>
+      <c r="AG21" s="135"/>
+      <c r="AH21" s="135"/>
+      <c r="AI21" s="135"/>
+      <c r="AJ21" s="135"/>
+      <c r="AK21" s="135"/>
+      <c r="AL21" s="135"/>
+      <c r="AM21" s="135"/>
+      <c r="AN21" s="135"/>
+      <c r="AO21" s="135"/>
+      <c r="AP21" s="135"/>
+      <c r="AQ21" s="135"/>
+      <c r="AR21" s="135"/>
+      <c r="AS21" s="135"/>
+      <c r="AT21" s="135"/>
+      <c r="AU21" s="135"/>
+      <c r="AV21" s="135"/>
+      <c r="AW21" s="135"/>
+      <c r="AX21" s="135"/>
+      <c r="AY21" s="135"/>
+      <c r="AZ21" s="135"/>
+      <c r="BA21" s="135"/>
+      <c r="BB21" s="136"/>
     </row>
     <row r="22" spans="1:54" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="145"/>
-      <c r="B22" s="147"/>
-      <c r="C22" s="149"/>
-      <c r="D22" s="149"/>
-      <c r="E22" s="151"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="135"/>
-      <c r="H22" s="135"/>
-      <c r="I22" s="135"/>
-      <c r="J22" s="135"/>
-      <c r="K22" s="135"/>
-      <c r="L22" s="135"/>
-      <c r="M22" s="135"/>
-      <c r="N22" s="135"/>
-      <c r="O22" s="135"/>
-      <c r="P22" s="135"/>
-      <c r="Q22" s="135"/>
-      <c r="R22" s="135"/>
-      <c r="S22" s="135"/>
-      <c r="T22" s="135"/>
-      <c r="U22" s="135"/>
-      <c r="V22" s="135"/>
-      <c r="W22" s="135"/>
-      <c r="X22" s="135"/>
-      <c r="Y22" s="135"/>
-      <c r="Z22" s="135"/>
-      <c r="AA22" s="135"/>
-      <c r="AB22" s="135"/>
-      <c r="AC22" s="135"/>
-      <c r="AD22" s="135"/>
-      <c r="AE22" s="135"/>
-      <c r="AF22" s="135"/>
-      <c r="AG22" s="135"/>
-      <c r="AH22" s="135"/>
-      <c r="AI22" s="135"/>
-      <c r="AJ22" s="135"/>
-      <c r="AK22" s="135"/>
-      <c r="AL22" s="135"/>
-      <c r="AM22" s="135"/>
-      <c r="AN22" s="135"/>
-      <c r="AO22" s="135"/>
-      <c r="AP22" s="135"/>
-      <c r="AQ22" s="135"/>
-      <c r="AR22" s="135"/>
-      <c r="AS22" s="135"/>
-      <c r="AT22" s="135"/>
-      <c r="AU22" s="135"/>
-      <c r="AV22" s="135"/>
-      <c r="AW22" s="135"/>
-      <c r="AX22" s="135"/>
-      <c r="AY22" s="135"/>
-      <c r="AZ22" s="135"/>
-      <c r="BA22" s="135"/>
-      <c r="BB22" s="136"/>
+      <c r="A22" s="149"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="138"/>
+      <c r="N22" s="138"/>
+      <c r="O22" s="138"/>
+      <c r="P22" s="138"/>
+      <c r="Q22" s="138"/>
+      <c r="R22" s="138"/>
+      <c r="S22" s="138"/>
+      <c r="T22" s="138"/>
+      <c r="U22" s="138"/>
+      <c r="V22" s="138"/>
+      <c r="W22" s="138"/>
+      <c r="X22" s="138"/>
+      <c r="Y22" s="138"/>
+      <c r="Z22" s="138"/>
+      <c r="AA22" s="138"/>
+      <c r="AB22" s="138"/>
+      <c r="AC22" s="138"/>
+      <c r="AD22" s="138"/>
+      <c r="AE22" s="138"/>
+      <c r="AF22" s="138"/>
+      <c r="AG22" s="138"/>
+      <c r="AH22" s="138"/>
+      <c r="AI22" s="138"/>
+      <c r="AJ22" s="138"/>
+      <c r="AK22" s="138"/>
+      <c r="AL22" s="138"/>
+      <c r="AM22" s="138"/>
+      <c r="AN22" s="138"/>
+      <c r="AO22" s="138"/>
+      <c r="AP22" s="138"/>
+      <c r="AQ22" s="138"/>
+      <c r="AR22" s="138"/>
+      <c r="AS22" s="138"/>
+      <c r="AT22" s="138"/>
+      <c r="AU22" s="138"/>
+      <c r="AV22" s="138"/>
+      <c r="AW22" s="138"/>
+      <c r="AX22" s="138"/>
+      <c r="AY22" s="138"/>
+      <c r="AZ22" s="138"/>
+      <c r="BA22" s="138"/>
+      <c r="BB22" s="139"/>
     </row>
     <row r="23" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="137" t="b">
+      <c r="A23" s="140" t="b">
         <v>1</v>
       </c>
-      <c r="B23" s="139" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="111">
+      <c r="B23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="114">
         <f>SUM(F23:BB23)</f>
         <v>1</v>
       </c>
-      <c r="D23" s="111">
+      <c r="D23" s="114">
         <f>SUM(F24:BB24)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E23" s="101">
+        <f>(AVERAGE(C23,C24)-AVERAGE(D23,D24) )</f>
+        <v>-0.5</v>
+      </c>
+      <c r="F23" s="33"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" s="63">
         <v>1</v>
       </c>
-      <c r="E23" s="105">
-        <f>(AVERAGE(C23,C24)-AVERAGE(D23,D24) )</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="33"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="K23" s="64">
-        <v>1</v>
-      </c>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
+      <c r="L23" s="57"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="57"/>
       <c r="O23" s="26"/>
       <c r="P23" s="25"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
+      <c r="Q23" s="57"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
       <c r="T23" s="26"/>
       <c r="U23" s="25"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="58"/>
+      <c r="V23" s="57"/>
+      <c r="W23" s="57"/>
+      <c r="X23" s="57"/>
       <c r="Y23" s="26"/>
       <c r="Z23" s="25"/>
-      <c r="AA23" s="58"/>
-      <c r="AB23" s="58"/>
-      <c r="AC23" s="58"/>
+      <c r="AA23" s="57"/>
+      <c r="AB23" s="57"/>
+      <c r="AC23" s="57"/>
       <c r="AD23" s="26"/>
       <c r="AE23" s="25"/>
-      <c r="AF23" s="58"/>
-      <c r="AG23" s="58"/>
-      <c r="AH23" s="58"/>
+      <c r="AF23" s="57"/>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="57"/>
       <c r="AI23" s="26"/>
       <c r="AJ23" s="25"/>
-      <c r="AK23" s="58"/>
-      <c r="AL23" s="58"/>
-      <c r="AM23" s="58"/>
+      <c r="AK23" s="57"/>
+      <c r="AL23" s="57"/>
+      <c r="AM23" s="57"/>
       <c r="AN23" s="26"/>
       <c r="AO23" s="25"/>
-      <c r="AP23" s="58"/>
-      <c r="AQ23" s="58"/>
-      <c r="AR23" s="58"/>
+      <c r="AP23" s="57"/>
+      <c r="AQ23" s="57"/>
+      <c r="AR23" s="57"/>
       <c r="AS23" s="26"/>
       <c r="AT23" s="25"/>
-      <c r="AU23" s="58"/>
+      <c r="AU23" s="57"/>
       <c r="AV23" s="25"/>
-      <c r="AW23" s="58"/>
-      <c r="AX23" s="58"/>
-      <c r="AY23" s="58"/>
+      <c r="AW23" s="57"/>
+      <c r="AX23" s="57"/>
+      <c r="AY23" s="57"/>
       <c r="AZ23" s="26"/>
       <c r="BA23" s="25"/>
       <c r="BB23" s="26"/>
     </row>
     <row r="24" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="138"/>
-      <c r="B24" s="140"/>
-      <c r="C24" s="102"/>
-      <c r="D24" s="102"/>
-      <c r="E24" s="106"/>
+      <c r="A24" s="141"/>
+      <c r="B24" s="143"/>
+      <c r="C24" s="98"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="102"/>
       <c r="F24" s="35"/>
       <c r="G24" s="36"/>
       <c r="H24" s="36"/>
@@ -4147,7 +4141,9 @@
         <v>1</v>
       </c>
       <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
+      <c r="M24" s="28">
+        <v>0.5</v>
+      </c>
       <c r="N24" s="28"/>
       <c r="O24" s="29"/>
       <c r="P24" s="27"/>
@@ -4191,70 +4187,70 @@
       <c r="BB24" s="29"/>
     </row>
     <row r="25" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="166" t="b">
-        <v>0</v>
-      </c>
-      <c r="B25" s="167" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="111">
+      <c r="A25" s="170" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" s="171" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="114">
         <f>SUM(F25:BB25)</f>
         <v>1</v>
       </c>
-      <c r="D25" s="111">
+      <c r="D25" s="114">
         <f>SUM(F26:BB26)</f>
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="112">
+        <v>1</v>
+      </c>
+      <c r="E25" s="115">
         <f>(AVERAGE(C25,C26)-AVERAGE(D25,D26) )</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F25" s="33"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
       <c r="J25" s="34"/>
-      <c r="K25" s="71">
+      <c r="K25" s="70">
         <v>1</v>
       </c>
-      <c r="L25" s="58"/>
+      <c r="L25" s="57"/>
       <c r="M25" s="31"/>
       <c r="N25" s="31"/>
       <c r="O25" s="32"/>
       <c r="P25" s="25"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
       <c r="T25" s="26"/>
       <c r="U25" s="30"/>
-      <c r="V25" s="58"/>
+      <c r="V25" s="57"/>
       <c r="W25" s="31"/>
       <c r="X25" s="31"/>
       <c r="Y25" s="32"/>
       <c r="Z25" s="30"/>
-      <c r="AA25" s="58"/>
+      <c r="AA25" s="57"/>
       <c r="AB25" s="31"/>
       <c r="AC25" s="31"/>
       <c r="AD25" s="32"/>
       <c r="AE25" s="30"/>
-      <c r="AF25" s="58"/>
+      <c r="AF25" s="57"/>
       <c r="AG25" s="31"/>
       <c r="AH25" s="31"/>
       <c r="AI25" s="32"/>
       <c r="AJ25" s="30"/>
-      <c r="AK25" s="58"/>
+      <c r="AK25" s="57"/>
       <c r="AL25" s="31"/>
       <c r="AM25" s="31"/>
       <c r="AN25" s="32"/>
       <c r="AO25" s="30"/>
-      <c r="AP25" s="58"/>
+      <c r="AP25" s="57"/>
       <c r="AQ25" s="31"/>
       <c r="AR25" s="31"/>
       <c r="AS25" s="32"/>
       <c r="AT25" s="30"/>
-      <c r="AU25" s="58"/>
+      <c r="AU25" s="57"/>
       <c r="AV25" s="30"/>
-      <c r="AW25" s="58"/>
+      <c r="AW25" s="57"/>
       <c r="AX25" s="31"/>
       <c r="AY25" s="31"/>
       <c r="AZ25" s="32"/>
@@ -4262,21 +4258,21 @@
       <c r="BB25" s="26"/>
     </row>
     <row r="26" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="138"/>
-      <c r="B26" s="140"/>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="106"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="143"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="102"/>
       <c r="F26" s="35"/>
       <c r="G26" s="36"/>
       <c r="H26" s="36"/>
       <c r="I26" s="36"/>
       <c r="J26" s="37"/>
       <c r="K26" s="27">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L26" s="28">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
@@ -4322,40 +4318,40 @@
       <c r="BB26" s="29"/>
     </row>
     <row r="27" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="166" t="b">
-        <v>0</v>
-      </c>
-      <c r="B27" s="167" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="111">
+      <c r="A27" s="170" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" s="171" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="114">
         <f>SUM(F27:BB27)</f>
         <v>1</v>
       </c>
-      <c r="D27" s="111">
+      <c r="D27" s="114">
         <f>SUM(F28:BB28)</f>
         <v>1</v>
       </c>
-      <c r="E27" s="112">
+      <c r="E27" s="115">
         <f>(AVERAGE(C27,C28)-AVERAGE(D27,D28) )</f>
         <v>0</v>
       </c>
       <c r="F27" s="33"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
       <c r="J27" s="34"/>
       <c r="K27" s="30"/>
-      <c r="L27" s="66">
+      <c r="L27" s="65">
         <v>1</v>
       </c>
       <c r="M27" s="31"/>
       <c r="N27" s="31"/>
       <c r="O27" s="32"/>
       <c r="P27" s="25"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
+      <c r="Q27" s="57"/>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
       <c r="T27" s="26"/>
       <c r="U27" s="30"/>
       <c r="V27" s="31"/>
@@ -4393,22 +4389,22 @@
       <c r="BB27" s="32"/>
     </row>
     <row r="28" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="138"/>
-      <c r="B28" s="140"/>
-      <c r="C28" s="102"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="143"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="143"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="147"/>
       <c r="F28" s="33"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
       <c r="J28" s="34"/>
       <c r="K28" s="25"/>
-      <c r="L28" s="58">
+      <c r="L28" s="57"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="57">
         <v>1</v>
       </c>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
       <c r="O28" s="26"/>
       <c r="P28" s="27"/>
       <c r="Q28" s="28"/>
@@ -4416,246 +4412,246 @@
       <c r="S28" s="28"/>
       <c r="T28" s="29"/>
       <c r="U28" s="25"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="58"/>
+      <c r="V28" s="57"/>
+      <c r="W28" s="57"/>
+      <c r="X28" s="57"/>
       <c r="Y28" s="26"/>
       <c r="Z28" s="25"/>
-      <c r="AA28" s="58"/>
-      <c r="AB28" s="58"/>
-      <c r="AC28" s="58"/>
+      <c r="AA28" s="57"/>
+      <c r="AB28" s="57"/>
+      <c r="AC28" s="57"/>
       <c r="AD28" s="26"/>
       <c r="AE28" s="25"/>
-      <c r="AF28" s="58"/>
-      <c r="AG28" s="58"/>
-      <c r="AH28" s="58"/>
+      <c r="AF28" s="57"/>
+      <c r="AG28" s="57"/>
+      <c r="AH28" s="57"/>
       <c r="AI28" s="26"/>
       <c r="AJ28" s="25"/>
-      <c r="AK28" s="58"/>
-      <c r="AL28" s="58"/>
-      <c r="AM28" s="58"/>
+      <c r="AK28" s="57"/>
+      <c r="AL28" s="57"/>
+      <c r="AM28" s="57"/>
       <c r="AN28" s="26"/>
       <c r="AO28" s="25"/>
-      <c r="AP28" s="58"/>
-      <c r="AQ28" s="58"/>
-      <c r="AR28" s="58"/>
+      <c r="AP28" s="57"/>
+      <c r="AQ28" s="57"/>
+      <c r="AR28" s="57"/>
       <c r="AS28" s="26"/>
       <c r="AT28" s="25"/>
-      <c r="AU28" s="58"/>
+      <c r="AU28" s="57"/>
       <c r="AV28" s="25"/>
-      <c r="AW28" s="58"/>
-      <c r="AX28" s="58"/>
-      <c r="AY28" s="58"/>
+      <c r="AW28" s="57"/>
+      <c r="AX28" s="57"/>
+      <c r="AY28" s="57"/>
       <c r="AZ28" s="26"/>
       <c r="BA28" s="25"/>
       <c r="BB28" s="26"/>
     </row>
     <row r="29" spans="1:54" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="152" t="b">
-        <v>0</v>
-      </c>
-      <c r="B29" s="154" t="s">
+      <c r="A29" s="156" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="156">
+      <c r="C29" s="160">
         <f>SUM(C31:C40)</f>
         <v>7.5</v>
       </c>
-      <c r="D29" s="156">
+      <c r="D29" s="160">
         <f>SUM(D31:D40)</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="158">
+        <v>7.83</v>
+      </c>
+      <c r="E29" s="162">
         <f>(C29-D29)</f>
-        <v>7.5</v>
-      </c>
-      <c r="F29" s="160"/>
-      <c r="G29" s="161"/>
-      <c r="H29" s="161"/>
-      <c r="I29" s="161"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="161"/>
-      <c r="L29" s="161"/>
-      <c r="M29" s="161"/>
-      <c r="N29" s="161"/>
-      <c r="O29" s="161"/>
-      <c r="P29" s="161"/>
-      <c r="Q29" s="161"/>
-      <c r="R29" s="161"/>
-      <c r="S29" s="161"/>
-      <c r="T29" s="161"/>
-      <c r="U29" s="161"/>
-      <c r="V29" s="161"/>
-      <c r="W29" s="161"/>
-      <c r="X29" s="161"/>
-      <c r="Y29" s="161"/>
-      <c r="Z29" s="161"/>
-      <c r="AA29" s="161"/>
-      <c r="AB29" s="161"/>
-      <c r="AC29" s="161"/>
-      <c r="AD29" s="161"/>
-      <c r="AE29" s="161"/>
-      <c r="AF29" s="161"/>
-      <c r="AG29" s="161"/>
-      <c r="AH29" s="161"/>
-      <c r="AI29" s="161"/>
-      <c r="AJ29" s="161"/>
-      <c r="AK29" s="161"/>
-      <c r="AL29" s="161"/>
-      <c r="AM29" s="161"/>
-      <c r="AN29" s="161"/>
-      <c r="AO29" s="161"/>
-      <c r="AP29" s="161"/>
-      <c r="AQ29" s="161"/>
-      <c r="AR29" s="161"/>
-      <c r="AS29" s="161"/>
-      <c r="AT29" s="161"/>
-      <c r="AU29" s="161"/>
-      <c r="AV29" s="161"/>
-      <c r="AW29" s="161"/>
-      <c r="AX29" s="161"/>
-      <c r="AY29" s="161"/>
-      <c r="AZ29" s="161"/>
-      <c r="BA29" s="161"/>
-      <c r="BB29" s="162"/>
+        <v>-0.33000000000000007</v>
+      </c>
+      <c r="F29" s="164"/>
+      <c r="G29" s="165"/>
+      <c r="H29" s="165"/>
+      <c r="I29" s="165"/>
+      <c r="J29" s="165"/>
+      <c r="K29" s="165"/>
+      <c r="L29" s="165"/>
+      <c r="M29" s="165"/>
+      <c r="N29" s="165"/>
+      <c r="O29" s="165"/>
+      <c r="P29" s="165"/>
+      <c r="Q29" s="165"/>
+      <c r="R29" s="165"/>
+      <c r="S29" s="165"/>
+      <c r="T29" s="165"/>
+      <c r="U29" s="165"/>
+      <c r="V29" s="165"/>
+      <c r="W29" s="165"/>
+      <c r="X29" s="165"/>
+      <c r="Y29" s="165"/>
+      <c r="Z29" s="165"/>
+      <c r="AA29" s="165"/>
+      <c r="AB29" s="165"/>
+      <c r="AC29" s="165"/>
+      <c r="AD29" s="165"/>
+      <c r="AE29" s="165"/>
+      <c r="AF29" s="165"/>
+      <c r="AG29" s="165"/>
+      <c r="AH29" s="165"/>
+      <c r="AI29" s="165"/>
+      <c r="AJ29" s="165"/>
+      <c r="AK29" s="165"/>
+      <c r="AL29" s="165"/>
+      <c r="AM29" s="165"/>
+      <c r="AN29" s="165"/>
+      <c r="AO29" s="165"/>
+      <c r="AP29" s="165"/>
+      <c r="AQ29" s="165"/>
+      <c r="AR29" s="165"/>
+      <c r="AS29" s="165"/>
+      <c r="AT29" s="165"/>
+      <c r="AU29" s="165"/>
+      <c r="AV29" s="165"/>
+      <c r="AW29" s="165"/>
+      <c r="AX29" s="165"/>
+      <c r="AY29" s="165"/>
+      <c r="AZ29" s="165"/>
+      <c r="BA29" s="165"/>
+      <c r="BB29" s="166"/>
     </row>
     <row r="30" spans="1:54" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A30" s="153"/>
-      <c r="B30" s="155"/>
-      <c r="C30" s="157"/>
-      <c r="D30" s="157"/>
-      <c r="E30" s="159"/>
-      <c r="F30" s="163"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="164"/>
-      <c r="I30" s="164"/>
-      <c r="J30" s="164"/>
-      <c r="K30" s="164"/>
-      <c r="L30" s="164"/>
-      <c r="M30" s="164"/>
-      <c r="N30" s="164"/>
-      <c r="O30" s="164"/>
-      <c r="P30" s="164"/>
-      <c r="Q30" s="164"/>
-      <c r="R30" s="164"/>
-      <c r="S30" s="164"/>
-      <c r="T30" s="164"/>
-      <c r="U30" s="164"/>
-      <c r="V30" s="164"/>
-      <c r="W30" s="164"/>
-      <c r="X30" s="164"/>
-      <c r="Y30" s="164"/>
-      <c r="Z30" s="164"/>
-      <c r="AA30" s="164"/>
-      <c r="AB30" s="164"/>
-      <c r="AC30" s="164"/>
-      <c r="AD30" s="164"/>
-      <c r="AE30" s="164"/>
-      <c r="AF30" s="164"/>
-      <c r="AG30" s="164"/>
-      <c r="AH30" s="164"/>
-      <c r="AI30" s="164"/>
-      <c r="AJ30" s="164"/>
-      <c r="AK30" s="164"/>
-      <c r="AL30" s="164"/>
-      <c r="AM30" s="164"/>
-      <c r="AN30" s="164"/>
-      <c r="AO30" s="164"/>
-      <c r="AP30" s="164"/>
-      <c r="AQ30" s="164"/>
-      <c r="AR30" s="164"/>
-      <c r="AS30" s="164"/>
-      <c r="AT30" s="164"/>
-      <c r="AU30" s="164"/>
-      <c r="AV30" s="164"/>
-      <c r="AW30" s="164"/>
-      <c r="AX30" s="164"/>
-      <c r="AY30" s="164"/>
-      <c r="AZ30" s="164"/>
-      <c r="BA30" s="164"/>
-      <c r="BB30" s="165"/>
+      <c r="A30" s="157"/>
+      <c r="B30" s="159"/>
+      <c r="C30" s="161"/>
+      <c r="D30" s="161"/>
+      <c r="E30" s="163"/>
+      <c r="F30" s="167"/>
+      <c r="G30" s="168"/>
+      <c r="H30" s="168"/>
+      <c r="I30" s="168"/>
+      <c r="J30" s="168"/>
+      <c r="K30" s="168"/>
+      <c r="L30" s="168"/>
+      <c r="M30" s="168"/>
+      <c r="N30" s="168"/>
+      <c r="O30" s="168"/>
+      <c r="P30" s="168"/>
+      <c r="Q30" s="168"/>
+      <c r="R30" s="168"/>
+      <c r="S30" s="168"/>
+      <c r="T30" s="168"/>
+      <c r="U30" s="168"/>
+      <c r="V30" s="168"/>
+      <c r="W30" s="168"/>
+      <c r="X30" s="168"/>
+      <c r="Y30" s="168"/>
+      <c r="Z30" s="168"/>
+      <c r="AA30" s="168"/>
+      <c r="AB30" s="168"/>
+      <c r="AC30" s="168"/>
+      <c r="AD30" s="168"/>
+      <c r="AE30" s="168"/>
+      <c r="AF30" s="168"/>
+      <c r="AG30" s="168"/>
+      <c r="AH30" s="168"/>
+      <c r="AI30" s="168"/>
+      <c r="AJ30" s="168"/>
+      <c r="AK30" s="168"/>
+      <c r="AL30" s="168"/>
+      <c r="AM30" s="168"/>
+      <c r="AN30" s="168"/>
+      <c r="AO30" s="168"/>
+      <c r="AP30" s="168"/>
+      <c r="AQ30" s="168"/>
+      <c r="AR30" s="168"/>
+      <c r="AS30" s="168"/>
+      <c r="AT30" s="168"/>
+      <c r="AU30" s="168"/>
+      <c r="AV30" s="168"/>
+      <c r="AW30" s="168"/>
+      <c r="AX30" s="168"/>
+      <c r="AY30" s="168"/>
+      <c r="AZ30" s="168"/>
+      <c r="BA30" s="168"/>
+      <c r="BB30" s="169"/>
     </row>
     <row r="31" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="168" t="b">
-        <v>0</v>
-      </c>
-      <c r="B31" s="170" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="111">
+      <c r="A31" s="172" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" s="174" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="114">
         <f>SUM(F31:BB31)</f>
         <v>1.5</v>
       </c>
-      <c r="D31" s="111">
+      <c r="D31" s="114">
         <f>SUM(F32:BB32)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E31" s="101">
+        <f>(AVERAGE(C31,C32)-AVERAGE(D31,D32) )</f>
         <v>0</v>
       </c>
-      <c r="E31" s="105">
-        <f>(AVERAGE(C31,C32)-AVERAGE(D31,D32) )</f>
-        <v>1.5</v>
-      </c>
       <c r="F31" s="25"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
       <c r="J31" s="26"/>
       <c r="K31" s="25"/>
-      <c r="L31" s="66">
+      <c r="L31" s="65">
         <v>0.5</v>
       </c>
-      <c r="M31" s="66">
+      <c r="M31" s="65">
         <v>0.5</v>
       </c>
-      <c r="N31" s="66">
+      <c r="N31" s="65">
         <v>0.5</v>
       </c>
       <c r="O31" s="26"/>
       <c r="P31" s="25"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
+      <c r="Q31" s="57"/>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
       <c r="T31" s="26"/>
       <c r="U31" s="25"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="58"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="57"/>
       <c r="Y31" s="26"/>
       <c r="Z31" s="25"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="58"/>
-      <c r="AC31" s="58"/>
+      <c r="AA31" s="57"/>
+      <c r="AB31" s="57"/>
+      <c r="AC31" s="57"/>
       <c r="AD31" s="26"/>
       <c r="AE31" s="25"/>
-      <c r="AF31" s="58"/>
-      <c r="AG31" s="58"/>
-      <c r="AH31" s="58"/>
+      <c r="AF31" s="57"/>
+      <c r="AG31" s="57"/>
+      <c r="AH31" s="57"/>
       <c r="AI31" s="26"/>
       <c r="AJ31" s="25"/>
-      <c r="AK31" s="58"/>
-      <c r="AL31" s="58"/>
-      <c r="AM31" s="58"/>
+      <c r="AK31" s="57"/>
+      <c r="AL31" s="57"/>
+      <c r="AM31" s="57"/>
       <c r="AN31" s="26"/>
       <c r="AO31" s="25"/>
-      <c r="AP31" s="58"/>
-      <c r="AQ31" s="58"/>
-      <c r="AR31" s="58"/>
+      <c r="AP31" s="57"/>
+      <c r="AQ31" s="57"/>
+      <c r="AR31" s="57"/>
       <c r="AS31" s="26"/>
       <c r="AT31" s="25"/>
-      <c r="AU31" s="58"/>
+      <c r="AU31" s="57"/>
       <c r="AV31" s="25"/>
-      <c r="AW31" s="58"/>
-      <c r="AX31" s="58"/>
-      <c r="AY31" s="58"/>
+      <c r="AW31" s="57"/>
+      <c r="AX31" s="57"/>
+      <c r="AY31" s="57"/>
       <c r="AZ31" s="26"/>
       <c r="BA31" s="25"/>
       <c r="BB31" s="26"/>
     </row>
     <row r="32" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="169"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="102"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="106"/>
+      <c r="A32" s="173"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="102"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
       <c r="H32" s="28"/>
@@ -4663,8 +4659,12 @@
       <c r="J32" s="29"/>
       <c r="K32" s="27"/>
       <c r="L32" s="28"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="28"/>
+      <c r="M32" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="28">
+        <v>1</v>
+      </c>
       <c r="O32" s="29"/>
       <c r="P32" s="27"/>
       <c r="Q32" s="28"/>
@@ -4707,23 +4707,23 @@
       <c r="BB32" s="29"/>
     </row>
     <row r="33" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="B33" s="173" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="111">
+      <c r="A33" s="176" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" s="177" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="114">
         <f>SUM(F33:BB33)</f>
         <v>1</v>
       </c>
-      <c r="D33" s="111">
+      <c r="D33" s="114">
         <f>SUM(F34:BB34)</f>
-        <v>0</v>
-      </c>
-      <c r="E33" s="112">
+        <v>0.83000000000000007</v>
+      </c>
+      <c r="E33" s="115">
         <f>(AVERAGE(C33,C34)-AVERAGE(D33,D34) )</f>
-        <v>1</v>
+        <v>0.16999999999999993</v>
       </c>
       <c r="F33" s="30"/>
       <c r="G33" s="31"/>
@@ -4733,14 +4733,14 @@
       <c r="K33" s="30"/>
       <c r="L33" s="31"/>
       <c r="M33" s="31"/>
-      <c r="N33" s="70">
+      <c r="N33" s="69">
         <v>1</v>
       </c>
       <c r="O33" s="32"/>
       <c r="P33" s="30"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="58"/>
+      <c r="Q33" s="57"/>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
       <c r="T33" s="26"/>
       <c r="U33" s="30"/>
       <c r="V33" s="31"/>
@@ -4778,11 +4778,11 @@
       <c r="BB33" s="32"/>
     </row>
     <row r="34" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="169"/>
-      <c r="B34" s="171"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
-      <c r="E34" s="106"/>
+      <c r="A34" s="173"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="98"/>
+      <c r="D34" s="98"/>
+      <c r="E34" s="102"/>
       <c r="F34" s="27"/>
       <c r="G34" s="28"/>
       <c r="H34" s="28"/>
@@ -4791,9 +4791,13 @@
       <c r="K34" s="27"/>
       <c r="L34" s="28"/>
       <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
+      <c r="N34" s="28">
+        <v>0.33</v>
+      </c>
       <c r="O34" s="29"/>
-      <c r="P34" s="27"/>
+      <c r="P34" s="27">
+        <v>0.5</v>
+      </c>
       <c r="Q34" s="28"/>
       <c r="R34" s="28"/>
       <c r="S34" s="28"/>
@@ -4834,26 +4838,26 @@
       <c r="BB34" s="29"/>
     </row>
     <row r="35" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="B35" s="173" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="111">
+      <c r="A35" s="176" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" s="177" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="114">
         <f>SUM(F35:BB35)</f>
         <v>2</v>
       </c>
-      <c r="D35" s="111">
+      <c r="D35" s="114">
         <f>SUM(F36:BB36)</f>
-        <v>0</v>
-      </c>
-      <c r="E35" s="112">
-        <f t="shared" ref="E35" si="0">(AVERAGE(C35,C36)-AVERAGE(D35,D36) )</f>
-        <v>2</v>
+        <v>1.5</v>
+      </c>
+      <c r="E35" s="115">
+        <f>(AVERAGE(C35,C36)-AVERAGE(D35,D36) )</f>
+        <v>0.5</v>
       </c>
       <c r="F35" s="30"/>
-      <c r="G35" s="58"/>
+      <c r="G35" s="57"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="J35" s="32"/>
@@ -4862,12 +4866,12 @@
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
       <c r="O35" s="32"/>
-      <c r="P35" s="64">
+      <c r="P35" s="63">
         <v>2</v>
       </c>
       <c r="Q35" s="31"/>
-      <c r="R35" s="58"/>
-      <c r="S35" s="58"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
       <c r="T35" s="26"/>
       <c r="U35" s="30"/>
       <c r="V35" s="31"/>
@@ -4905,11 +4909,11 @@
       <c r="BB35" s="32"/>
     </row>
     <row r="36" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="169"/>
-      <c r="B36" s="171"/>
-      <c r="C36" s="102"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="106"/>
+      <c r="A36" s="173"/>
+      <c r="B36" s="175"/>
+      <c r="C36" s="98"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="102"/>
       <c r="F36" s="27"/>
       <c r="G36" s="28"/>
       <c r="H36" s="28"/>
@@ -4920,7 +4924,9 @@
       <c r="M36" s="28"/>
       <c r="N36" s="28"/>
       <c r="O36" s="29"/>
-      <c r="P36" s="27"/>
+      <c r="P36" s="27">
+        <v>1.5</v>
+      </c>
       <c r="Q36" s="28"/>
       <c r="R36" s="28"/>
       <c r="S36" s="28"/>
@@ -4961,23 +4967,23 @@
       <c r="BB36" s="29"/>
     </row>
     <row r="37" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="B37" s="173" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="111">
+      <c r="A37" s="176" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" s="177" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="114">
         <f>SUM(F37:BB37)</f>
         <v>0.5</v>
       </c>
-      <c r="D37" s="111">
+      <c r="D37" s="114">
         <f>SUM(F38:BB38)</f>
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="115">
+        <f>(AVERAGE(C37,C38)-AVERAGE(D37,D38) )</f>
         <v>0</v>
-      </c>
-      <c r="E37" s="112">
-        <f t="shared" ref="E37" si="1">(AVERAGE(C37,C38)-AVERAGE(D37,D38) )</f>
-        <v>0.5</v>
       </c>
       <c r="F37" s="30"/>
       <c r="G37" s="31"/>
@@ -4987,14 +4993,14 @@
       <c r="K37" s="30"/>
       <c r="L37" s="31"/>
       <c r="M37" s="31"/>
-      <c r="N37" s="63"/>
+      <c r="N37" s="62"/>
       <c r="O37" s="32"/>
       <c r="P37" s="25"/>
-      <c r="Q37" s="66">
+      <c r="Q37" s="65">
         <v>0.5</v>
       </c>
-      <c r="R37" s="58"/>
-      <c r="S37" s="58"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
       <c r="T37" s="26"/>
       <c r="U37" s="30"/>
       <c r="V37" s="31"/>
@@ -5032,11 +5038,11 @@
       <c r="BB37" s="32"/>
     </row>
     <row r="38" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="169"/>
-      <c r="B38" s="171"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="106"/>
+      <c r="A38" s="173"/>
+      <c r="B38" s="175"/>
+      <c r="C38" s="98"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="102"/>
       <c r="F38" s="27"/>
       <c r="G38" s="28"/>
       <c r="H38" s="28"/>
@@ -5048,7 +5054,9 @@
       <c r="N38" s="28"/>
       <c r="O38" s="29"/>
       <c r="P38" s="27"/>
-      <c r="Q38" s="28"/>
+      <c r="Q38" s="28">
+        <v>0.5</v>
+      </c>
       <c r="R38" s="28"/>
       <c r="S38" s="28"/>
       <c r="T38" s="29"/>
@@ -5088,23 +5096,23 @@
       <c r="BB38" s="29"/>
     </row>
     <row r="39" spans="1:54" ht="13.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="172" t="b">
-        <v>0</v>
-      </c>
-      <c r="B39" s="173" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="111">
+      <c r="A39" s="176" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" s="177" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="114">
         <f>SUM(F39:BB39)</f>
         <v>2.5</v>
       </c>
-      <c r="D39" s="111">
+      <c r="D39" s="114">
         <f>SUM(F40:BB40)</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="112">
-        <f t="shared" ref="E39" si="2">(AVERAGE(C39,C40)-AVERAGE(D39,D40) )</f>
-        <v>2.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="E39" s="115">
+        <f>(AVERAGE(C39,C40)-AVERAGE(D39,D40) )</f>
+        <v>-1</v>
       </c>
       <c r="F39" s="30"/>
       <c r="G39" s="31"/>
@@ -5117,10 +5125,10 @@
       <c r="N39" s="31"/>
       <c r="O39" s="32"/>
       <c r="P39" s="25"/>
-      <c r="Q39" s="66">
+      <c r="Q39" s="65">
         <v>1</v>
       </c>
-      <c r="R39" s="66">
+      <c r="R39" s="65">
         <v>1.5</v>
       </c>
       <c r="S39" s="31"/>
@@ -5161,11 +5169,11 @@
       <c r="BB39" s="32"/>
     </row>
     <row r="40" spans="1:54" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A40" s="169"/>
-      <c r="B40" s="171"/>
-      <c r="C40" s="102"/>
-      <c r="D40" s="102"/>
-      <c r="E40" s="106"/>
+      <c r="A40" s="173"/>
+      <c r="B40" s="175"/>
+      <c r="C40" s="98"/>
+      <c r="D40" s="98"/>
+      <c r="E40" s="102"/>
       <c r="F40" s="27"/>
       <c r="G40" s="28"/>
       <c r="H40" s="28"/>
@@ -5177,9 +5185,15 @@
       <c r="N40" s="28"/>
       <c r="O40" s="29"/>
       <c r="P40" s="27"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
+      <c r="Q40" s="28">
+        <v>1</v>
+      </c>
+      <c r="R40" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="S40" s="28">
+        <v>1</v>
+      </c>
       <c r="T40" s="29"/>
       <c r="U40" s="27"/>
       <c r="V40" s="28"/>
@@ -5217,148 +5231,148 @@
       <c r="BB40" s="29"/>
     </row>
     <row r="41" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="174" t="b">
+      <c r="A41" s="178" t="b">
         <v>0</v>
       </c>
-      <c r="B41" s="176" t="s">
+      <c r="B41" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="178">
+      <c r="C41" s="182">
         <f>SUM(C43:C48)</f>
         <v>4.5</v>
       </c>
-      <c r="D41" s="178">
+      <c r="D41" s="182">
         <f>SUM(D43:D48)</f>
+        <v>3</v>
+      </c>
+      <c r="E41" s="182">
+        <f>(C41-D41)</f>
+        <v>1.5</v>
+      </c>
+      <c r="F41" s="185"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="186"/>
+      <c r="I41" s="186"/>
+      <c r="J41" s="186"/>
+      <c r="K41" s="186"/>
+      <c r="L41" s="186"/>
+      <c r="M41" s="186"/>
+      <c r="N41" s="186"/>
+      <c r="O41" s="186"/>
+      <c r="P41" s="186"/>
+      <c r="Q41" s="186"/>
+      <c r="R41" s="186"/>
+      <c r="S41" s="186"/>
+      <c r="T41" s="186"/>
+      <c r="U41" s="186"/>
+      <c r="V41" s="186"/>
+      <c r="W41" s="186"/>
+      <c r="X41" s="186"/>
+      <c r="Y41" s="186"/>
+      <c r="Z41" s="186"/>
+      <c r="AA41" s="186"/>
+      <c r="AB41" s="186"/>
+      <c r="AC41" s="186"/>
+      <c r="AD41" s="186"/>
+      <c r="AE41" s="186"/>
+      <c r="AF41" s="186"/>
+      <c r="AG41" s="186"/>
+      <c r="AH41" s="186"/>
+      <c r="AI41" s="186"/>
+      <c r="AJ41" s="186"/>
+      <c r="AK41" s="186"/>
+      <c r="AL41" s="186"/>
+      <c r="AM41" s="186"/>
+      <c r="AN41" s="186"/>
+      <c r="AO41" s="186"/>
+      <c r="AP41" s="186"/>
+      <c r="AQ41" s="186"/>
+      <c r="AR41" s="186"/>
+      <c r="AS41" s="186"/>
+      <c r="AT41" s="186"/>
+      <c r="AU41" s="186"/>
+      <c r="AV41" s="186"/>
+      <c r="AW41" s="186"/>
+      <c r="AX41" s="186"/>
+      <c r="AY41" s="186"/>
+      <c r="AZ41" s="186"/>
+      <c r="BA41" s="186"/>
+      <c r="BB41" s="187"/>
+    </row>
+    <row r="42" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A42" s="179"/>
+      <c r="B42" s="181"/>
+      <c r="C42" s="183"/>
+      <c r="D42" s="183"/>
+      <c r="E42" s="184"/>
+      <c r="F42" s="188"/>
+      <c r="G42" s="189"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="189"/>
+      <c r="J42" s="189"/>
+      <c r="K42" s="189"/>
+      <c r="L42" s="189"/>
+      <c r="M42" s="189"/>
+      <c r="N42" s="189"/>
+      <c r="O42" s="189"/>
+      <c r="P42" s="189"/>
+      <c r="Q42" s="189"/>
+      <c r="R42" s="189"/>
+      <c r="S42" s="189"/>
+      <c r="T42" s="189"/>
+      <c r="U42" s="189"/>
+      <c r="V42" s="189"/>
+      <c r="W42" s="189"/>
+      <c r="X42" s="189"/>
+      <c r="Y42" s="189"/>
+      <c r="Z42" s="189"/>
+      <c r="AA42" s="189"/>
+      <c r="AB42" s="189"/>
+      <c r="AC42" s="189"/>
+      <c r="AD42" s="189"/>
+      <c r="AE42" s="189"/>
+      <c r="AF42" s="189"/>
+      <c r="AG42" s="189"/>
+      <c r="AH42" s="189"/>
+      <c r="AI42" s="189"/>
+      <c r="AJ42" s="189"/>
+      <c r="AK42" s="189"/>
+      <c r="AL42" s="189"/>
+      <c r="AM42" s="189"/>
+      <c r="AN42" s="189"/>
+      <c r="AO42" s="189"/>
+      <c r="AP42" s="189"/>
+      <c r="AQ42" s="189"/>
+      <c r="AR42" s="189"/>
+      <c r="AS42" s="189"/>
+      <c r="AT42" s="189"/>
+      <c r="AU42" s="189"/>
+      <c r="AV42" s="189"/>
+      <c r="AW42" s="189"/>
+      <c r="AX42" s="189"/>
+      <c r="AY42" s="189"/>
+      <c r="AZ42" s="189"/>
+      <c r="BA42" s="189"/>
+      <c r="BB42" s="190"/>
+    </row>
+    <row r="43" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="204" t="b">
         <v>0</v>
       </c>
-      <c r="E41" s="178">
-        <f>(C41-D41)</f>
-        <v>4.5</v>
-      </c>
-      <c r="F41" s="181"/>
-      <c r="G41" s="182"/>
-      <c r="H41" s="182"/>
-      <c r="I41" s="182"/>
-      <c r="J41" s="182"/>
-      <c r="K41" s="182"/>
-      <c r="L41" s="182"/>
-      <c r="M41" s="182"/>
-      <c r="N41" s="182"/>
-      <c r="O41" s="182"/>
-      <c r="P41" s="182"/>
-      <c r="Q41" s="182"/>
-      <c r="R41" s="182"/>
-      <c r="S41" s="182"/>
-      <c r="T41" s="182"/>
-      <c r="U41" s="182"/>
-      <c r="V41" s="182"/>
-      <c r="W41" s="182"/>
-      <c r="X41" s="182"/>
-      <c r="Y41" s="182"/>
-      <c r="Z41" s="182"/>
-      <c r="AA41" s="182"/>
-      <c r="AB41" s="182"/>
-      <c r="AC41" s="182"/>
-      <c r="AD41" s="182"/>
-      <c r="AE41" s="182"/>
-      <c r="AF41" s="182"/>
-      <c r="AG41" s="182"/>
-      <c r="AH41" s="182"/>
-      <c r="AI41" s="182"/>
-      <c r="AJ41" s="182"/>
-      <c r="AK41" s="182"/>
-      <c r="AL41" s="182"/>
-      <c r="AM41" s="182"/>
-      <c r="AN41" s="182"/>
-      <c r="AO41" s="182"/>
-      <c r="AP41" s="182"/>
-      <c r="AQ41" s="182"/>
-      <c r="AR41" s="182"/>
-      <c r="AS41" s="182"/>
-      <c r="AT41" s="182"/>
-      <c r="AU41" s="182"/>
-      <c r="AV41" s="182"/>
-      <c r="AW41" s="182"/>
-      <c r="AX41" s="182"/>
-      <c r="AY41" s="182"/>
-      <c r="AZ41" s="182"/>
-      <c r="BA41" s="182"/>
-      <c r="BB41" s="183"/>
-    </row>
-    <row r="42" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A42" s="175"/>
-      <c r="B42" s="177"/>
-      <c r="C42" s="179"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="180"/>
-      <c r="F42" s="184"/>
-      <c r="G42" s="185"/>
-      <c r="H42" s="185"/>
-      <c r="I42" s="185"/>
-      <c r="J42" s="185"/>
-      <c r="K42" s="185"/>
-      <c r="L42" s="185"/>
-      <c r="M42" s="185"/>
-      <c r="N42" s="185"/>
-      <c r="O42" s="185"/>
-      <c r="P42" s="185"/>
-      <c r="Q42" s="185"/>
-      <c r="R42" s="185"/>
-      <c r="S42" s="185"/>
-      <c r="T42" s="185"/>
-      <c r="U42" s="185"/>
-      <c r="V42" s="185"/>
-      <c r="W42" s="185"/>
-      <c r="X42" s="185"/>
-      <c r="Y42" s="185"/>
-      <c r="Z42" s="185"/>
-      <c r="AA42" s="185"/>
-      <c r="AB42" s="185"/>
-      <c r="AC42" s="185"/>
-      <c r="AD42" s="185"/>
-      <c r="AE42" s="185"/>
-      <c r="AF42" s="185"/>
-      <c r="AG42" s="185"/>
-      <c r="AH42" s="185"/>
-      <c r="AI42" s="185"/>
-      <c r="AJ42" s="185"/>
-      <c r="AK42" s="185"/>
-      <c r="AL42" s="185"/>
-      <c r="AM42" s="185"/>
-      <c r="AN42" s="185"/>
-      <c r="AO42" s="185"/>
-      <c r="AP42" s="185"/>
-      <c r="AQ42" s="185"/>
-      <c r="AR42" s="185"/>
-      <c r="AS42" s="185"/>
-      <c r="AT42" s="185"/>
-      <c r="AU42" s="185"/>
-      <c r="AV42" s="185"/>
-      <c r="AW42" s="185"/>
-      <c r="AX42" s="185"/>
-      <c r="AY42" s="185"/>
-      <c r="AZ42" s="185"/>
-      <c r="BA42" s="185"/>
-      <c r="BB42" s="186"/>
-    </row>
-    <row r="43" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="200" t="b">
-        <v>0</v>
-      </c>
-      <c r="B43" s="202" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="111">
+      <c r="B43" s="206" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="114">
         <f>SUM(F43:BB43)</f>
         <v>1</v>
       </c>
-      <c r="D43" s="111">
+      <c r="D43" s="114">
         <f>SUM(F44:BB44)</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="101">
+        <f>(AVERAGE(C43,C44)-AVERAGE(D43,D44) )</f>
         <v>0</v>
-      </c>
-      <c r="E43" s="105">
-        <f>(AVERAGE(C43,C44)-AVERAGE(D43,D44) )</f>
-        <v>1</v>
       </c>
       <c r="F43" s="38"/>
       <c r="G43" s="39"/>
@@ -5371,9 +5385,9 @@
       <c r="N43" s="39"/>
       <c r="O43" s="40"/>
       <c r="P43" s="25"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="58"/>
-      <c r="S43" s="66">
+      <c r="Q43" s="57"/>
+      <c r="R43" s="57"/>
+      <c r="S43" s="65">
         <v>1</v>
       </c>
       <c r="T43" s="26"/>
@@ -5413,11 +5427,11 @@
       <c r="BB43" s="40"/>
     </row>
     <row r="44" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="201"/>
-      <c r="B44" s="203"/>
-      <c r="C44" s="102"/>
-      <c r="D44" s="102"/>
-      <c r="E44" s="106"/>
+      <c r="A44" s="205"/>
+      <c r="B44" s="207"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="98"/>
+      <c r="E44" s="102"/>
       <c r="F44" s="27"/>
       <c r="G44" s="28"/>
       <c r="H44" s="28"/>
@@ -5431,7 +5445,9 @@
       <c r="P44" s="27"/>
       <c r="Q44" s="28"/>
       <c r="R44" s="28"/>
-      <c r="S44" s="28"/>
+      <c r="S44" s="28">
+        <v>1</v>
+      </c>
       <c r="T44" s="29"/>
       <c r="U44" s="27"/>
       <c r="V44" s="28"/>
@@ -5469,23 +5485,23 @@
       <c r="BB44" s="29"/>
     </row>
     <row r="45" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="204" t="b">
+      <c r="A45" s="208" t="b">
         <v>0</v>
       </c>
-      <c r="B45" s="205" t="s">
-        <v>44</v>
-      </c>
-      <c r="C45" s="111">
+      <c r="B45" s="209" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="114">
         <f>SUM(F45:BB45)</f>
         <v>1</v>
       </c>
-      <c r="D45" s="111">
+      <c r="D45" s="114">
         <f>SUM(F46:BB46)</f>
+        <v>1</v>
+      </c>
+      <c r="E45" s="115">
+        <f>(AVERAGE(C45,C46)-AVERAGE(D45,D46) )</f>
         <v>0</v>
-      </c>
-      <c r="E45" s="112">
-        <f>(AVERAGE(C45,C46)-AVERAGE(D45,D46) )</f>
-        <v>1</v>
       </c>
       <c r="F45" s="30"/>
       <c r="G45" s="31"/>
@@ -5498,11 +5514,11 @@
       <c r="N45" s="31"/>
       <c r="O45" s="32"/>
       <c r="P45" s="25"/>
-      <c r="Q45" s="58"/>
-      <c r="R45" s="58"/>
-      <c r="S45" s="58"/>
+      <c r="Q45" s="57"/>
+      <c r="R45" s="57"/>
+      <c r="S45" s="57"/>
       <c r="T45" s="26"/>
-      <c r="U45" s="71">
+      <c r="U45" s="70">
         <v>1</v>
       </c>
       <c r="V45" s="31"/>
@@ -5540,11 +5556,11 @@
       <c r="BB45" s="32"/>
     </row>
     <row r="46" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A46" s="201"/>
-      <c r="B46" s="203"/>
-      <c r="C46" s="102"/>
-      <c r="D46" s="102"/>
-      <c r="E46" s="143"/>
+      <c r="A46" s="205"/>
+      <c r="B46" s="207"/>
+      <c r="C46" s="98"/>
+      <c r="D46" s="98"/>
+      <c r="E46" s="147"/>
       <c r="F46" s="27"/>
       <c r="G46" s="28"/>
       <c r="H46" s="28"/>
@@ -5560,7 +5576,9 @@
       <c r="R46" s="28"/>
       <c r="S46" s="28"/>
       <c r="T46" s="29"/>
-      <c r="U46" s="27"/>
+      <c r="U46" s="27">
+        <v>1</v>
+      </c>
       <c r="V46" s="28"/>
       <c r="W46" s="28"/>
       <c r="X46" s="28"/>
@@ -5596,23 +5614,23 @@
       <c r="BB46" s="29"/>
     </row>
     <row r="47" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="204" t="b">
+      <c r="A47" s="208" t="b">
         <v>0</v>
       </c>
-      <c r="B47" s="205" t="s">
-        <v>43</v>
-      </c>
-      <c r="C47" s="111">
+      <c r="B47" s="209" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="114">
         <f>SUM(F47:BB47)</f>
         <v>2.5</v>
       </c>
-      <c r="D47" s="111">
+      <c r="D47" s="114">
         <f>SUM(F48:BB48)</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="112">
+        <v>1</v>
+      </c>
+      <c r="E47" s="115">
         <f>(AVERAGE(C47,C48)-AVERAGE(D47,D48) )</f>
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F47" s="30"/>
       <c r="G47" s="31"/>
@@ -5625,14 +5643,14 @@
       <c r="N47" s="31"/>
       <c r="O47" s="32"/>
       <c r="P47" s="25"/>
-      <c r="Q47" s="58"/>
-      <c r="R47" s="58"/>
-      <c r="S47" s="58"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="57"/>
+      <c r="S47" s="57"/>
       <c r="T47" s="26"/>
-      <c r="U47" s="71">
+      <c r="U47" s="70">
         <v>1</v>
       </c>
-      <c r="V47" s="70">
+      <c r="V47" s="69">
         <v>1.5</v>
       </c>
       <c r="W47" s="31"/>
@@ -5669,11 +5687,11 @@
       <c r="BB47" s="32"/>
     </row>
     <row r="48" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A48" s="201"/>
-      <c r="B48" s="203"/>
-      <c r="C48" s="102"/>
-      <c r="D48" s="102"/>
-      <c r="E48" s="143"/>
+      <c r="A48" s="205"/>
+      <c r="B48" s="207"/>
+      <c r="C48" s="98"/>
+      <c r="D48" s="98"/>
+      <c r="E48" s="147"/>
       <c r="F48" s="27"/>
       <c r="G48" s="28"/>
       <c r="H48" s="28"/>
@@ -5689,7 +5707,9 @@
       <c r="R48" s="28"/>
       <c r="S48" s="28"/>
       <c r="T48" s="29"/>
-      <c r="U48" s="27"/>
+      <c r="U48" s="27">
+        <v>1</v>
+      </c>
       <c r="V48" s="28"/>
       <c r="W48" s="28"/>
       <c r="X48" s="28"/>
@@ -5725,148 +5745,148 @@
       <c r="BB48" s="29"/>
     </row>
     <row r="49" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="187" t="b">
+      <c r="A49" s="191" t="b">
         <v>0</v>
       </c>
-      <c r="B49" s="189" t="s">
+      <c r="B49" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="C49" s="191">
+      <c r="C49" s="195">
         <f>SUM(C51:C66)</f>
         <v>23</v>
       </c>
-      <c r="D49" s="191">
+      <c r="D49" s="195">
         <f>SUM(D51:D66)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E49" s="195">
+        <f>(C49-D49)</f>
+        <v>21.5</v>
+      </c>
+      <c r="F49" s="198"/>
+      <c r="G49" s="199"/>
+      <c r="H49" s="199"/>
+      <c r="I49" s="199"/>
+      <c r="J49" s="199"/>
+      <c r="K49" s="199"/>
+      <c r="L49" s="199"/>
+      <c r="M49" s="199"/>
+      <c r="N49" s="199"/>
+      <c r="O49" s="199"/>
+      <c r="P49" s="199"/>
+      <c r="Q49" s="199"/>
+      <c r="R49" s="199"/>
+      <c r="S49" s="199"/>
+      <c r="T49" s="199"/>
+      <c r="U49" s="199"/>
+      <c r="V49" s="199"/>
+      <c r="W49" s="199"/>
+      <c r="X49" s="199"/>
+      <c r="Y49" s="199"/>
+      <c r="Z49" s="199"/>
+      <c r="AA49" s="199"/>
+      <c r="AB49" s="199"/>
+      <c r="AC49" s="199"/>
+      <c r="AD49" s="199"/>
+      <c r="AE49" s="199"/>
+      <c r="AF49" s="199"/>
+      <c r="AG49" s="199"/>
+      <c r="AH49" s="199"/>
+      <c r="AI49" s="199"/>
+      <c r="AJ49" s="199"/>
+      <c r="AK49" s="199"/>
+      <c r="AL49" s="199"/>
+      <c r="AM49" s="199"/>
+      <c r="AN49" s="199"/>
+      <c r="AO49" s="199"/>
+      <c r="AP49" s="199"/>
+      <c r="AQ49" s="199"/>
+      <c r="AR49" s="199"/>
+      <c r="AS49" s="199"/>
+      <c r="AT49" s="199"/>
+      <c r="AU49" s="199"/>
+      <c r="AV49" s="199"/>
+      <c r="AW49" s="199"/>
+      <c r="AX49" s="199"/>
+      <c r="AY49" s="199"/>
+      <c r="AZ49" s="199"/>
+      <c r="BA49" s="199"/>
+      <c r="BB49" s="200"/>
+    </row>
+    <row r="50" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A50" s="192"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="196"/>
+      <c r="D50" s="196"/>
+      <c r="E50" s="197"/>
+      <c r="F50" s="201"/>
+      <c r="G50" s="202"/>
+      <c r="H50" s="202"/>
+      <c r="I50" s="202"/>
+      <c r="J50" s="202"/>
+      <c r="K50" s="202"/>
+      <c r="L50" s="202"/>
+      <c r="M50" s="202"/>
+      <c r="N50" s="202"/>
+      <c r="O50" s="202"/>
+      <c r="P50" s="202"/>
+      <c r="Q50" s="202"/>
+      <c r="R50" s="202"/>
+      <c r="S50" s="202"/>
+      <c r="T50" s="202"/>
+      <c r="U50" s="202"/>
+      <c r="V50" s="202"/>
+      <c r="W50" s="202"/>
+      <c r="X50" s="202"/>
+      <c r="Y50" s="202"/>
+      <c r="Z50" s="202"/>
+      <c r="AA50" s="202"/>
+      <c r="AB50" s="202"/>
+      <c r="AC50" s="202"/>
+      <c r="AD50" s="202"/>
+      <c r="AE50" s="202"/>
+      <c r="AF50" s="202"/>
+      <c r="AG50" s="202"/>
+      <c r="AH50" s="202"/>
+      <c r="AI50" s="202"/>
+      <c r="AJ50" s="202"/>
+      <c r="AK50" s="202"/>
+      <c r="AL50" s="202"/>
+      <c r="AM50" s="202"/>
+      <c r="AN50" s="202"/>
+      <c r="AO50" s="202"/>
+      <c r="AP50" s="202"/>
+      <c r="AQ50" s="202"/>
+      <c r="AR50" s="202"/>
+      <c r="AS50" s="202"/>
+      <c r="AT50" s="202"/>
+      <c r="AU50" s="202"/>
+      <c r="AV50" s="202"/>
+      <c r="AW50" s="202"/>
+      <c r="AX50" s="202"/>
+      <c r="AY50" s="202"/>
+      <c r="AZ50" s="202"/>
+      <c r="BA50" s="202"/>
+      <c r="BB50" s="203"/>
+    </row>
+    <row r="51" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="210" t="b">
         <v>0</v>
       </c>
-      <c r="E49" s="191">
-        <f>(C49-D49)</f>
-        <v>23</v>
-      </c>
-      <c r="F49" s="194"/>
-      <c r="G49" s="195"/>
-      <c r="H49" s="195"/>
-      <c r="I49" s="195"/>
-      <c r="J49" s="195"/>
-      <c r="K49" s="195"/>
-      <c r="L49" s="195"/>
-      <c r="M49" s="195"/>
-      <c r="N49" s="195"/>
-      <c r="O49" s="195"/>
-      <c r="P49" s="195"/>
-      <c r="Q49" s="195"/>
-      <c r="R49" s="195"/>
-      <c r="S49" s="195"/>
-      <c r="T49" s="195"/>
-      <c r="U49" s="195"/>
-      <c r="V49" s="195"/>
-      <c r="W49" s="195"/>
-      <c r="X49" s="195"/>
-      <c r="Y49" s="195"/>
-      <c r="Z49" s="195"/>
-      <c r="AA49" s="195"/>
-      <c r="AB49" s="195"/>
-      <c r="AC49" s="195"/>
-      <c r="AD49" s="195"/>
-      <c r="AE49" s="195"/>
-      <c r="AF49" s="195"/>
-      <c r="AG49" s="195"/>
-      <c r="AH49" s="195"/>
-      <c r="AI49" s="195"/>
-      <c r="AJ49" s="195"/>
-      <c r="AK49" s="195"/>
-      <c r="AL49" s="195"/>
-      <c r="AM49" s="195"/>
-      <c r="AN49" s="195"/>
-      <c r="AO49" s="195"/>
-      <c r="AP49" s="195"/>
-      <c r="AQ49" s="195"/>
-      <c r="AR49" s="195"/>
-      <c r="AS49" s="195"/>
-      <c r="AT49" s="195"/>
-      <c r="AU49" s="195"/>
-      <c r="AV49" s="195"/>
-      <c r="AW49" s="195"/>
-      <c r="AX49" s="195"/>
-      <c r="AY49" s="195"/>
-      <c r="AZ49" s="195"/>
-      <c r="BA49" s="195"/>
-      <c r="BB49" s="196"/>
-    </row>
-    <row r="50" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A50" s="188"/>
-      <c r="B50" s="190"/>
-      <c r="C50" s="192"/>
-      <c r="D50" s="192"/>
-      <c r="E50" s="193"/>
-      <c r="F50" s="197"/>
-      <c r="G50" s="198"/>
-      <c r="H50" s="198"/>
-      <c r="I50" s="198"/>
-      <c r="J50" s="198"/>
-      <c r="K50" s="198"/>
-      <c r="L50" s="198"/>
-      <c r="M50" s="198"/>
-      <c r="N50" s="198"/>
-      <c r="O50" s="198"/>
-      <c r="P50" s="198"/>
-      <c r="Q50" s="198"/>
-      <c r="R50" s="198"/>
-      <c r="S50" s="198"/>
-      <c r="T50" s="198"/>
-      <c r="U50" s="198"/>
-      <c r="V50" s="198"/>
-      <c r="W50" s="198"/>
-      <c r="X50" s="198"/>
-      <c r="Y50" s="198"/>
-      <c r="Z50" s="198"/>
-      <c r="AA50" s="198"/>
-      <c r="AB50" s="198"/>
-      <c r="AC50" s="198"/>
-      <c r="AD50" s="198"/>
-      <c r="AE50" s="198"/>
-      <c r="AF50" s="198"/>
-      <c r="AG50" s="198"/>
-      <c r="AH50" s="198"/>
-      <c r="AI50" s="198"/>
-      <c r="AJ50" s="198"/>
-      <c r="AK50" s="198"/>
-      <c r="AL50" s="198"/>
-      <c r="AM50" s="198"/>
-      <c r="AN50" s="198"/>
-      <c r="AO50" s="198"/>
-      <c r="AP50" s="198"/>
-      <c r="AQ50" s="198"/>
-      <c r="AR50" s="198"/>
-      <c r="AS50" s="198"/>
-      <c r="AT50" s="198"/>
-      <c r="AU50" s="198"/>
-      <c r="AV50" s="198"/>
-      <c r="AW50" s="198"/>
-      <c r="AX50" s="198"/>
-      <c r="AY50" s="198"/>
-      <c r="AZ50" s="198"/>
-      <c r="BA50" s="198"/>
-      <c r="BB50" s="199"/>
-    </row>
-    <row r="51" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="206" t="b">
-        <v>0</v>
-      </c>
-      <c r="B51" s="208" t="s">
-        <v>55</v>
-      </c>
-      <c r="C51" s="111">
+      <c r="B51" s="212" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" s="114">
         <f>SUM(F51:BB51)</f>
         <v>3</v>
       </c>
-      <c r="D51" s="111">
+      <c r="D51" s="114">
         <f>SUM(F52:BB52)</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="105">
+        <v>1.5</v>
+      </c>
+      <c r="E51" s="101">
         <f>(AVERAGE(C51,C52)-AVERAGE(D51,D52) )</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F51" s="38"/>
       <c r="G51" s="39"/>
@@ -5879,20 +5899,20 @@
       <c r="N51" s="39"/>
       <c r="O51" s="40"/>
       <c r="P51" s="25"/>
-      <c r="Q51" s="58"/>
-      <c r="R51" s="58"/>
-      <c r="S51" s="58"/>
+      <c r="Q51" s="57"/>
+      <c r="R51" s="57"/>
+      <c r="S51" s="57"/>
       <c r="T51" s="26"/>
       <c r="U51" s="38"/>
       <c r="V51" s="39"/>
-      <c r="W51" s="72">
+      <c r="W51" s="71">
         <v>1.5</v>
       </c>
-      <c r="X51" s="72">
+      <c r="X51" s="71">
         <v>1</v>
       </c>
       <c r="Y51" s="40"/>
-      <c r="Z51" s="73">
+      <c r="Z51" s="72">
         <v>0.5</v>
       </c>
       <c r="AA51" s="39"/>
@@ -5925,11 +5945,11 @@
       <c r="BB51" s="40"/>
     </row>
     <row r="52" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="207"/>
-      <c r="B52" s="209"/>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="106"/>
+      <c r="A52" s="211"/>
+      <c r="B52" s="213"/>
+      <c r="C52" s="98"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="102"/>
       <c r="F52" s="27"/>
       <c r="G52" s="28"/>
       <c r="H52" s="28"/>
@@ -5946,8 +5966,12 @@
       <c r="S52" s="28"/>
       <c r="T52" s="29"/>
       <c r="U52" s="27"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
+      <c r="V52" s="28">
+        <v>1</v>
+      </c>
+      <c r="W52" s="28">
+        <v>0.5</v>
+      </c>
       <c r="X52" s="28"/>
       <c r="Y52" s="29"/>
       <c r="Z52" s="27"/>
@@ -5981,22 +6005,22 @@
       <c r="BB52" s="29"/>
     </row>
     <row r="53" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="210" t="b">
+      <c r="A53" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B53" s="208" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="111">
+      <c r="B53" s="212" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="114">
         <f>SUM(F53:BB53)</f>
         <v>1.5</v>
       </c>
-      <c r="D53" s="111">
+      <c r="D53" s="114">
         <f>SUM(F54:BB54)</f>
         <v>0</v>
       </c>
-      <c r="E53" s="112">
-        <f t="shared" ref="E53:E65" si="3">(AVERAGE(C53,C54)-AVERAGE(D53,D54) )</f>
+      <c r="E53" s="115">
+        <f t="shared" ref="E53:E65" si="0">(AVERAGE(C53,C54)-AVERAGE(D53,D54) )</f>
         <v>1.5</v>
       </c>
       <c r="F53" s="30"/>
@@ -6010,20 +6034,20 @@
       <c r="N53" s="31"/>
       <c r="O53" s="32"/>
       <c r="P53" s="25"/>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="58"/>
-      <c r="S53" s="58"/>
+      <c r="Q53" s="57"/>
+      <c r="R53" s="57"/>
+      <c r="S53" s="57"/>
       <c r="T53" s="26"/>
       <c r="U53" s="30"/>
       <c r="V53" s="31"/>
-      <c r="W53" s="63"/>
+      <c r="W53" s="62"/>
       <c r="X53" s="31"/>
       <c r="Y53" s="32"/>
-      <c r="Z53" s="71">
+      <c r="Z53" s="70">
         <v>1.5</v>
       </c>
       <c r="AA53" s="31"/>
-      <c r="AB53" s="63"/>
+      <c r="AB53" s="62"/>
       <c r="AC53" s="31"/>
       <c r="AD53" s="32"/>
       <c r="AE53" s="30"/>
@@ -6052,11 +6076,11 @@
       <c r="BB53" s="32"/>
     </row>
     <row r="54" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="207"/>
-      <c r="B54" s="209"/>
-      <c r="C54" s="102"/>
-      <c r="D54" s="102"/>
-      <c r="E54" s="106"/>
+      <c r="A54" s="211"/>
+      <c r="B54" s="213"/>
+      <c r="C54" s="98"/>
+      <c r="D54" s="98"/>
+      <c r="E54" s="102"/>
       <c r="F54" s="27"/>
       <c r="G54" s="28"/>
       <c r="H54" s="28"/>
@@ -6074,12 +6098,12 @@
       <c r="T54" s="29"/>
       <c r="U54" s="27"/>
       <c r="V54" s="28"/>
-      <c r="W54" s="63"/>
+      <c r="W54" s="62"/>
       <c r="X54" s="28"/>
       <c r="Y54" s="29"/>
       <c r="Z54" s="27"/>
       <c r="AA54" s="28"/>
-      <c r="AB54" s="63"/>
+      <c r="AB54" s="62"/>
       <c r="AC54" s="28"/>
       <c r="AD54" s="29"/>
       <c r="AE54" s="27"/>
@@ -6108,22 +6132,22 @@
       <c r="BB54" s="29"/>
     </row>
     <row r="55" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="210" t="b">
+      <c r="A55" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B55" s="208" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="111">
+      <c r="B55" s="212" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55" s="114">
         <f>SUM(F55:BB55)</f>
         <v>1.5</v>
       </c>
-      <c r="D55" s="111">
+      <c r="D55" s="114">
         <f>SUM(F56:BB56)</f>
         <v>0</v>
       </c>
-      <c r="E55" s="112">
-        <f t="shared" si="3"/>
+      <c r="E55" s="115">
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="F55" s="30"/>
@@ -6137,17 +6161,17 @@
       <c r="N55" s="31"/>
       <c r="O55" s="31"/>
       <c r="P55" s="25"/>
-      <c r="Q55" s="58"/>
-      <c r="R55" s="58"/>
-      <c r="S55" s="58"/>
+      <c r="Q55" s="57"/>
+      <c r="R55" s="57"/>
+      <c r="S55" s="57"/>
       <c r="T55" s="26"/>
       <c r="U55" s="30"/>
       <c r="V55" s="31"/>
       <c r="W55" s="31"/>
-      <c r="X55" s="63"/>
+      <c r="X55" s="62"/>
       <c r="Y55" s="32"/>
       <c r="Z55" s="31"/>
-      <c r="AA55" s="70">
+      <c r="AA55" s="69">
         <v>1.5</v>
       </c>
       <c r="AB55" s="31"/>
@@ -6179,11 +6203,11 @@
       <c r="BB55" s="32"/>
     </row>
     <row r="56" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="207"/>
-      <c r="B56" s="209"/>
-      <c r="C56" s="102"/>
-      <c r="D56" s="102"/>
-      <c r="E56" s="106"/>
+      <c r="A56" s="211"/>
+      <c r="B56" s="213"/>
+      <c r="C56" s="98"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="102"/>
       <c r="F56" s="27"/>
       <c r="G56" s="28"/>
       <c r="H56" s="28"/>
@@ -6202,7 +6226,7 @@
       <c r="U56" s="27"/>
       <c r="V56" s="28"/>
       <c r="W56" s="28"/>
-      <c r="X56" s="63"/>
+      <c r="X56" s="62"/>
       <c r="Y56" s="29"/>
       <c r="Z56" s="28"/>
       <c r="AA56" s="28"/>
@@ -6235,22 +6259,22 @@
       <c r="BB56" s="29"/>
     </row>
     <row r="57" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="210" t="b">
+      <c r="A57" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B57" s="208" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="111">
+      <c r="B57" s="212" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="114">
         <f>SUM(F57:BB57)</f>
         <v>5.5</v>
       </c>
-      <c r="D57" s="111">
+      <c r="D57" s="114">
         <f>SUM(F58:BB58)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="112">
-        <f t="shared" si="3"/>
+      <c r="E57" s="115">
+        <f t="shared" si="0"/>
         <v>5.5</v>
       </c>
       <c r="F57" s="30"/>
@@ -6264,9 +6288,9 @@
       <c r="N57" s="31"/>
       <c r="O57" s="32"/>
       <c r="P57" s="25"/>
-      <c r="Q57" s="58"/>
-      <c r="R57" s="58"/>
-      <c r="S57" s="58"/>
+      <c r="Q57" s="57"/>
+      <c r="R57" s="57"/>
+      <c r="S57" s="57"/>
       <c r="T57" s="26"/>
       <c r="U57" s="30"/>
       <c r="V57" s="31"/>
@@ -6275,24 +6299,24 @@
       <c r="Y57" s="32"/>
       <c r="Z57" s="30"/>
       <c r="AA57" s="31"/>
-      <c r="AB57" s="70">
+      <c r="AB57" s="69">
         <v>1.5</v>
       </c>
-      <c r="AC57" s="70">
+      <c r="AC57" s="69">
         <v>1</v>
       </c>
-      <c r="AD57" s="74">
+      <c r="AD57" s="73">
         <v>0.5</v>
       </c>
-      <c r="AE57" s="71">
+      <c r="AE57" s="70">
         <v>1</v>
       </c>
-      <c r="AF57" s="70">
+      <c r="AF57" s="69">
         <v>1</v>
       </c>
       <c r="AG57" s="31"/>
       <c r="AH57" s="31"/>
-      <c r="AI57" s="74">
+      <c r="AI57" s="73">
         <v>0.5</v>
       </c>
       <c r="AJ57" s="30"/>
@@ -6316,11 +6340,11 @@
       <c r="BB57" s="32"/>
     </row>
     <row r="58" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="207"/>
-      <c r="B58" s="209"/>
-      <c r="C58" s="102"/>
-      <c r="D58" s="102"/>
-      <c r="E58" s="106"/>
+      <c r="A58" s="211"/>
+      <c r="B58" s="213"/>
+      <c r="C58" s="98"/>
+      <c r="D58" s="98"/>
+      <c r="E58" s="102"/>
       <c r="F58" s="27"/>
       <c r="G58" s="28"/>
       <c r="H58" s="28"/>
@@ -6372,22 +6396,22 @@
       <c r="BB58" s="29"/>
     </row>
     <row r="59" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="210" t="b">
+      <c r="A59" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B59" s="208" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="111">
+      <c r="B59" s="212" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="114">
         <f>SUM(F59:BB59)</f>
         <v>4</v>
       </c>
-      <c r="D59" s="111">
+      <c r="D59" s="114">
         <f>SUM(F60:BB60)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="112">
-        <f t="shared" si="3"/>
+      <c r="E59" s="115">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F59" s="30"/>
@@ -6401,9 +6425,9 @@
       <c r="N59" s="31"/>
       <c r="O59" s="32"/>
       <c r="P59" s="25"/>
-      <c r="Q59" s="58"/>
-      <c r="R59" s="58"/>
-      <c r="S59" s="58"/>
+      <c r="Q59" s="57"/>
+      <c r="R59" s="57"/>
+      <c r="S59" s="57"/>
       <c r="T59" s="26"/>
       <c r="U59" s="30"/>
       <c r="V59" s="31"/>
@@ -6411,21 +6435,21 @@
       <c r="X59" s="31"/>
       <c r="Y59" s="32"/>
       <c r="Z59" s="30"/>
-      <c r="AA59" s="63"/>
-      <c r="AB59" s="63"/>
+      <c r="AA59" s="62"/>
+      <c r="AB59" s="62"/>
       <c r="AC59" s="31"/>
       <c r="AD59" s="32"/>
       <c r="AE59" s="31"/>
-      <c r="AF59" s="70">
+      <c r="AF59" s="69">
         <v>0.5</v>
       </c>
-      <c r="AG59" s="70">
+      <c r="AG59" s="69">
         <v>1.5</v>
       </c>
-      <c r="AH59" s="70">
+      <c r="AH59" s="69">
         <v>1.5</v>
       </c>
-      <c r="AI59" s="74">
+      <c r="AI59" s="73">
         <v>0.5</v>
       </c>
       <c r="AJ59" s="30"/>
@@ -6449,11 +6473,11 @@
       <c r="BB59" s="32"/>
     </row>
     <row r="60" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="207"/>
-      <c r="B60" s="209"/>
-      <c r="C60" s="102"/>
-      <c r="D60" s="102"/>
-      <c r="E60" s="106"/>
+      <c r="A60" s="211"/>
+      <c r="B60" s="213"/>
+      <c r="C60" s="98"/>
+      <c r="D60" s="98"/>
+      <c r="E60" s="102"/>
       <c r="F60" s="27"/>
       <c r="G60" s="28"/>
       <c r="H60" s="28"/>
@@ -6474,9 +6498,9 @@
       <c r="W60" s="28"/>
       <c r="X60" s="28"/>
       <c r="Y60" s="29"/>
-      <c r="Z60" s="63"/>
-      <c r="AA60" s="63"/>
-      <c r="AB60" s="63"/>
+      <c r="Z60" s="62"/>
+      <c r="AA60" s="62"/>
+      <c r="AB60" s="62"/>
       <c r="AC60" s="28"/>
       <c r="AD60" s="29"/>
       <c r="AE60" s="28"/>
@@ -6505,22 +6529,22 @@
       <c r="BB60" s="29"/>
     </row>
     <row r="61" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="210" t="b">
+      <c r="A61" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B61" s="208" t="s">
-        <v>60</v>
-      </c>
-      <c r="C61" s="111">
+      <c r="B61" s="212" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" s="114">
         <f>SUM(F61:BB61)</f>
         <v>1.5</v>
       </c>
-      <c r="D61" s="111">
+      <c r="D61" s="114">
         <f>SUM(F62:BB62)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="112">
-        <f t="shared" si="3"/>
+      <c r="E61" s="115">
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="F61" s="30"/>
@@ -6535,8 +6559,8 @@
       <c r="O61" s="32"/>
       <c r="P61" s="25"/>
       <c r="Q61" s="31"/>
-      <c r="R61" s="58"/>
-      <c r="S61" s="58"/>
+      <c r="R61" s="57"/>
+      <c r="S61" s="57"/>
       <c r="T61" s="26"/>
       <c r="U61" s="30"/>
       <c r="V61" s="31"/>
@@ -6546,14 +6570,14 @@
       <c r="Z61" s="30"/>
       <c r="AA61" s="31"/>
       <c r="AB61" s="31"/>
-      <c r="AC61" s="63"/>
+      <c r="AC61" s="62"/>
       <c r="AD61" s="32"/>
-      <c r="AE61" s="63"/>
+      <c r="AE61" s="62"/>
       <c r="AF61" s="31"/>
       <c r="AG61" s="31"/>
       <c r="AH61" s="31"/>
       <c r="AI61" s="32"/>
-      <c r="AJ61" s="71">
+      <c r="AJ61" s="70">
         <v>1.5</v>
       </c>
       <c r="AK61" s="31"/>
@@ -6576,11 +6600,11 @@
       <c r="BB61" s="32"/>
     </row>
     <row r="62" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="207"/>
-      <c r="B62" s="209"/>
-      <c r="C62" s="102"/>
-      <c r="D62" s="102"/>
-      <c r="E62" s="106"/>
+      <c r="A62" s="211"/>
+      <c r="B62" s="213"/>
+      <c r="C62" s="98"/>
+      <c r="D62" s="98"/>
+      <c r="E62" s="102"/>
       <c r="F62" s="27"/>
       <c r="G62" s="28"/>
       <c r="H62" s="28"/>
@@ -6604,9 +6628,9 @@
       <c r="Z62" s="27"/>
       <c r="AA62" s="28"/>
       <c r="AB62" s="28"/>
-      <c r="AC62" s="63"/>
+      <c r="AC62" s="62"/>
       <c r="AD62" s="29"/>
-      <c r="AE62" s="63"/>
+      <c r="AE62" s="62"/>
       <c r="AF62" s="28"/>
       <c r="AG62" s="28"/>
       <c r="AH62" s="28"/>
@@ -6632,22 +6656,22 @@
       <c r="BB62" s="29"/>
     </row>
     <row r="63" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="210" t="b">
+      <c r="A63" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B63" s="211" t="s">
-        <v>61</v>
-      </c>
-      <c r="C63" s="111">
+      <c r="B63" s="215" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" s="114">
         <f>SUM(F63:BB63)</f>
         <v>1.5</v>
       </c>
-      <c r="D63" s="111">
+      <c r="D63" s="114">
         <f>SUM(F64:BB64)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="112">
-        <f t="shared" si="3"/>
+      <c r="E63" s="115">
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="F63" s="30"/>
@@ -6661,9 +6685,9 @@
       <c r="N63" s="31"/>
       <c r="O63" s="32"/>
       <c r="P63" s="25"/>
-      <c r="Q63" s="58"/>
-      <c r="R63" s="58"/>
-      <c r="S63" s="58"/>
+      <c r="Q63" s="57"/>
+      <c r="R63" s="57"/>
+      <c r="S63" s="57"/>
       <c r="T63" s="26"/>
       <c r="U63" s="30"/>
       <c r="V63" s="31"/>
@@ -6681,7 +6705,7 @@
       <c r="AH63" s="31"/>
       <c r="AI63" s="32"/>
       <c r="AJ63" s="30"/>
-      <c r="AK63" s="70">
+      <c r="AK63" s="69">
         <v>1.5</v>
       </c>
       <c r="AL63" s="31"/>
@@ -6703,11 +6727,11 @@
       <c r="BB63" s="32"/>
     </row>
     <row r="64" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="207"/>
-      <c r="B64" s="212"/>
-      <c r="C64" s="102"/>
-      <c r="D64" s="102"/>
-      <c r="E64" s="106"/>
+      <c r="A64" s="211"/>
+      <c r="B64" s="216"/>
+      <c r="C64" s="98"/>
+      <c r="D64" s="98"/>
+      <c r="E64" s="102"/>
       <c r="F64" s="27"/>
       <c r="G64" s="28"/>
       <c r="H64" s="28"/>
@@ -6759,22 +6783,22 @@
       <c r="BB64" s="29"/>
     </row>
     <row r="65" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="210" t="b">
+      <c r="A65" s="214" t="b">
         <v>0</v>
       </c>
-      <c r="B65" s="213" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="111">
+      <c r="B65" s="217" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" s="114">
         <f>SUM(F65:BB65)</f>
         <v>4.5</v>
       </c>
-      <c r="D65" s="111">
+      <c r="D65" s="114">
         <f>SUM(F66:BB66)</f>
         <v>0</v>
       </c>
-      <c r="E65" s="112">
-        <f t="shared" si="3"/>
+      <c r="E65" s="115">
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
       <c r="F65" s="30"/>
@@ -6788,10 +6812,10 @@
       <c r="N65" s="31"/>
       <c r="O65" s="32"/>
       <c r="P65" s="25"/>
-      <c r="Q65" s="58"/>
-      <c r="R65" s="58"/>
-      <c r="S65" s="58"/>
-      <c r="T65" s="276"/>
+      <c r="Q65" s="57"/>
+      <c r="R65" s="57"/>
+      <c r="S65" s="57"/>
+      <c r="T65" s="77"/>
       <c r="U65" s="30"/>
       <c r="V65" s="31"/>
       <c r="W65" s="31"/>
@@ -6809,14 +6833,14 @@
       <c r="AI65" s="32"/>
       <c r="AJ65" s="30"/>
       <c r="AK65" s="31"/>
-      <c r="AL65" s="70">
+      <c r="AL65" s="69">
         <v>1.5</v>
       </c>
-      <c r="AM65" s="70">
+      <c r="AM65" s="69">
         <v>1.5</v>
       </c>
       <c r="AN65" s="32"/>
-      <c r="AO65" s="71">
+      <c r="AO65" s="70">
         <v>1.5</v>
       </c>
       <c r="AP65" s="31"/>
@@ -6834,11 +6858,11 @@
       <c r="BB65" s="32"/>
     </row>
     <row r="66" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A66" s="207"/>
-      <c r="B66" s="209"/>
-      <c r="C66" s="102"/>
-      <c r="D66" s="102"/>
-      <c r="E66" s="106"/>
+      <c r="A66" s="211"/>
+      <c r="B66" s="213"/>
+      <c r="C66" s="98"/>
+      <c r="D66" s="98"/>
+      <c r="E66" s="102"/>
       <c r="F66" s="27"/>
       <c r="G66" s="28"/>
       <c r="H66" s="28"/>
@@ -6890,146 +6914,146 @@
       <c r="BB66" s="29"/>
     </row>
     <row r="67" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="224" t="b">
+      <c r="A67" s="228" t="b">
         <v>0</v>
       </c>
-      <c r="B67" s="226" t="s">
+      <c r="B67" s="230" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="228">
+      <c r="C67" s="232">
         <f>SUM(C69:C74)</f>
         <v>3.5</v>
       </c>
-      <c r="D67" s="228">
+      <c r="D67" s="232">
         <f>SUM(D69:D74)</f>
         <v>0</v>
       </c>
-      <c r="E67" s="228">
+      <c r="E67" s="232">
         <f>(C67-D67)</f>
         <v>3.5</v>
       </c>
-      <c r="F67" s="214"/>
-      <c r="G67" s="215"/>
-      <c r="H67" s="215"/>
-      <c r="I67" s="215"/>
-      <c r="J67" s="215"/>
-      <c r="K67" s="215"/>
-      <c r="L67" s="215"/>
-      <c r="M67" s="215"/>
-      <c r="N67" s="215"/>
-      <c r="O67" s="215"/>
-      <c r="P67" s="215"/>
-      <c r="Q67" s="215"/>
-      <c r="R67" s="215"/>
-      <c r="S67" s="215"/>
-      <c r="T67" s="215"/>
-      <c r="U67" s="215"/>
-      <c r="V67" s="215"/>
-      <c r="W67" s="215"/>
-      <c r="X67" s="215"/>
-      <c r="Y67" s="215"/>
-      <c r="Z67" s="215"/>
-      <c r="AA67" s="215"/>
-      <c r="AB67" s="215"/>
-      <c r="AC67" s="215"/>
-      <c r="AD67" s="215"/>
-      <c r="AE67" s="215"/>
-      <c r="AF67" s="215"/>
-      <c r="AG67" s="215"/>
-      <c r="AH67" s="215"/>
-      <c r="AI67" s="215"/>
-      <c r="AJ67" s="215"/>
-      <c r="AK67" s="215"/>
-      <c r="AL67" s="215"/>
-      <c r="AM67" s="215"/>
-      <c r="AN67" s="215"/>
-      <c r="AO67" s="215"/>
-      <c r="AP67" s="215"/>
-      <c r="AQ67" s="215"/>
-      <c r="AR67" s="215"/>
-      <c r="AS67" s="215"/>
-      <c r="AT67" s="215"/>
-      <c r="AU67" s="215"/>
-      <c r="AV67" s="215"/>
-      <c r="AW67" s="215"/>
-      <c r="AX67" s="215"/>
-      <c r="AY67" s="215"/>
-      <c r="AZ67" s="215"/>
-      <c r="BA67" s="215"/>
-      <c r="BB67" s="216"/>
+      <c r="F67" s="218"/>
+      <c r="G67" s="219"/>
+      <c r="H67" s="219"/>
+      <c r="I67" s="219"/>
+      <c r="J67" s="219"/>
+      <c r="K67" s="219"/>
+      <c r="L67" s="219"/>
+      <c r="M67" s="219"/>
+      <c r="N67" s="219"/>
+      <c r="O67" s="219"/>
+      <c r="P67" s="219"/>
+      <c r="Q67" s="219"/>
+      <c r="R67" s="219"/>
+      <c r="S67" s="219"/>
+      <c r="T67" s="219"/>
+      <c r="U67" s="219"/>
+      <c r="V67" s="219"/>
+      <c r="W67" s="219"/>
+      <c r="X67" s="219"/>
+      <c r="Y67" s="219"/>
+      <c r="Z67" s="219"/>
+      <c r="AA67" s="219"/>
+      <c r="AB67" s="219"/>
+      <c r="AC67" s="219"/>
+      <c r="AD67" s="219"/>
+      <c r="AE67" s="219"/>
+      <c r="AF67" s="219"/>
+      <c r="AG67" s="219"/>
+      <c r="AH67" s="219"/>
+      <c r="AI67" s="219"/>
+      <c r="AJ67" s="219"/>
+      <c r="AK67" s="219"/>
+      <c r="AL67" s="219"/>
+      <c r="AM67" s="219"/>
+      <c r="AN67" s="219"/>
+      <c r="AO67" s="219"/>
+      <c r="AP67" s="219"/>
+      <c r="AQ67" s="219"/>
+      <c r="AR67" s="219"/>
+      <c r="AS67" s="219"/>
+      <c r="AT67" s="219"/>
+      <c r="AU67" s="219"/>
+      <c r="AV67" s="219"/>
+      <c r="AW67" s="219"/>
+      <c r="AX67" s="219"/>
+      <c r="AY67" s="219"/>
+      <c r="AZ67" s="219"/>
+      <c r="BA67" s="219"/>
+      <c r="BB67" s="220"/>
     </row>
     <row r="68" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A68" s="225"/>
-      <c r="B68" s="227"/>
-      <c r="C68" s="229"/>
-      <c r="D68" s="229"/>
-      <c r="E68" s="230"/>
-      <c r="F68" s="217"/>
-      <c r="G68" s="218"/>
-      <c r="H68" s="218"/>
-      <c r="I68" s="218"/>
-      <c r="J68" s="218"/>
-      <c r="K68" s="218"/>
-      <c r="L68" s="218"/>
-      <c r="M68" s="218"/>
-      <c r="N68" s="218"/>
-      <c r="O68" s="218"/>
-      <c r="P68" s="218"/>
-      <c r="Q68" s="218"/>
-      <c r="R68" s="218"/>
-      <c r="S68" s="218"/>
-      <c r="T68" s="218"/>
-      <c r="U68" s="218"/>
-      <c r="V68" s="218"/>
-      <c r="W68" s="218"/>
-      <c r="X68" s="218"/>
-      <c r="Y68" s="218"/>
-      <c r="Z68" s="218"/>
-      <c r="AA68" s="218"/>
-      <c r="AB68" s="218"/>
-      <c r="AC68" s="218"/>
-      <c r="AD68" s="218"/>
-      <c r="AE68" s="218"/>
-      <c r="AF68" s="218"/>
-      <c r="AG68" s="218"/>
-      <c r="AH68" s="218"/>
-      <c r="AI68" s="218"/>
-      <c r="AJ68" s="218"/>
-      <c r="AK68" s="218"/>
-      <c r="AL68" s="218"/>
-      <c r="AM68" s="218"/>
-      <c r="AN68" s="218"/>
-      <c r="AO68" s="218"/>
-      <c r="AP68" s="218"/>
-      <c r="AQ68" s="218"/>
-      <c r="AR68" s="218"/>
-      <c r="AS68" s="218"/>
-      <c r="AT68" s="218"/>
-      <c r="AU68" s="218"/>
-      <c r="AV68" s="218"/>
-      <c r="AW68" s="218"/>
-      <c r="AX68" s="218"/>
-      <c r="AY68" s="218"/>
-      <c r="AZ68" s="218"/>
-      <c r="BA68" s="218"/>
-      <c r="BB68" s="219"/>
+      <c r="A68" s="229"/>
+      <c r="B68" s="231"/>
+      <c r="C68" s="233"/>
+      <c r="D68" s="233"/>
+      <c r="E68" s="234"/>
+      <c r="F68" s="221"/>
+      <c r="G68" s="222"/>
+      <c r="H68" s="222"/>
+      <c r="I68" s="222"/>
+      <c r="J68" s="222"/>
+      <c r="K68" s="222"/>
+      <c r="L68" s="222"/>
+      <c r="M68" s="222"/>
+      <c r="N68" s="222"/>
+      <c r="O68" s="222"/>
+      <c r="P68" s="222"/>
+      <c r="Q68" s="222"/>
+      <c r="R68" s="222"/>
+      <c r="S68" s="222"/>
+      <c r="T68" s="222"/>
+      <c r="U68" s="222"/>
+      <c r="V68" s="222"/>
+      <c r="W68" s="222"/>
+      <c r="X68" s="222"/>
+      <c r="Y68" s="222"/>
+      <c r="Z68" s="222"/>
+      <c r="AA68" s="222"/>
+      <c r="AB68" s="222"/>
+      <c r="AC68" s="222"/>
+      <c r="AD68" s="222"/>
+      <c r="AE68" s="222"/>
+      <c r="AF68" s="222"/>
+      <c r="AG68" s="222"/>
+      <c r="AH68" s="222"/>
+      <c r="AI68" s="222"/>
+      <c r="AJ68" s="222"/>
+      <c r="AK68" s="222"/>
+      <c r="AL68" s="222"/>
+      <c r="AM68" s="222"/>
+      <c r="AN68" s="222"/>
+      <c r="AO68" s="222"/>
+      <c r="AP68" s="222"/>
+      <c r="AQ68" s="222"/>
+      <c r="AR68" s="222"/>
+      <c r="AS68" s="222"/>
+      <c r="AT68" s="222"/>
+      <c r="AU68" s="222"/>
+      <c r="AV68" s="222"/>
+      <c r="AW68" s="222"/>
+      <c r="AX68" s="222"/>
+      <c r="AY68" s="222"/>
+      <c r="AZ68" s="222"/>
+      <c r="BA68" s="222"/>
+      <c r="BB68" s="223"/>
     </row>
     <row r="69" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="220" t="b">
+      <c r="A69" s="224" t="b">
         <v>0</v>
       </c>
-      <c r="B69" s="222" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="111">
+      <c r="B69" s="226" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" s="114">
         <f>SUM(F69:BB69)</f>
         <v>1.5</v>
       </c>
-      <c r="D69" s="111">
+      <c r="D69" s="114">
         <f>SUM(F70:BB70)</f>
         <v>0</v>
       </c>
-      <c r="E69" s="105">
+      <c r="E69" s="101">
         <f>(AVERAGE(C69,C70)-AVERAGE(D69,D70) )</f>
         <v>1.5</v>
       </c>
@@ -7044,9 +7068,9 @@
       <c r="N69" s="31"/>
       <c r="O69" s="32"/>
       <c r="P69" s="25"/>
-      <c r="Q69" s="58"/>
-      <c r="R69" s="58"/>
-      <c r="S69" s="58"/>
+      <c r="Q69" s="57"/>
+      <c r="R69" s="57"/>
+      <c r="S69" s="57"/>
       <c r="T69" s="26"/>
       <c r="U69" s="30"/>
       <c r="V69" s="31"/>
@@ -7069,7 +7093,7 @@
       <c r="AM69" s="31"/>
       <c r="AN69" s="32"/>
       <c r="AO69" s="30"/>
-      <c r="AP69" s="70">
+      <c r="AP69" s="69">
         <v>1.5</v>
       </c>
       <c r="AQ69" s="31"/>
@@ -7086,11 +7110,11 @@
       <c r="BB69" s="32"/>
     </row>
     <row r="70" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="221"/>
-      <c r="B70" s="223"/>
-      <c r="C70" s="102"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="106"/>
+      <c r="A70" s="225"/>
+      <c r="B70" s="227"/>
+      <c r="C70" s="98"/>
+      <c r="D70" s="98"/>
+      <c r="E70" s="102"/>
       <c r="F70" s="27"/>
       <c r="G70" s="28"/>
       <c r="H70" s="28"/>
@@ -7142,22 +7166,22 @@
       <c r="BB70" s="29"/>
     </row>
     <row r="71" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="242" t="b">
+      <c r="A71" s="246" t="b">
         <v>0</v>
       </c>
-      <c r="B71" s="243" t="s">
-        <v>46</v>
-      </c>
-      <c r="C71" s="111">
+      <c r="B71" s="247" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" s="114">
         <f>SUM(F71:BB71)</f>
         <v>1</v>
       </c>
-      <c r="D71" s="111">
+      <c r="D71" s="114">
         <f>SUM(F72:BB72)</f>
         <v>0</v>
       </c>
-      <c r="E71" s="112">
-        <f t="shared" ref="E71" si="4">(AVERAGE(C71,C72)-AVERAGE(D71,D72) )</f>
+      <c r="E71" s="115">
+        <f>(AVERAGE(C71,C72)-AVERAGE(D71,D72) )</f>
         <v>1</v>
       </c>
       <c r="F71" s="30"/>
@@ -7171,9 +7195,9 @@
       <c r="N71" s="31"/>
       <c r="O71" s="32"/>
       <c r="P71" s="25"/>
-      <c r="Q71" s="58"/>
-      <c r="R71" s="58"/>
-      <c r="S71" s="58"/>
+      <c r="Q71" s="57"/>
+      <c r="R71" s="57"/>
+      <c r="S71" s="57"/>
       <c r="T71" s="26"/>
       <c r="U71" s="30"/>
       <c r="V71" s="31"/>
@@ -7197,7 +7221,7 @@
       <c r="AN71" s="32"/>
       <c r="AO71" s="30"/>
       <c r="AP71" s="31"/>
-      <c r="AQ71" s="70">
+      <c r="AQ71" s="69">
         <v>1</v>
       </c>
       <c r="AR71" s="31"/>
@@ -7213,11 +7237,11 @@
       <c r="BB71" s="32"/>
     </row>
     <row r="72" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="221"/>
-      <c r="B72" s="244"/>
-      <c r="C72" s="102"/>
-      <c r="D72" s="102"/>
-      <c r="E72" s="106"/>
+      <c r="A72" s="225"/>
+      <c r="B72" s="248"/>
+      <c r="C72" s="98"/>
+      <c r="D72" s="98"/>
+      <c r="E72" s="102"/>
       <c r="F72" s="27"/>
       <c r="G72" s="28"/>
       <c r="H72" s="28"/>
@@ -7269,91 +7293,91 @@
       <c r="BB72" s="29"/>
     </row>
     <row r="73" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="245" t="b">
+      <c r="A73" s="249" t="b">
         <v>0</v>
       </c>
-      <c r="B73" s="246" t="s">
-        <v>47</v>
-      </c>
-      <c r="C73" s="111">
+      <c r="B73" s="250" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="114">
         <f>SUM(F73:BB73)</f>
         <v>1</v>
       </c>
-      <c r="D73" s="111">
+      <c r="D73" s="114">
         <f>SUM(F74:BB74)</f>
         <v>0</v>
       </c>
-      <c r="E73" s="112">
+      <c r="E73" s="115">
         <f>(AVERAGE(C73,C74)-AVERAGE(D73,D74) )</f>
         <v>1</v>
       </c>
       <c r="F73" s="25"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
       <c r="J73" s="26"/>
       <c r="K73" s="25"/>
-      <c r="L73" s="58"/>
-      <c r="M73" s="58"/>
-      <c r="N73" s="58"/>
+      <c r="L73" s="57"/>
+      <c r="M73" s="57"/>
+      <c r="N73" s="57"/>
       <c r="O73" s="26"/>
       <c r="P73" s="25"/>
-      <c r="Q73" s="58"/>
-      <c r="R73" s="58"/>
-      <c r="S73" s="58"/>
+      <c r="Q73" s="57"/>
+      <c r="R73" s="57"/>
+      <c r="S73" s="57"/>
       <c r="T73" s="26"/>
       <c r="U73" s="25"/>
-      <c r="V73" s="58"/>
-      <c r="W73" s="58"/>
-      <c r="X73" s="58"/>
+      <c r="V73" s="57"/>
+      <c r="W73" s="57"/>
+      <c r="X73" s="57"/>
       <c r="Y73" s="26"/>
       <c r="Z73" s="25"/>
-      <c r="AA73" s="58"/>
-      <c r="AB73" s="58"/>
-      <c r="AC73" s="58"/>
+      <c r="AA73" s="57"/>
+      <c r="AB73" s="57"/>
+      <c r="AC73" s="57"/>
       <c r="AD73" s="26"/>
       <c r="AE73" s="25"/>
-      <c r="AF73" s="58"/>
-      <c r="AG73" s="58"/>
-      <c r="AH73" s="58"/>
+      <c r="AF73" s="57"/>
+      <c r="AG73" s="57"/>
+      <c r="AH73" s="57"/>
       <c r="AI73" s="26"/>
       <c r="AJ73" s="25"/>
-      <c r="AK73" s="58"/>
-      <c r="AL73" s="58"/>
-      <c r="AM73" s="58"/>
+      <c r="AK73" s="57"/>
+      <c r="AL73" s="57"/>
+      <c r="AM73" s="57"/>
       <c r="AN73" s="26"/>
       <c r="AO73" s="25"/>
-      <c r="AP73" s="58"/>
-      <c r="AQ73" s="66">
+      <c r="AP73" s="57"/>
+      <c r="AQ73" s="65">
         <v>1</v>
       </c>
-      <c r="AR73" s="58"/>
+      <c r="AR73" s="57"/>
       <c r="AS73" s="26"/>
       <c r="AT73" s="25"/>
-      <c r="AU73" s="58"/>
+      <c r="AU73" s="57"/>
       <c r="AV73" s="25"/>
-      <c r="AW73" s="58"/>
-      <c r="AX73" s="58"/>
-      <c r="AY73" s="58"/>
+      <c r="AW73" s="57"/>
+      <c r="AX73" s="57"/>
+      <c r="AY73" s="57"/>
       <c r="AZ73" s="26"/>
       <c r="BA73" s="25"/>
       <c r="BB73" s="26"/>
     </row>
     <row r="74" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A74" s="245"/>
-      <c r="B74" s="247"/>
-      <c r="C74" s="102"/>
-      <c r="D74" s="102"/>
-      <c r="E74" s="143"/>
+      <c r="A74" s="249"/>
+      <c r="B74" s="251"/>
+      <c r="C74" s="98"/>
+      <c r="D74" s="98"/>
+      <c r="E74" s="147"/>
       <c r="F74" s="25"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="58"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
       <c r="J74" s="26"/>
       <c r="K74" s="25"/>
-      <c r="L74" s="58"/>
-      <c r="M74" s="58"/>
-      <c r="N74" s="58"/>
+      <c r="L74" s="57"/>
+      <c r="M74" s="57"/>
+      <c r="N74" s="57"/>
       <c r="O74" s="26"/>
       <c r="P74" s="27"/>
       <c r="Q74" s="28"/>
@@ -7361,181 +7385,181 @@
       <c r="S74" s="28"/>
       <c r="T74" s="29"/>
       <c r="U74" s="25"/>
-      <c r="V74" s="58"/>
-      <c r="W74" s="58"/>
-      <c r="X74" s="58"/>
+      <c r="V74" s="57"/>
+      <c r="W74" s="57"/>
+      <c r="X74" s="57"/>
       <c r="Y74" s="26"/>
       <c r="Z74" s="25"/>
-      <c r="AA74" s="58"/>
-      <c r="AB74" s="58"/>
-      <c r="AC74" s="58"/>
+      <c r="AA74" s="57"/>
+      <c r="AB74" s="57"/>
+      <c r="AC74" s="57"/>
       <c r="AD74" s="26"/>
       <c r="AE74" s="25"/>
-      <c r="AF74" s="58"/>
-      <c r="AG74" s="58"/>
-      <c r="AH74" s="58"/>
+      <c r="AF74" s="57"/>
+      <c r="AG74" s="57"/>
+      <c r="AH74" s="57"/>
       <c r="AI74" s="26"/>
       <c r="AJ74" s="25"/>
-      <c r="AK74" s="58"/>
-      <c r="AL74" s="58"/>
-      <c r="AM74" s="58"/>
+      <c r="AK74" s="57"/>
+      <c r="AL74" s="57"/>
+      <c r="AM74" s="57"/>
       <c r="AN74" s="26"/>
       <c r="AO74" s="25"/>
-      <c r="AP74" s="58"/>
-      <c r="AQ74" s="58"/>
-      <c r="AR74" s="58"/>
+      <c r="AP74" s="57"/>
+      <c r="AQ74" s="57"/>
+      <c r="AR74" s="57"/>
       <c r="AS74" s="26"/>
       <c r="AT74" s="25"/>
-      <c r="AU74" s="58"/>
+      <c r="AU74" s="57"/>
       <c r="AV74" s="25"/>
-      <c r="AW74" s="58"/>
-      <c r="AX74" s="58"/>
-      <c r="AY74" s="58"/>
+      <c r="AW74" s="57"/>
+      <c r="AX74" s="57"/>
+      <c r="AY74" s="57"/>
       <c r="AZ74" s="26"/>
       <c r="BA74" s="25"/>
       <c r="BB74" s="26"/>
     </row>
     <row r="75" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="231" t="b">
+      <c r="A75" s="235" t="b">
         <v>0</v>
       </c>
-      <c r="B75" s="233" t="s">
+      <c r="B75" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="C75" s="127">
+      <c r="C75" s="130">
         <f>SUM(C77:C86)</f>
         <v>11</v>
       </c>
-      <c r="D75" s="127">
+      <c r="D75" s="130">
         <f>SUM(D77:D86)</f>
         <v>0</v>
       </c>
-      <c r="E75" s="127">
+      <c r="E75" s="130">
         <f>(C75-D75)</f>
         <v>11</v>
       </c>
-      <c r="F75" s="236"/>
-      <c r="G75" s="237"/>
-      <c r="H75" s="237"/>
-      <c r="I75" s="237"/>
-      <c r="J75" s="237"/>
-      <c r="K75" s="237"/>
-      <c r="L75" s="237"/>
-      <c r="M75" s="237"/>
-      <c r="N75" s="237"/>
-      <c r="O75" s="237"/>
-      <c r="P75" s="237"/>
-      <c r="Q75" s="237"/>
-      <c r="R75" s="237"/>
-      <c r="S75" s="237"/>
-      <c r="T75" s="237"/>
-      <c r="U75" s="237"/>
-      <c r="V75" s="237"/>
-      <c r="W75" s="237"/>
-      <c r="X75" s="237"/>
-      <c r="Y75" s="237"/>
-      <c r="Z75" s="237"/>
-      <c r="AA75" s="237"/>
-      <c r="AB75" s="237"/>
-      <c r="AC75" s="237"/>
-      <c r="AD75" s="237"/>
-      <c r="AE75" s="237"/>
-      <c r="AF75" s="237"/>
-      <c r="AG75" s="237"/>
-      <c r="AH75" s="237"/>
-      <c r="AI75" s="237"/>
-      <c r="AJ75" s="237"/>
-      <c r="AK75" s="237"/>
-      <c r="AL75" s="237"/>
-      <c r="AM75" s="237"/>
-      <c r="AN75" s="237"/>
-      <c r="AO75" s="237"/>
-      <c r="AP75" s="237"/>
-      <c r="AQ75" s="237"/>
-      <c r="AR75" s="237"/>
-      <c r="AS75" s="237"/>
-      <c r="AT75" s="237"/>
-      <c r="AU75" s="237"/>
-      <c r="AV75" s="237"/>
-      <c r="AW75" s="237"/>
-      <c r="AX75" s="237"/>
-      <c r="AY75" s="237"/>
-      <c r="AZ75" s="237"/>
-      <c r="BA75" s="237"/>
-      <c r="BB75" s="238"/>
+      <c r="F75" s="240"/>
+      <c r="G75" s="241"/>
+      <c r="H75" s="241"/>
+      <c r="I75" s="241"/>
+      <c r="J75" s="241"/>
+      <c r="K75" s="241"/>
+      <c r="L75" s="241"/>
+      <c r="M75" s="241"/>
+      <c r="N75" s="241"/>
+      <c r="O75" s="241"/>
+      <c r="P75" s="241"/>
+      <c r="Q75" s="241"/>
+      <c r="R75" s="241"/>
+      <c r="S75" s="241"/>
+      <c r="T75" s="241"/>
+      <c r="U75" s="241"/>
+      <c r="V75" s="241"/>
+      <c r="W75" s="241"/>
+      <c r="X75" s="241"/>
+      <c r="Y75" s="241"/>
+      <c r="Z75" s="241"/>
+      <c r="AA75" s="241"/>
+      <c r="AB75" s="241"/>
+      <c r="AC75" s="241"/>
+      <c r="AD75" s="241"/>
+      <c r="AE75" s="241"/>
+      <c r="AF75" s="241"/>
+      <c r="AG75" s="241"/>
+      <c r="AH75" s="241"/>
+      <c r="AI75" s="241"/>
+      <c r="AJ75" s="241"/>
+      <c r="AK75" s="241"/>
+      <c r="AL75" s="241"/>
+      <c r="AM75" s="241"/>
+      <c r="AN75" s="241"/>
+      <c r="AO75" s="241"/>
+      <c r="AP75" s="241"/>
+      <c r="AQ75" s="241"/>
+      <c r="AR75" s="241"/>
+      <c r="AS75" s="241"/>
+      <c r="AT75" s="241"/>
+      <c r="AU75" s="241"/>
+      <c r="AV75" s="241"/>
+      <c r="AW75" s="241"/>
+      <c r="AX75" s="241"/>
+      <c r="AY75" s="241"/>
+      <c r="AZ75" s="241"/>
+      <c r="BA75" s="241"/>
+      <c r="BB75" s="242"/>
     </row>
     <row r="76" spans="1:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A76" s="232"/>
-      <c r="B76" s="234"/>
-      <c r="C76" s="235"/>
-      <c r="D76" s="235"/>
-      <c r="E76" s="128"/>
-      <c r="F76" s="239"/>
-      <c r="G76" s="240"/>
-      <c r="H76" s="240"/>
-      <c r="I76" s="240"/>
-      <c r="J76" s="240"/>
-      <c r="K76" s="240"/>
-      <c r="L76" s="240"/>
-      <c r="M76" s="240"/>
-      <c r="N76" s="240"/>
-      <c r="O76" s="240"/>
-      <c r="P76" s="240"/>
-      <c r="Q76" s="240"/>
-      <c r="R76" s="240"/>
-      <c r="S76" s="240"/>
-      <c r="T76" s="240"/>
-      <c r="U76" s="240"/>
-      <c r="V76" s="240"/>
-      <c r="W76" s="240"/>
-      <c r="X76" s="240"/>
-      <c r="Y76" s="240"/>
-      <c r="Z76" s="240"/>
-      <c r="AA76" s="240"/>
-      <c r="AB76" s="240"/>
-      <c r="AC76" s="240"/>
-      <c r="AD76" s="240"/>
-      <c r="AE76" s="240"/>
-      <c r="AF76" s="240"/>
-      <c r="AG76" s="240"/>
-      <c r="AH76" s="240"/>
-      <c r="AI76" s="240"/>
-      <c r="AJ76" s="240"/>
-      <c r="AK76" s="240"/>
-      <c r="AL76" s="240"/>
-      <c r="AM76" s="240"/>
-      <c r="AN76" s="240"/>
-      <c r="AO76" s="240"/>
-      <c r="AP76" s="240"/>
-      <c r="AQ76" s="240"/>
-      <c r="AR76" s="240"/>
-      <c r="AS76" s="240"/>
-      <c r="AT76" s="240"/>
-      <c r="AU76" s="240"/>
-      <c r="AV76" s="240"/>
-      <c r="AW76" s="240"/>
-      <c r="AX76" s="240"/>
-      <c r="AY76" s="240"/>
-      <c r="AZ76" s="240"/>
-      <c r="BA76" s="240"/>
-      <c r="BB76" s="241"/>
+      <c r="A76" s="236"/>
+      <c r="B76" s="238"/>
+      <c r="C76" s="239"/>
+      <c r="D76" s="239"/>
+      <c r="E76" s="131"/>
+      <c r="F76" s="243"/>
+      <c r="G76" s="244"/>
+      <c r="H76" s="244"/>
+      <c r="I76" s="244"/>
+      <c r="J76" s="244"/>
+      <c r="K76" s="244"/>
+      <c r="L76" s="244"/>
+      <c r="M76" s="244"/>
+      <c r="N76" s="244"/>
+      <c r="O76" s="244"/>
+      <c r="P76" s="244"/>
+      <c r="Q76" s="244"/>
+      <c r="R76" s="244"/>
+      <c r="S76" s="244"/>
+      <c r="T76" s="244"/>
+      <c r="U76" s="244"/>
+      <c r="V76" s="244"/>
+      <c r="W76" s="244"/>
+      <c r="X76" s="244"/>
+      <c r="Y76" s="244"/>
+      <c r="Z76" s="244"/>
+      <c r="AA76" s="244"/>
+      <c r="AB76" s="244"/>
+      <c r="AC76" s="244"/>
+      <c r="AD76" s="244"/>
+      <c r="AE76" s="244"/>
+      <c r="AF76" s="244"/>
+      <c r="AG76" s="244"/>
+      <c r="AH76" s="244"/>
+      <c r="AI76" s="244"/>
+      <c r="AJ76" s="244"/>
+      <c r="AK76" s="244"/>
+      <c r="AL76" s="244"/>
+      <c r="AM76" s="244"/>
+      <c r="AN76" s="244"/>
+      <c r="AO76" s="244"/>
+      <c r="AP76" s="244"/>
+      <c r="AQ76" s="244"/>
+      <c r="AR76" s="244"/>
+      <c r="AS76" s="244"/>
+      <c r="AT76" s="244"/>
+      <c r="AU76" s="244"/>
+      <c r="AV76" s="244"/>
+      <c r="AW76" s="244"/>
+      <c r="AX76" s="244"/>
+      <c r="AY76" s="244"/>
+      <c r="AZ76" s="244"/>
+      <c r="BA76" s="244"/>
+      <c r="BB76" s="245"/>
     </row>
     <row r="77" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="248" t="b">
+      <c r="A77" s="252" t="b">
         <v>0</v>
       </c>
-      <c r="B77" s="250" t="s">
-        <v>48</v>
-      </c>
-      <c r="C77" s="111">
+      <c r="B77" s="254" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="114">
         <f>SUM(F77:BB77)</f>
         <v>1.5</v>
       </c>
-      <c r="D77" s="111">
+      <c r="D77" s="114">
         <f>SUM(F78:BB78)</f>
         <v>0</v>
       </c>
-      <c r="E77" s="105">
+      <c r="E77" s="101">
         <f>(AVERAGE(C77,C78)-AVERAGE(D77,D78) )</f>
         <v>1.5</v>
       </c>
@@ -7550,9 +7574,9 @@
       <c r="N77" s="39"/>
       <c r="O77" s="40"/>
       <c r="P77" s="25"/>
-      <c r="Q77" s="58"/>
-      <c r="R77" s="58"/>
-      <c r="S77" s="58"/>
+      <c r="Q77" s="57"/>
+      <c r="R77" s="57"/>
+      <c r="S77" s="57"/>
       <c r="T77" s="26"/>
       <c r="U77" s="38"/>
       <c r="V77" s="39"/>
@@ -7577,7 +7601,7 @@
       <c r="AO77" s="38"/>
       <c r="AP77" s="39"/>
       <c r="AQ77" s="39"/>
-      <c r="AR77" s="72">
+      <c r="AR77" s="71">
         <v>1.5</v>
       </c>
       <c r="AS77" s="40"/>
@@ -7592,11 +7616,11 @@
       <c r="BB77" s="40"/>
     </row>
     <row r="78" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="249"/>
-      <c r="B78" s="251"/>
-      <c r="C78" s="102"/>
-      <c r="D78" s="102"/>
-      <c r="E78" s="106"/>
+      <c r="A78" s="253"/>
+      <c r="B78" s="255"/>
+      <c r="C78" s="98"/>
+      <c r="D78" s="98"/>
+      <c r="E78" s="102"/>
       <c r="F78" s="27"/>
       <c r="G78" s="28"/>
       <c r="H78" s="28"/>
@@ -7648,82 +7672,82 @@
       <c r="BB78" s="29"/>
     </row>
     <row r="79" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="252" t="b">
+      <c r="A79" s="256" t="b">
         <v>0</v>
       </c>
-      <c r="B79" s="253" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="111">
+      <c r="B79" s="257" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="114">
         <f>SUM(F79:BB79)</f>
         <v>1</v>
       </c>
-      <c r="D79" s="111">
+      <c r="D79" s="114">
         <f>SUM(F80:BB80)</f>
         <v>0</v>
       </c>
-      <c r="E79" s="112">
-        <f t="shared" ref="E79:E83" si="5">(AVERAGE(C79,C80)-AVERAGE(D79,D80) )</f>
+      <c r="E79" s="115">
+        <f>(AVERAGE(C79,C80)-AVERAGE(D79,D80) )</f>
         <v>1</v>
       </c>
       <c r="F79" s="25"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="58"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
       <c r="J79" s="26"/>
       <c r="K79" s="25"/>
-      <c r="L79" s="58"/>
-      <c r="M79" s="58"/>
-      <c r="N79" s="58"/>
+      <c r="L79" s="57"/>
+      <c r="M79" s="57"/>
+      <c r="N79" s="57"/>
       <c r="O79" s="26"/>
       <c r="P79" s="25"/>
-      <c r="Q79" s="58"/>
-      <c r="R79" s="58"/>
-      <c r="S79" s="58"/>
+      <c r="Q79" s="57"/>
+      <c r="R79" s="57"/>
+      <c r="S79" s="57"/>
       <c r="T79" s="26"/>
       <c r="U79" s="25"/>
-      <c r="V79" s="58"/>
-      <c r="W79" s="58"/>
-      <c r="X79" s="58"/>
+      <c r="V79" s="57"/>
+      <c r="W79" s="57"/>
+      <c r="X79" s="57"/>
       <c r="Y79" s="26"/>
       <c r="Z79" s="25"/>
-      <c r="AA79" s="58"/>
-      <c r="AB79" s="58"/>
-      <c r="AC79" s="58"/>
+      <c r="AA79" s="57"/>
+      <c r="AB79" s="57"/>
+      <c r="AC79" s="57"/>
       <c r="AD79" s="26"/>
       <c r="AE79" s="25"/>
-      <c r="AF79" s="58"/>
-      <c r="AG79" s="58"/>
-      <c r="AH79" s="58"/>
+      <c r="AF79" s="57"/>
+      <c r="AG79" s="57"/>
+      <c r="AH79" s="57"/>
       <c r="AI79" s="26"/>
       <c r="AJ79" s="25"/>
-      <c r="AK79" s="58"/>
-      <c r="AL79" s="58"/>
-      <c r="AM79" s="58"/>
+      <c r="AK79" s="57"/>
+      <c r="AL79" s="57"/>
+      <c r="AM79" s="57"/>
       <c r="AN79" s="26"/>
       <c r="AO79" s="25"/>
-      <c r="AP79" s="58"/>
-      <c r="AQ79" s="58"/>
-      <c r="AR79" s="58"/>
+      <c r="AP79" s="57"/>
+      <c r="AQ79" s="57"/>
+      <c r="AR79" s="57"/>
       <c r="AS79" s="26"/>
-      <c r="AT79" s="64">
+      <c r="AT79" s="63">
         <v>1</v>
       </c>
-      <c r="AU79" s="58"/>
+      <c r="AU79" s="57"/>
       <c r="AV79" s="25"/>
-      <c r="AW79" s="58"/>
-      <c r="AX79" s="58"/>
-      <c r="AY79" s="58"/>
+      <c r="AW79" s="57"/>
+      <c r="AX79" s="57"/>
+      <c r="AY79" s="57"/>
       <c r="AZ79" s="26"/>
       <c r="BA79" s="25"/>
       <c r="BB79" s="26"/>
     </row>
     <row r="80" spans="1:54" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="249"/>
-      <c r="B80" s="251"/>
-      <c r="C80" s="102"/>
-      <c r="D80" s="102"/>
-      <c r="E80" s="106"/>
+      <c r="A80" s="253"/>
+      <c r="B80" s="255"/>
+      <c r="C80" s="98"/>
+      <c r="D80" s="98"/>
+      <c r="E80" s="102"/>
       <c r="F80" s="27"/>
       <c r="G80" s="28"/>
       <c r="H80" s="28"/>
@@ -7775,22 +7799,22 @@
       <c r="BB80" s="29"/>
     </row>
     <row r="81" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="254" t="b">
+      <c r="A81" s="258" t="b">
         <v>0</v>
       </c>
-      <c r="B81" s="255" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="111">
+      <c r="B81" s="259" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81" s="114">
         <f>SUM(F81:BB81)</f>
         <v>2.5</v>
       </c>
-      <c r="D81" s="111">
+      <c r="D81" s="114">
         <f>SUM(F82:BB82)</f>
         <v>0</v>
       </c>
-      <c r="E81" s="112">
-        <f t="shared" si="5"/>
+      <c r="E81" s="115">
+        <f>(AVERAGE(C81,C82)-AVERAGE(D81,D82) )</f>
         <v>2.5</v>
       </c>
       <c r="F81" s="30"/>
@@ -7804,9 +7828,9 @@
       <c r="N81" s="31"/>
       <c r="O81" s="32"/>
       <c r="P81" s="25"/>
-      <c r="Q81" s="58"/>
-      <c r="R81" s="58"/>
-      <c r="S81" s="58"/>
+      <c r="Q81" s="57"/>
+      <c r="R81" s="57"/>
+      <c r="S81" s="57"/>
       <c r="T81" s="26"/>
       <c r="U81" s="30"/>
       <c r="V81" s="31"/>
@@ -7834,10 +7858,10 @@
       <c r="AR81" s="31"/>
       <c r="AS81" s="32"/>
       <c r="AT81" s="30"/>
-      <c r="AU81" s="70">
+      <c r="AU81" s="69">
         <v>1.5</v>
       </c>
-      <c r="AV81" s="71">
+      <c r="AV81" s="70">
         <v>1</v>
       </c>
       <c r="AW81" s="31"/>
@@ -7848,11 +7872,11 @@
       <c r="BB81" s="32"/>
     </row>
     <row r="82" spans="1:55" ht="16" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="249"/>
-      <c r="B82" s="251"/>
-      <c r="C82" s="102"/>
-      <c r="D82" s="102"/>
-      <c r="E82" s="106"/>
+      <c r="A82" s="253"/>
+      <c r="B82" s="255"/>
+      <c r="C82" s="98"/>
+      <c r="D82" s="98"/>
+      <c r="E82" s="102"/>
       <c r="F82" s="27"/>
       <c r="G82" s="28"/>
       <c r="H82" s="28"/>
@@ -7904,22 +7928,22 @@
       <c r="BB82" s="29"/>
     </row>
     <row r="83" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="252" t="b">
+      <c r="A83" s="256" t="b">
         <v>0</v>
       </c>
-      <c r="B83" s="253" t="s">
-        <v>51</v>
-      </c>
-      <c r="C83" s="111">
+      <c r="B83" s="257" t="s">
+        <v>50</v>
+      </c>
+      <c r="C83" s="114">
         <f>SUM(F83:BB83)</f>
         <v>5.5</v>
       </c>
-      <c r="D83" s="111">
+      <c r="D83" s="114">
         <f>SUM(F84:BB84)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="112">
-        <f t="shared" si="5"/>
+      <c r="E83" s="115">
+        <f>(AVERAGE(C83,C84)-AVERAGE(D83,D84) )</f>
         <v>5.5</v>
       </c>
       <c r="F83" s="30"/>
@@ -7933,9 +7957,9 @@
       <c r="N83" s="31"/>
       <c r="O83" s="32"/>
       <c r="P83" s="25"/>
-      <c r="Q83" s="58"/>
-      <c r="R83" s="58"/>
-      <c r="S83" s="58"/>
+      <c r="Q83" s="57"/>
+      <c r="R83" s="57"/>
+      <c r="S83" s="57"/>
       <c r="T83" s="26"/>
       <c r="U83" s="30"/>
       <c r="V83" s="31"/>
@@ -7965,27 +7989,27 @@
       <c r="AT83" s="30"/>
       <c r="AU83" s="31"/>
       <c r="AV83" s="30"/>
-      <c r="AW83" s="70">
+      <c r="AW83" s="69">
         <v>1.5</v>
       </c>
-      <c r="AX83" s="70">
+      <c r="AX83" s="69">
         <v>1.5</v>
       </c>
-      <c r="AY83" s="70">
+      <c r="AY83" s="69">
         <v>1.5</v>
       </c>
       <c r="AZ83" s="32"/>
-      <c r="BA83" s="71">
+      <c r="BA83" s="70">
         <v>1</v>
       </c>
       <c r="BB83" s="32"/>
     </row>
     <row r="84" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="249"/>
-      <c r="B84" s="251"/>
-      <c r="C84" s="102"/>
-      <c r="D84" s="102"/>
-      <c r="E84" s="106"/>
+      <c r="A84" s="253"/>
+      <c r="B84" s="255"/>
+      <c r="C84" s="98"/>
+      <c r="D84" s="98"/>
+      <c r="E84" s="102"/>
       <c r="F84" s="27"/>
       <c r="G84" s="28"/>
       <c r="H84" s="28"/>
@@ -8037,91 +8061,91 @@
       <c r="BB84" s="29"/>
     </row>
     <row r="85" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="252" t="b">
+      <c r="A85" s="256" t="b">
         <v>0</v>
       </c>
-      <c r="B85" s="266" t="s">
-        <v>50</v>
-      </c>
-      <c r="C85" s="111">
+      <c r="B85" s="270" t="s">
+        <v>49</v>
+      </c>
+      <c r="C85" s="114">
         <f>SUM(F85:BB85)</f>
         <v>0.5</v>
       </c>
-      <c r="D85" s="111">
+      <c r="D85" s="114">
         <f>SUM(F86:BB86)</f>
         <v>0</v>
       </c>
-      <c r="E85" s="112">
+      <c r="E85" s="115">
         <f>(AVERAGE(C85,C86)-AVERAGE(D85,D86) )</f>
         <v>0.5</v>
       </c>
       <c r="F85" s="25"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="57"/>
+      <c r="I85" s="57"/>
       <c r="J85" s="26"/>
       <c r="K85" s="25"/>
-      <c r="L85" s="58"/>
-      <c r="M85" s="58"/>
-      <c r="N85" s="58"/>
+      <c r="L85" s="57"/>
+      <c r="M85" s="57"/>
+      <c r="N85" s="57"/>
       <c r="O85" s="26"/>
       <c r="P85" s="25"/>
-      <c r="Q85" s="58"/>
-      <c r="R85" s="58"/>
-      <c r="S85" s="58"/>
+      <c r="Q85" s="57"/>
+      <c r="R85" s="57"/>
+      <c r="S85" s="57"/>
       <c r="T85" s="26"/>
       <c r="U85" s="25"/>
-      <c r="V85" s="58"/>
-      <c r="W85" s="58"/>
-      <c r="X85" s="58"/>
+      <c r="V85" s="57"/>
+      <c r="W85" s="57"/>
+      <c r="X85" s="57"/>
       <c r="Y85" s="26"/>
       <c r="Z85" s="25"/>
-      <c r="AA85" s="58"/>
-      <c r="AB85" s="58"/>
-      <c r="AC85" s="58"/>
+      <c r="AA85" s="57"/>
+      <c r="AB85" s="57"/>
+      <c r="AC85" s="57"/>
       <c r="AD85" s="26"/>
       <c r="AE85" s="25"/>
-      <c r="AF85" s="58"/>
-      <c r="AG85" s="58"/>
-      <c r="AH85" s="58"/>
+      <c r="AF85" s="57"/>
+      <c r="AG85" s="57"/>
+      <c r="AH85" s="57"/>
       <c r="AI85" s="26"/>
       <c r="AJ85" s="25"/>
-      <c r="AK85" s="58"/>
-      <c r="AL85" s="58"/>
-      <c r="AM85" s="58"/>
+      <c r="AK85" s="57"/>
+      <c r="AL85" s="57"/>
+      <c r="AM85" s="57"/>
       <c r="AN85" s="26"/>
       <c r="AO85" s="25"/>
-      <c r="AP85" s="58"/>
-      <c r="AQ85" s="58"/>
-      <c r="AR85" s="58"/>
+      <c r="AP85" s="57"/>
+      <c r="AQ85" s="57"/>
+      <c r="AR85" s="57"/>
       <c r="AS85" s="26"/>
       <c r="AT85" s="25"/>
-      <c r="AU85" s="58"/>
+      <c r="AU85" s="57"/>
       <c r="AV85" s="25"/>
-      <c r="AW85" s="58"/>
-      <c r="AX85" s="58"/>
-      <c r="AY85" s="58"/>
+      <c r="AW85" s="57"/>
+      <c r="AX85" s="57"/>
+      <c r="AY85" s="57"/>
       <c r="AZ85" s="26"/>
       <c r="BA85" s="25"/>
-      <c r="BB85" s="65">
+      <c r="BB85" s="64">
         <v>0.5</v>
       </c>
     </row>
     <row r="86" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A86" s="254"/>
-      <c r="B86" s="267"/>
-      <c r="C86" s="102"/>
-      <c r="D86" s="102"/>
-      <c r="E86" s="143"/>
+      <c r="A86" s="258"/>
+      <c r="B86" s="271"/>
+      <c r="C86" s="98"/>
+      <c r="D86" s="98"/>
+      <c r="E86" s="147"/>
       <c r="F86" s="25"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
       <c r="J86" s="26"/>
       <c r="K86" s="25"/>
-      <c r="L86" s="58"/>
-      <c r="M86" s="58"/>
-      <c r="N86" s="58"/>
+      <c r="L86" s="57"/>
+      <c r="M86" s="57"/>
+      <c r="N86" s="57"/>
       <c r="O86" s="26"/>
       <c r="P86" s="27"/>
       <c r="Q86" s="28"/>
@@ -8129,331 +8153,342 @@
       <c r="S86" s="28"/>
       <c r="T86" s="29"/>
       <c r="U86" s="25"/>
-      <c r="V86" s="58"/>
-      <c r="W86" s="58"/>
-      <c r="X86" s="58"/>
+      <c r="V86" s="57"/>
+      <c r="W86" s="57"/>
+      <c r="X86" s="57"/>
       <c r="Y86" s="26"/>
       <c r="Z86" s="25"/>
-      <c r="AA86" s="58"/>
-      <c r="AB86" s="58"/>
-      <c r="AC86" s="58"/>
+      <c r="AA86" s="57"/>
+      <c r="AB86" s="57"/>
+      <c r="AC86" s="57"/>
       <c r="AD86" s="26"/>
       <c r="AE86" s="25"/>
-      <c r="AF86" s="58"/>
-      <c r="AG86" s="58"/>
-      <c r="AH86" s="58"/>
+      <c r="AF86" s="57"/>
+      <c r="AG86" s="57"/>
+      <c r="AH86" s="57"/>
       <c r="AI86" s="26"/>
       <c r="AJ86" s="25"/>
-      <c r="AK86" s="58"/>
-      <c r="AL86" s="58"/>
-      <c r="AM86" s="58"/>
+      <c r="AK86" s="57"/>
+      <c r="AL86" s="57"/>
+      <c r="AM86" s="57"/>
       <c r="AN86" s="26"/>
       <c r="AO86" s="25"/>
-      <c r="AP86" s="58"/>
-      <c r="AQ86" s="58"/>
-      <c r="AR86" s="58"/>
+      <c r="AP86" s="57"/>
+      <c r="AQ86" s="57"/>
+      <c r="AR86" s="57"/>
       <c r="AS86" s="26"/>
       <c r="AT86" s="25"/>
-      <c r="AU86" s="58"/>
+      <c r="AU86" s="57"/>
       <c r="AV86" s="25"/>
-      <c r="AW86" s="58"/>
-      <c r="AX86" s="58"/>
-      <c r="AY86" s="58"/>
+      <c r="AW86" s="57"/>
+      <c r="AX86" s="57"/>
+      <c r="AY86" s="57"/>
       <c r="AZ86" s="26"/>
       <c r="BA86" s="25"/>
       <c r="BB86" s="26"/>
     </row>
     <row r="87" spans="1:55" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="268" t="s">
+      <c r="A87" s="272" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="269"/>
-      <c r="C87" s="272">
+      <c r="B87" s="273"/>
+      <c r="C87" s="276">
         <f>SUM(C89,C92)</f>
         <v>22</v>
       </c>
-      <c r="D87" s="272">
+      <c r="D87" s="276">
         <f>SUM(D89)</f>
-        <v>2.5</v>
-      </c>
-      <c r="E87" s="274">
+        <v>5.7</v>
+      </c>
+      <c r="E87" s="278">
         <f>(C87-D87)</f>
-        <v>19.5</v>
-      </c>
-      <c r="F87" s="256"/>
-      <c r="G87" s="257"/>
-      <c r="H87" s="257"/>
-      <c r="I87" s="257"/>
-      <c r="J87" s="257"/>
-      <c r="K87" s="257"/>
-      <c r="L87" s="257"/>
-      <c r="M87" s="257"/>
-      <c r="N87" s="257"/>
-      <c r="O87" s="257"/>
-      <c r="P87" s="257"/>
-      <c r="Q87" s="257"/>
-      <c r="R87" s="257"/>
-      <c r="S87" s="257"/>
-      <c r="T87" s="257"/>
-      <c r="U87" s="257"/>
-      <c r="V87" s="257"/>
-      <c r="W87" s="257"/>
-      <c r="X87" s="257"/>
-      <c r="Y87" s="257"/>
-      <c r="Z87" s="257"/>
-      <c r="AA87" s="257"/>
-      <c r="AB87" s="257"/>
-      <c r="AC87" s="257"/>
-      <c r="AD87" s="257"/>
-      <c r="AE87" s="257"/>
-      <c r="AF87" s="257"/>
-      <c r="AG87" s="257"/>
-      <c r="AH87" s="257"/>
-      <c r="AI87" s="257"/>
-      <c r="AJ87" s="257"/>
-      <c r="AK87" s="257"/>
-      <c r="AL87" s="257"/>
-      <c r="AM87" s="257"/>
-      <c r="AN87" s="257"/>
-      <c r="AO87" s="257"/>
-      <c r="AP87" s="257"/>
-      <c r="AQ87" s="257"/>
-      <c r="AR87" s="257"/>
-      <c r="AS87" s="257"/>
-      <c r="AT87" s="257"/>
-      <c r="AU87" s="257"/>
-      <c r="AV87" s="257"/>
-      <c r="AW87" s="257"/>
-      <c r="AX87" s="257"/>
-      <c r="AY87" s="257"/>
-      <c r="AZ87" s="257"/>
-      <c r="BA87" s="257"/>
-      <c r="BB87" s="258"/>
+        <v>16.3</v>
+      </c>
+      <c r="F87" s="260"/>
+      <c r="G87" s="261"/>
+      <c r="H87" s="261"/>
+      <c r="I87" s="261"/>
+      <c r="J87" s="261"/>
+      <c r="K87" s="261"/>
+      <c r="L87" s="261"/>
+      <c r="M87" s="261"/>
+      <c r="N87" s="261"/>
+      <c r="O87" s="261"/>
+      <c r="P87" s="261"/>
+      <c r="Q87" s="261"/>
+      <c r="R87" s="261"/>
+      <c r="S87" s="261"/>
+      <c r="T87" s="261"/>
+      <c r="U87" s="261"/>
+      <c r="V87" s="261"/>
+      <c r="W87" s="261"/>
+      <c r="X87" s="261"/>
+      <c r="Y87" s="261"/>
+      <c r="Z87" s="261"/>
+      <c r="AA87" s="261"/>
+      <c r="AB87" s="261"/>
+      <c r="AC87" s="261"/>
+      <c r="AD87" s="261"/>
+      <c r="AE87" s="261"/>
+      <c r="AF87" s="261"/>
+      <c r="AG87" s="261"/>
+      <c r="AH87" s="261"/>
+      <c r="AI87" s="261"/>
+      <c r="AJ87" s="261"/>
+      <c r="AK87" s="261"/>
+      <c r="AL87" s="261"/>
+      <c r="AM87" s="261"/>
+      <c r="AN87" s="261"/>
+      <c r="AO87" s="261"/>
+      <c r="AP87" s="261"/>
+      <c r="AQ87" s="261"/>
+      <c r="AR87" s="261"/>
+      <c r="AS87" s="261"/>
+      <c r="AT87" s="261"/>
+      <c r="AU87" s="261"/>
+      <c r="AV87" s="261"/>
+      <c r="AW87" s="261"/>
+      <c r="AX87" s="261"/>
+      <c r="AY87" s="261"/>
+      <c r="AZ87" s="261"/>
+      <c r="BA87" s="261"/>
+      <c r="BB87" s="262"/>
     </row>
     <row r="88" spans="1:55" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A88" s="270"/>
-      <c r="B88" s="271"/>
-      <c r="C88" s="273"/>
-      <c r="D88" s="273"/>
-      <c r="E88" s="275"/>
-      <c r="F88" s="259"/>
-      <c r="G88" s="260"/>
-      <c r="H88" s="260"/>
-      <c r="I88" s="260"/>
-      <c r="J88" s="260"/>
-      <c r="K88" s="260"/>
-      <c r="L88" s="260"/>
-      <c r="M88" s="260"/>
-      <c r="N88" s="260"/>
-      <c r="O88" s="260"/>
-      <c r="P88" s="260"/>
-      <c r="Q88" s="260"/>
-      <c r="R88" s="260"/>
-      <c r="S88" s="260"/>
-      <c r="T88" s="260"/>
-      <c r="U88" s="260"/>
-      <c r="V88" s="260"/>
-      <c r="W88" s="260"/>
-      <c r="X88" s="260"/>
-      <c r="Y88" s="260"/>
-      <c r="Z88" s="260"/>
-      <c r="AA88" s="260"/>
-      <c r="AB88" s="260"/>
-      <c r="AC88" s="260"/>
-      <c r="AD88" s="260"/>
-      <c r="AE88" s="260"/>
-      <c r="AF88" s="260"/>
-      <c r="AG88" s="260"/>
-      <c r="AH88" s="260"/>
-      <c r="AI88" s="260"/>
-      <c r="AJ88" s="260"/>
-      <c r="AK88" s="260"/>
-      <c r="AL88" s="260"/>
-      <c r="AM88" s="260"/>
-      <c r="AN88" s="260"/>
-      <c r="AO88" s="260"/>
-      <c r="AP88" s="260"/>
-      <c r="AQ88" s="260"/>
-      <c r="AR88" s="260"/>
-      <c r="AS88" s="260"/>
-      <c r="AT88" s="260"/>
-      <c r="AU88" s="260"/>
-      <c r="AV88" s="260"/>
-      <c r="AW88" s="260"/>
-      <c r="AX88" s="260"/>
-      <c r="AY88" s="260"/>
-      <c r="AZ88" s="260"/>
-      <c r="BA88" s="260"/>
-      <c r="BB88" s="261"/>
+      <c r="A88" s="274"/>
+      <c r="B88" s="275"/>
+      <c r="C88" s="277"/>
+      <c r="D88" s="277"/>
+      <c r="E88" s="279"/>
+      <c r="F88" s="263"/>
+      <c r="G88" s="264"/>
+      <c r="H88" s="264"/>
+      <c r="I88" s="264"/>
+      <c r="J88" s="264"/>
+      <c r="K88" s="264"/>
+      <c r="L88" s="264"/>
+      <c r="M88" s="264"/>
+      <c r="N88" s="264"/>
+      <c r="O88" s="264"/>
+      <c r="P88" s="264"/>
+      <c r="Q88" s="264"/>
+      <c r="R88" s="264"/>
+      <c r="S88" s="264"/>
+      <c r="T88" s="264"/>
+      <c r="U88" s="264"/>
+      <c r="V88" s="264"/>
+      <c r="W88" s="264"/>
+      <c r="X88" s="264"/>
+      <c r="Y88" s="264"/>
+      <c r="Z88" s="264"/>
+      <c r="AA88" s="264"/>
+      <c r="AB88" s="264"/>
+      <c r="AC88" s="264"/>
+      <c r="AD88" s="264"/>
+      <c r="AE88" s="264"/>
+      <c r="AF88" s="264"/>
+      <c r="AG88" s="264"/>
+      <c r="AH88" s="264"/>
+      <c r="AI88" s="264"/>
+      <c r="AJ88" s="264"/>
+      <c r="AK88" s="264"/>
+      <c r="AL88" s="264"/>
+      <c r="AM88" s="264"/>
+      <c r="AN88" s="264"/>
+      <c r="AO88" s="264"/>
+      <c r="AP88" s="264"/>
+      <c r="AQ88" s="264"/>
+      <c r="AR88" s="264"/>
+      <c r="AS88" s="264"/>
+      <c r="AT88" s="264"/>
+      <c r="AU88" s="264"/>
+      <c r="AV88" s="264"/>
+      <c r="AW88" s="264"/>
+      <c r="AX88" s="264"/>
+      <c r="AY88" s="264"/>
+      <c r="AZ88" s="264"/>
+      <c r="BA88" s="264"/>
+      <c r="BB88" s="265"/>
     </row>
     <row r="89" spans="1:55" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="41"/>
-      <c r="B89" s="262" t="s">
-        <v>64</v>
-      </c>
-      <c r="C89" s="111">
+      <c r="B89" s="266" t="s">
+        <v>63</v>
+      </c>
+      <c r="C89" s="114">
         <f>SUM(F89:BB89)</f>
         <v>22</v>
       </c>
-      <c r="D89" s="111">
+      <c r="D89" s="114">
         <f>SUM(F90:BB90)</f>
-        <v>2.5</v>
-      </c>
-      <c r="E89" s="112">
+        <v>5.7</v>
+      </c>
+      <c r="E89" s="115">
         <f>(AVERAGE(C89,C90)-AVERAGE(D89,D90) )</f>
-        <v>19.5</v>
-      </c>
-      <c r="F89" s="64">
+        <v>16.3</v>
+      </c>
+      <c r="F89" s="63">
         <v>1</v>
       </c>
-      <c r="G89" s="66">
+      <c r="G89" s="65">
         <v>0.5</v>
       </c>
-      <c r="H89" s="66">
+      <c r="H89" s="65">
         <v>0.5</v>
       </c>
-      <c r="I89" s="66">
+      <c r="I89" s="65">
         <v>0.5</v>
       </c>
-      <c r="J89" s="67"/>
-      <c r="K89" s="68"/>
-      <c r="L89" s="66">
+      <c r="J89" s="66"/>
+      <c r="K89" s="67"/>
+      <c r="L89" s="65">
         <v>0.5</v>
       </c>
-      <c r="M89" s="66">
+      <c r="M89" s="65">
         <v>0.5</v>
       </c>
-      <c r="N89" s="66">
+      <c r="N89" s="65">
         <v>0.5</v>
       </c>
-      <c r="O89" s="67"/>
-      <c r="P89" s="68"/>
-      <c r="Q89" s="66">
+      <c r="O89" s="66"/>
+      <c r="P89" s="67"/>
+      <c r="Q89" s="65">
         <v>0.5</v>
       </c>
-      <c r="R89" s="66">
+      <c r="R89" s="65">
         <v>0.5</v>
       </c>
-      <c r="S89" s="66">
+      <c r="S89" s="65">
         <v>1</v>
       </c>
-      <c r="T89" s="67"/>
-      <c r="U89" s="68"/>
-      <c r="V89" s="66">
+      <c r="T89" s="66"/>
+      <c r="U89" s="67"/>
+      <c r="V89" s="65">
         <v>0.5</v>
       </c>
-      <c r="W89" s="66">
+      <c r="W89" s="65">
         <v>0.5</v>
       </c>
-      <c r="X89" s="66">
+      <c r="X89" s="65">
         <v>1</v>
       </c>
-      <c r="Y89" s="67"/>
-      <c r="Z89" s="68"/>
-      <c r="AA89" s="66">
+      <c r="Y89" s="66"/>
+      <c r="Z89" s="67"/>
+      <c r="AA89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AB89" s="66">
+      <c r="AB89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AC89" s="66">
+      <c r="AC89" s="65">
         <v>1</v>
       </c>
-      <c r="AD89" s="67"/>
-      <c r="AE89" s="64">
+      <c r="AD89" s="66"/>
+      <c r="AE89" s="63">
         <v>1</v>
       </c>
-      <c r="AF89" s="66">
+      <c r="AF89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AG89" s="66">
+      <c r="AG89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AH89" s="66">
+      <c r="AH89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AI89" s="67"/>
-      <c r="AJ89" s="64">
+      <c r="AI89" s="66"/>
+      <c r="AJ89" s="63">
         <v>0.5</v>
       </c>
-      <c r="AK89" s="66">
+      <c r="AK89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AL89" s="66">
+      <c r="AL89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AM89" s="66">
+      <c r="AM89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AN89" s="67"/>
-      <c r="AO89" s="64">
+      <c r="AN89" s="66"/>
+      <c r="AO89" s="63">
         <v>0.5</v>
       </c>
-      <c r="AP89" s="66">
+      <c r="AP89" s="65">
         <v>0.5</v>
       </c>
       <c r="AQ89" s="31"/>
-      <c r="AR89" s="66">
+      <c r="AR89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AS89" s="67"/>
-      <c r="AT89" s="64">
+      <c r="AS89" s="66"/>
+      <c r="AT89" s="63">
         <v>1</v>
       </c>
-      <c r="AU89" s="65">
+      <c r="AU89" s="64">
         <v>0.5</v>
       </c>
-      <c r="AV89" s="64">
+      <c r="AV89" s="63">
         <v>1</v>
       </c>
-      <c r="AW89" s="66">
+      <c r="AW89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AX89" s="66">
+      <c r="AX89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AY89" s="66">
+      <c r="AY89" s="65">
         <v>0.5</v>
       </c>
-      <c r="AZ89" s="67"/>
-      <c r="BA89" s="64">
+      <c r="AZ89" s="66"/>
+      <c r="BA89" s="63">
         <v>1</v>
       </c>
-      <c r="BB89" s="65">
+      <c r="BB89" s="64">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:55" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A90" s="42"/>
-      <c r="B90" s="263"/>
-      <c r="C90" s="102"/>
-      <c r="D90" s="102"/>
-      <c r="E90" s="143"/>
-      <c r="F90" s="77">
+      <c r="B90" s="267"/>
+      <c r="C90" s="98"/>
+      <c r="D90" s="98"/>
+      <c r="E90" s="147"/>
+      <c r="F90" s="75">
         <v>1</v>
       </c>
-      <c r="G90" s="78">
+      <c r="G90" s="76">
         <v>0.5</v>
       </c>
-      <c r="H90" s="78">
+      <c r="H90" s="76">
         <v>0.5</v>
       </c>
-      <c r="I90" s="78">
+      <c r="I90" s="76">
         <v>0.5</v>
       </c>
       <c r="J90" s="45"/>
       <c r="K90" s="25"/>
-      <c r="L90" s="58"/>
-      <c r="N90" s="58"/>
+      <c r="L90" s="57"/>
+      <c r="M90" s="44">
+        <v>0.3</v>
+      </c>
+      <c r="N90" s="57"/>
       <c r="O90" s="26"/>
       <c r="P90" s="43"/>
-      <c r="Q90" s="44"/>
-      <c r="R90" s="44"/>
+      <c r="Q90" s="44">
+        <v>0.5</v>
+      </c>
+      <c r="R90" s="44">
+        <v>0.5</v>
+      </c>
       <c r="S90" s="44"/>
       <c r="T90" s="45"/>
       <c r="U90" s="43"/>
-      <c r="V90" s="44"/>
-      <c r="W90" s="44"/>
+      <c r="V90" s="44">
+        <v>0.4</v>
+      </c>
+      <c r="W90" s="44">
+        <v>1.5</v>
+      </c>
       <c r="X90" s="44"/>
       <c r="Y90" s="45"/>
       <c r="Z90" s="43"/>
@@ -8485,19 +8520,19 @@
       <c r="AZ90" s="45"/>
       <c r="BA90" s="43"/>
       <c r="BB90" s="45"/>
-      <c r="BC90" s="76"/>
+      <c r="BC90" s="74"/>
     </row>
     <row r="91" spans="1:55" ht="15.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A91" s="278"/>
-      <c r="B91" s="279" t="s">
+      <c r="A91" s="280"/>
+      <c r="B91" s="282" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="281">
+      <c r="C91" s="284">
         <f>SUM((F91:BB91))</f>
-        <v>1</v>
-      </c>
-      <c r="D91" s="111"/>
-      <c r="E91" s="101"/>
+        <v>2</v>
+      </c>
+      <c r="D91" s="114"/>
+      <c r="E91" s="97"/>
       <c r="F91" s="30"/>
       <c r="G91" s="31"/>
       <c r="H91" s="31"/>
@@ -8505,15 +8540,15 @@
       <c r="J91" s="32"/>
       <c r="K91" s="30"/>
       <c r="L91" s="31"/>
-      <c r="M91" s="56">
+      <c r="M91" s="55">
         <v>1</v>
       </c>
       <c r="N91" s="31"/>
       <c r="O91" s="32"/>
       <c r="P91" s="25"/>
-      <c r="Q91" s="58"/>
-      <c r="R91" s="58"/>
-      <c r="S91" s="58"/>
+      <c r="Q91" s="57"/>
+      <c r="R91" s="57"/>
+      <c r="S91" s="57"/>
       <c r="T91" s="26"/>
       <c r="U91" s="30"/>
       <c r="V91" s="31"/>
@@ -8537,7 +8572,9 @@
       <c r="AN91" s="32"/>
       <c r="AO91" s="30"/>
       <c r="AP91" s="31"/>
-      <c r="AQ91" s="31"/>
+      <c r="AQ91" s="55">
+        <v>1</v>
+      </c>
       <c r="AR91" s="31"/>
       <c r="AS91" s="32"/>
       <c r="AT91" s="30"/>
@@ -8549,14 +8586,14 @@
       <c r="AZ91" s="32"/>
       <c r="BA91" s="30"/>
       <c r="BB91" s="32"/>
-      <c r="BC91" s="76"/>
+      <c r="BC91" s="74"/>
     </row>
     <row r="92" spans="1:55" ht="15.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A92" s="277"/>
-      <c r="B92" s="280"/>
-      <c r="C92" s="282"/>
-      <c r="D92" s="283"/>
-      <c r="E92" s="283"/>
+      <c r="A92" s="281"/>
+      <c r="B92" s="283"/>
+      <c r="C92" s="285"/>
+      <c r="D92" s="286"/>
+      <c r="E92" s="286"/>
       <c r="F92" s="27"/>
       <c r="G92" s="28"/>
       <c r="H92" s="28"/>
@@ -8564,7 +8601,9 @@
       <c r="J92" s="29"/>
       <c r="K92" s="27"/>
       <c r="L92" s="28"/>
-      <c r="M92" s="28"/>
+      <c r="M92" s="28">
+        <v>0.7</v>
+      </c>
       <c r="N92" s="28"/>
       <c r="O92" s="29"/>
       <c r="P92" s="27"/>
@@ -8617,61 +8656,61 @@
       </c>
       <c r="D93" s="47">
         <f>SUM(D21,D29,D41,D49,D67,D75,D87, D15,D6)</f>
-        <v>10.5</v>
+        <v>28.53</v>
       </c>
       <c r="E93" s="48">
         <f>SUM(E21,E29,E41,E49,E67,E75,E87,E6,E15)</f>
-        <v>69.5</v>
-      </c>
-      <c r="F93" s="264"/>
-      <c r="G93" s="265"/>
-      <c r="H93" s="265"/>
-      <c r="I93" s="265"/>
-      <c r="J93" s="265"/>
-      <c r="K93" s="265"/>
-      <c r="L93" s="265"/>
-      <c r="M93" s="265"/>
-      <c r="N93" s="265"/>
-      <c r="O93" s="265"/>
-      <c r="P93" s="265"/>
-      <c r="Q93" s="265"/>
-      <c r="R93" s="265"/>
-      <c r="S93" s="265"/>
-      <c r="T93" s="265"/>
-      <c r="U93" s="265"/>
-      <c r="V93" s="265"/>
-      <c r="W93" s="265"/>
-      <c r="X93" s="265"/>
-      <c r="Y93" s="265"/>
-      <c r="Z93" s="265"/>
-      <c r="AA93" s="265"/>
-      <c r="AB93" s="265"/>
-      <c r="AC93" s="265"/>
-      <c r="AD93" s="265"/>
-      <c r="AE93" s="265"/>
-      <c r="AF93" s="265"/>
-      <c r="AG93" s="265"/>
-      <c r="AH93" s="265"/>
-      <c r="AI93" s="265"/>
-      <c r="AJ93" s="265"/>
-      <c r="AK93" s="265"/>
-      <c r="AL93" s="265"/>
-      <c r="AM93" s="265"/>
-      <c r="AN93" s="265"/>
-      <c r="AO93" s="265"/>
-      <c r="AP93" s="265"/>
-      <c r="AQ93" s="265"/>
-      <c r="AR93" s="265"/>
-      <c r="AS93" s="265"/>
-      <c r="AT93" s="265"/>
-      <c r="AU93" s="265"/>
-      <c r="AV93" s="265"/>
-      <c r="AW93" s="265"/>
-      <c r="AX93" s="265"/>
-      <c r="AY93" s="265"/>
-      <c r="AZ93" s="265"/>
-      <c r="BA93" s="265"/>
-      <c r="BB93" s="265"/>
+        <v>51.47</v>
+      </c>
+      <c r="F93" s="268"/>
+      <c r="G93" s="269"/>
+      <c r="H93" s="269"/>
+      <c r="I93" s="269"/>
+      <c r="J93" s="269"/>
+      <c r="K93" s="269"/>
+      <c r="L93" s="269"/>
+      <c r="M93" s="269"/>
+      <c r="N93" s="269"/>
+      <c r="O93" s="269"/>
+      <c r="P93" s="269"/>
+      <c r="Q93" s="269"/>
+      <c r="R93" s="269"/>
+      <c r="S93" s="269"/>
+      <c r="T93" s="269"/>
+      <c r="U93" s="269"/>
+      <c r="V93" s="269"/>
+      <c r="W93" s="269"/>
+      <c r="X93" s="269"/>
+      <c r="Y93" s="269"/>
+      <c r="Z93" s="269"/>
+      <c r="AA93" s="269"/>
+      <c r="AB93" s="269"/>
+      <c r="AC93" s="269"/>
+      <c r="AD93" s="269"/>
+      <c r="AE93" s="269"/>
+      <c r="AF93" s="269"/>
+      <c r="AG93" s="269"/>
+      <c r="AH93" s="269"/>
+      <c r="AI93" s="269"/>
+      <c r="AJ93" s="269"/>
+      <c r="AK93" s="269"/>
+      <c r="AL93" s="269"/>
+      <c r="AM93" s="269"/>
+      <c r="AN93" s="269"/>
+      <c r="AO93" s="269"/>
+      <c r="AP93" s="269"/>
+      <c r="AQ93" s="269"/>
+      <c r="AR93" s="269"/>
+      <c r="AS93" s="269"/>
+      <c r="AT93" s="269"/>
+      <c r="AU93" s="269"/>
+      <c r="AV93" s="269"/>
+      <c r="AW93" s="269"/>
+      <c r="AX93" s="269"/>
+      <c r="AY93" s="269"/>
+      <c r="AZ93" s="269"/>
+      <c r="BA93" s="269"/>
+      <c r="BB93" s="269"/>
     </row>
     <row r="94" spans="1:55" ht="75.599999999999994" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C94" s="49" t="s">
@@ -8693,11 +8732,7 @@
       <c r="J96" s="52"/>
       <c r="K96" s="53"/>
       <c r="O96" s="54"/>
-      <c r="P96" s="54"/>
-      <c r="Q96" s="54"/>
-      <c r="R96" s="54"/>
-      <c r="X96" s="55"/>
-      <c r="AD96" s="56"/>
+      <c r="AD96" s="55"/>
     </row>
     <row r="97" spans="5:30" x14ac:dyDescent="0.55000000000000004">
       <c r="E97" s="52"/>
@@ -8711,9 +8746,6 @@
       </c>
       <c r="O97" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="X97" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="AD97" s="2" t="s">
         <v>22</v>
@@ -8912,11 +8944,6 @@
     <mergeCell ref="C21:C22"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E21:E22"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
     <mergeCell ref="F15:BB16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
@@ -8928,16 +8955,33 @@
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="AO1:AS1"/>
+    <mergeCell ref="AO2:AS2"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="C1:E2"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="K1:O1"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="P1:T1"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="AV2:AZ2"/>
+    <mergeCell ref="BA2:BB2"/>
+    <mergeCell ref="F6:BB6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
@@ -8956,21 +9000,9 @@
     <mergeCell ref="AJ1:AN1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AV1:AZ1"/>
-    <mergeCell ref="AO1:AS1"/>
-    <mergeCell ref="AO2:AS2"/>
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="C1:E2"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="K1:O1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="P1:T1"/>
-    <mergeCell ref="P2:T2"/>
-    <mergeCell ref="AV2:AZ2"/>
-    <mergeCell ref="BA2:BB2"/>
-    <mergeCell ref="F6:BB6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="32" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="28" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
